--- a/Results/Hydrogen/hydrogen acidification results.xlsx
+++ b/Results/Hydrogen/hydrogen acidification results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1857340927966069</v>
+        <v>0.1857340927966087</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09701696200747977</v>
+        <v>0.09701696200747935</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3121296782093866</v>
+        <v>0.312129678209386</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09701696200747977</v>
+        <v>0.09701696200747935</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09701696200747977</v>
+        <v>0.09701696200747935</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2480335106839744</v>
+        <v>0.2480335106839734</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4498802099559149</v>
+        <v>0.449880209955913</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09701696200747977</v>
+        <v>0.09701696200747935</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2327693227070065</v>
+        <v>0.2327693227070053</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1267865409028715</v>
+        <v>0.1267865409028706</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9928481639916339</v>
+        <v>0.2394934131306479</v>
       </c>
     </row>
     <row r="3">
@@ -558,16 +558,16 @@
         <v>0.003914306244165961</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003578162453133323</v>
+        <v>0.00357816245313333</v>
       </c>
       <c r="D3" t="n">
         <v>0.003914306244165961</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003645440212022909</v>
+        <v>0.003645440212022925</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003645440212022909</v>
+        <v>0.003645440212022919</v>
       </c>
       <c r="G3" t="n">
         <v>0.003893578033175781</v>
@@ -576,7 +576,7 @@
         <v>0.003914306244165961</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003776331094216962</v>
+        <v>0.003776331094216981</v>
       </c>
       <c r="J3" t="n">
         <v>0.003914306244165961</v>
@@ -595,34 +595,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0117383507166846</v>
+        <v>0.006002747738987907</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005621131586167595</v>
+        <v>0.005621131586167589</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006253692663250144</v>
+        <v>0.006253680033066898</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005456617870408679</v>
+        <v>0.005456617870408663</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005848174496503677</v>
+        <v>0.005848174496503688</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01171762250569442</v>
+        <v>0.01171762250569444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01193158230737018</v>
+        <v>0.01193158230737015</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0116003755667356</v>
+        <v>0.005864772589038929</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0062152145565595</v>
+        <v>0.006215214556559606</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00588298036875692</v>
+        <v>0.005882980368756916</v>
       </c>
       <c r="L4" t="n">
         <v>0.006272075705435198</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008481529061823243</v>
+        <v>0.008481529061823232</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008343553911874276</v>
+        <v>0.008343553911874274</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008481373679581915</v>
+        <v>0.008481373679581931</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008338972503004667</v>
+        <v>0.008338972503004681</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008338972503004667</v>
+        <v>0.008338972503004681</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008460800850833086</v>
+        <v>0.008460800850833087</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008481529061823243</v>
+        <v>0.008481529061823232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008343553911874276</v>
+        <v>0.008343553911874274</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008481529061823243</v>
+        <v>0.008481529061823232</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008481529061823243</v>
+        <v>0.008481529061823232</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008481529061823243</v>
+        <v>0.008481529061823232</v>
       </c>
     </row>
     <row r="6">
@@ -678,25 +678,25 @@
         <v>0.01728627851729874</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02638653445321613</v>
+        <v>0.02638653445321616</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02844298523747886</v>
+        <v>0.02844298523747891</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02385952968094734</v>
+        <v>0.02385952968094735</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01743857599249397</v>
+        <v>0.01743857599249401</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02650615702620017</v>
+        <v>0.02650615702620016</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02652688523718991</v>
+        <v>0.02652688523719001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02638891008724142</v>
+        <v>0.0263889100872414</v>
       </c>
       <c r="J6" t="n">
         <v>0.02652870128071151</v>
@@ -705,7 +705,7 @@
         <v>0.01711462950339104</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0361794716426265</v>
+        <v>0.03617947164262653</v>
       </c>
     </row>
     <row r="7">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02264740886382463</v>
+        <v>0.02264740886382465</v>
       </c>
       <c r="C7" t="n">
         <v>0.02801408680434025</v>
@@ -724,28 +724,28 @@
         <v>0.02815206362428436</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03436633290144035</v>
+        <v>0.03436633290144033</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02801408011519053</v>
+        <v>0.02801408011519041</v>
       </c>
       <c r="G7" t="n">
-        <v>0.028131333743299</v>
+        <v>0.02813133374329904</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02815206195428912</v>
+        <v>0.0281520619542892</v>
       </c>
       <c r="I7" t="n">
         <v>0.02801408680434025</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02815206195428912</v>
+        <v>0.0281520619542892</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02122072070346631</v>
+        <v>0.02496264503762673</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02815206195428912</v>
+        <v>0.0281520619542892</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006748262312231487</v>
+        <v>0.006748262312231723</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004214783797620495</v>
+        <v>0.004214783797620491</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004147608422264328</v>
+        <v>0.004147608422264329</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004214783797620495</v>
+        <v>0.004214783797620491</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004214783797620495</v>
+        <v>0.004214783797620491</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005615900277369519</v>
+        <v>0.005615900277369541</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002278615155344393</v>
+        <v>0.002278615155344388</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004214783797620495</v>
+        <v>0.004214783797620491</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006108547361710685</v>
+        <v>0.006108547361710694</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008123322068307249</v>
+        <v>0.008123322068307265</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006214099283694671</v>
+        <v>0.006214099283694667</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008886826971756991</v>
+        <v>0.008886826971756995</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005246693453395966</v>
+        <v>0.005246693453395964</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007827769645855623</v>
+        <v>0.007827769645855631</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005246693453395966</v>
+        <v>0.005246693453395964</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005246693453395966</v>
+        <v>0.005246693453395964</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008411137965197659</v>
+        <v>0.008411137965197669</v>
       </c>
       <c r="H9" t="n">
-        <v>0.007074158089975174</v>
+        <v>0.007074158089975173</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005246693453395966</v>
+        <v>0.005246693453395964</v>
       </c>
       <c r="J9" t="n">
         <v>0.008628006249577413</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009447013566813618</v>
+        <v>0.009447013566813621</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008672573748275566</v>
+        <v>0.008672573748275576</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0156794804301401</v>
+        <v>0.01567948043014004</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03039589348898141</v>
+        <v>0.03039589348898135</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02972091806296252</v>
+        <v>0.02972091806296256</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03039589348898141</v>
+        <v>0.03039589348898135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03039589348898141</v>
+        <v>0.03039589348898135</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03511499962507032</v>
+        <v>0.03511499962506962</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02888744275140724</v>
+        <v>0.02888744275140718</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03039589348898141</v>
+        <v>0.03039589348898135</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03976421165000668</v>
+        <v>0.03976421165000667</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02945402794500921</v>
+        <v>0.02945402794500931</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02387587740237481</v>
+        <v>0.0225738121706574</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00303521971075691</v>
+        <v>0.003035219710756906</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002798293720050262</v>
+        <v>0.002798293720050252</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00303521971075691</v>
+        <v>0.003035219710756906</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002842412302599364</v>
+        <v>0.002842412302599349</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002842412302599363</v>
+        <v>0.00284241230259935</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003017760240580169</v>
+        <v>0.003017760240580161</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00303521971075691</v>
+        <v>0.003035219710756906</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002917425899776541</v>
+        <v>0.00291742589977653</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00303521971075691</v>
+        <v>0.003035219710756906</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00303521971075691</v>
+        <v>0.003035219710756906</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00303521971075691</v>
+        <v>0.003035219710756906</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008116621742232301</v>
+        <v>0.008116621742232292</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00421492998653682</v>
+        <v>0.004214929986536801</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004365818172762467</v>
+        <v>0.008141999116131855</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004094901296630751</v>
+        <v>0.004094901296630741</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00425596677758044</v>
+        <v>0.004255966777580435</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008099162272055541</v>
+        <v>0.004356404448464948</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008216597585221391</v>
+        <v>0.008216597585221372</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004256070107661322</v>
+        <v>0.004256070107661307</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008139755141598162</v>
+        <v>0.008139755141598161</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004377765042779841</v>
+        <v>0.004377765042779955</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004374541506231503</v>
+        <v>0.004374541506231499</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006126251383387502</v>
+        <v>0.006126251383387488</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006008457572407141</v>
+        <v>0.006008457572407116</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006126128266375222</v>
+        <v>0.006126128266375206</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00600303469177067</v>
+        <v>0.006003034691770649</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00600303469177067</v>
+        <v>0.006003034691770649</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006108791913210765</v>
+        <v>0.00610879191321075</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006126251383387502</v>
+        <v>0.006126251383387488</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006008457572407141</v>
+        <v>0.006008457572407116</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006126251383387502</v>
+        <v>0.006126251383387488</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006126251383387502</v>
+        <v>0.006126251383387488</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006126251383387502</v>
+        <v>0.006126251383387488</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01291855669580208</v>
+        <v>0.01291855669580204</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01954247762443441</v>
+        <v>0.01954247762443433</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0210626894204239</v>
+        <v>0.02106268942042385</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01769803136190745</v>
+        <v>0.01769803136190738</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01301142087295291</v>
+        <v>0.01301142087295287</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01964652214984481</v>
+        <v>0.01964652214984474</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01966398162002188</v>
+        <v>0.01966398162002184</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01954618780904118</v>
+        <v>0.01954618780904114</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01966530728945397</v>
+        <v>0.01966530728945392</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01279325696471605</v>
+        <v>0.01279325696471601</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02671014199677084</v>
+        <v>0.02671014199677074</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01239168899590098</v>
+        <v>0.01239168899590093</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01506415616407566</v>
+        <v>0.01506415616407563</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01518195125234832</v>
+        <v>0.01518195125234826</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01828405845929876</v>
+        <v>0.01828405845929872</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01506415547105379</v>
+        <v>0.01506415547105375</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0151644905048793</v>
+        <v>0.01516449050487924</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01518194997505601</v>
+        <v>0.01518194997505599</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01506415616407566</v>
+        <v>0.01506415616407563</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01518194997505601</v>
+        <v>0.01518194997505599</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01356526234275726</v>
+        <v>0.01356526234275721</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01518194997505601</v>
+        <v>0.01518194997505599</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009388527262897827</v>
+        <v>0.009388527262897817</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004447795831448501</v>
+        <v>0.004447795831448497</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009022070137413655</v>
+        <v>0.009022070137413648</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004447795831448501</v>
+        <v>0.004447795831448497</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004447795831448501</v>
+        <v>0.004447795831448497</v>
       </c>
       <c r="G8" t="n">
         <v>0.008897115634265693</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009120575280819644</v>
+        <v>0.009120575280819642</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004447795831448501</v>
+        <v>0.004447795831448497</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008835078673566315</v>
+        <v>0.008835078673566312</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009009201200431726</v>
+        <v>0.009009201200431725</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0092264935569637</v>
+        <v>0.009278461369751682</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009347104620078463</v>
+        <v>0.009347104620078454</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004703600067320935</v>
+        <v>0.004703600067320934</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009197864033112613</v>
+        <v>0.009197864033112603</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004703600067320935</v>
+        <v>0.004703600067320934</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004703600067320935</v>
+        <v>0.004703600067320934</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009144532246432026</v>
+        <v>0.009144532246432016</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00923840529142469</v>
+        <v>0.009238405291424695</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004703600067320935</v>
+        <v>0.004703600067320934</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009121976017102015</v>
+        <v>0.009121976017102008</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009192638211618339</v>
+        <v>0.009192638211618346</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009281379670013377</v>
+        <v>0.00928137967001337</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03380694518029954</v>
+        <v>0.03380694518029965</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1796038114713066</v>
+        <v>0.1796038114713068</v>
       </c>
       <c r="D2" t="n">
-        <v>0.172683944236633</v>
+        <v>0.1726839442366328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05526593035883252</v>
+        <v>0.05526593035883265</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05526593035883252</v>
+        <v>0.05526593035883265</v>
       </c>
       <c r="G2" t="n">
-        <v>0.119573320914719</v>
+        <v>0.1195733209147189</v>
       </c>
       <c r="H2" t="n">
         <v>0.1328431577757918</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05526593035883252</v>
+        <v>0.05526593035883265</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1981289972521834</v>
+        <v>0.1981289972521836</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0593676715137433</v>
+        <v>0.0593676715137434</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1936283805566681</v>
+        <v>0.193628380556668</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003525626344098711</v>
+        <v>0.003525626344098732</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003369076271382521</v>
+        <v>0.003369076271382522</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003525626344098711</v>
+        <v>0.003525626344098732</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003291929898167047</v>
+        <v>0.003291929898167018</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003291929898167048</v>
+        <v>0.003291929898167021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003504826951850797</v>
+        <v>0.003504826951850786</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003525626344098711</v>
+        <v>0.003525626344098732</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003386360955834123</v>
+        <v>0.003386360955834095</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003525626344098707</v>
+        <v>0.003525626344098732</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003525626344098711</v>
+        <v>0.003525626344098732</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003525626344098711</v>
+        <v>0.003525626344098732</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009828287873760883</v>
+        <v>0.005287124720452591</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005393701607407602</v>
+        <v>0.005393701607407597</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005451009025788004</v>
+        <v>0.005450994599426765</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004873849377653688</v>
+        <v>0.00487384937765369</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005142603731810343</v>
+        <v>0.005142603731810345</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009807488481512965</v>
+        <v>0.009807488481512952</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01003722146933662</v>
+        <v>0.01003722146933663</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009689022485496258</v>
+        <v>0.00968902248549626</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009855281323432935</v>
+        <v>0.009855281323432961</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005214709407349328</v>
+        <v>0.005214709407349303</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005329192701179511</v>
+        <v>0.005329192701179531</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007290632401697183</v>
+        <v>0.007290632401697219</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007292254210918633</v>
+        <v>0.00729225421091863</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007290513464460016</v>
+        <v>0.00729051346446004</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007150737664041041</v>
+        <v>0.007150737664041037</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007150737664041041</v>
+        <v>0.007150737664041037</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007269833009449254</v>
+        <v>0.00726983300944926</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007290632401697183</v>
+        <v>0.007290632401697219</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007151367013432584</v>
+        <v>0.007151367013432576</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007290632401697183</v>
+        <v>0.007290632401697219</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007290632401697183</v>
+        <v>0.007290632401697219</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007290632401697183</v>
+        <v>0.007290632401697219</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01498275071342003</v>
+        <v>0.01498275071342004</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02287714872984305</v>
+        <v>0.02287714872987531</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02451082523577918</v>
+        <v>0.02451082523577915</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02057781586618874</v>
+        <v>0.02057781586618872</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01509333499588113</v>
+        <v>0.01509333499588111</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02285363402530167</v>
+        <v>0.02285363402530168</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0228744334175567</v>
+        <v>0.02287443341755667</v>
       </c>
       <c r="I6" t="n">
-        <v>0.022735168029285</v>
+        <v>0.02273516802928498</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02287598435895785</v>
+        <v>0.02287598435895783</v>
       </c>
       <c r="K6" t="n">
         <v>0.01483615865562231</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03111795589348187</v>
+        <v>0.03111795589348185</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01646695537523476</v>
+        <v>0.01646695537523477</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02031392267203298</v>
+        <v>0.02031392267203295</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02031230267918092</v>
+        <v>0.02031230267918093</v>
       </c>
       <c r="E7" t="n">
         <v>0.02461048084090031</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02017303272752702</v>
+        <v>0.02017303272752701</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02029150147056361</v>
+        <v>0.02029150147056359</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02031230086281153</v>
+        <v>0.02031230086281151</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02017303547454691</v>
+        <v>0.0201730354745469</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02031230086281153</v>
+        <v>0.02031230086281151</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01547032403144686</v>
+        <v>0.01808429334943042</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02031230086281153</v>
+        <v>0.02031230086281151</v>
       </c>
     </row>
     <row r="8">
@@ -1547,31 +1547,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02332096655863213</v>
+        <v>0.02332096655863214</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006448317613038133</v>
+        <v>0.0006448317613038141</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002897751283397405</v>
+        <v>0.002897751283397398</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005077736034473469</v>
+        <v>0.005077736034473472</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005077736034473469</v>
+        <v>0.005077736034473472</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007829178191277281</v>
+        <v>0.00782917819127728</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004166554379894859</v>
+        <v>0.004166554379894866</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005077736034473469</v>
+        <v>0.005077736034473472</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006907857879169947</v>
+        <v>0.006907857879169934</v>
       </c>
       <c r="K8" t="n">
         <v>0.01416655500659431</v>
@@ -1587,34 +1587,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02333723344842171</v>
+        <v>0.0233372334484217</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002851171155555863</v>
+        <v>0.002851171155555857</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005039668304565206</v>
+        <v>0.005039668304565222</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005613963781961169</v>
+        <v>0.005613963781961166</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005613963781961169</v>
+        <v>0.005613963781961166</v>
       </c>
       <c r="G9" t="n">
         <v>0.009142329310190742</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005558713107085111</v>
+        <v>0.005558713107085119</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005613963781961169</v>
+        <v>0.005613963781961166</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009197711727701391</v>
+        <v>0.009197711727701405</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01461783325797913</v>
+        <v>0.01461783325797914</v>
       </c>
       <c r="L9" t="n">
         <v>0.004279232942128708</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02368919567650024</v>
+        <v>0.02368919567650015</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1073403050958527</v>
+        <v>0.1073403050958526</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1159948583435175</v>
+        <v>0.1159948583435174</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03738099926706009</v>
+        <v>0.03738099926705999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03738099926706009</v>
+        <v>0.03738099926705999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07313977714534421</v>
+        <v>0.0731397771453436</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07644959280814324</v>
+        <v>0.07644959280814317</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03738099926706009</v>
+        <v>0.03738099926705999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1182180631447173</v>
+        <v>0.1182180631447172</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02919021197172981</v>
+        <v>0.02919021197172969</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06412245224694861</v>
+        <v>0.06412245224694856</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003297116172674322</v>
+        <v>0.003297116172674249</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0031336565300157</v>
+        <v>0.003133656530015697</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003297116172674322</v>
+        <v>0.003297116172674249</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003204193080899494</v>
+        <v>0.003204193080899479</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003204193080899493</v>
+        <v>0.003204193080899484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003277978928802504</v>
+        <v>0.003277978928802478</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003297116172674322</v>
+        <v>0.003297116172674249</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003168636060463988</v>
+        <v>0.003168636060463981</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003297116172674322</v>
+        <v>0.003297116172674248</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003297116172674322</v>
+        <v>0.003297116172674249</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003297116172674322</v>
+        <v>0.003297116172674249</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00891694543490432</v>
+        <v>0.008916945434904198</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004873388415008208</v>
+        <v>0.004873388415008173</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004952170009581919</v>
+        <v>0.008959630890162858</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004503516305476475</v>
+        <v>0.004503516305476466</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004711983421112718</v>
+        <v>0.004711983421112703</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00481566068474859</v>
+        <v>0.004815660684748536</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009145660911213762</v>
+        <v>0.009145660911213684</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004706317816410062</v>
+        <v>0.004706317816410059</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004993597722587969</v>
+        <v>0.004993597722587927</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004779969338866864</v>
+        <v>0.004779969338866846</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004838102413252128</v>
+        <v>0.004838102413252049</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006695333304234801</v>
+        <v>0.006695333304234782</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00669685237865719</v>
+        <v>0.006696852378657189</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006695225390118386</v>
+        <v>0.006695225390118414</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006573858994226881</v>
+        <v>0.006573858994226876</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006573858994226881</v>
+        <v>0.006573858994226876</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006676196060362983</v>
+        <v>0.006676196060362993</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006695333304234801</v>
+        <v>0.006695333304234782</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006566853192024481</v>
+        <v>0.006566853192024479</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006695333304234801</v>
+        <v>0.006695333304234782</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006695333304234801</v>
+        <v>0.006695333304234782</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006695333304234801</v>
+        <v>0.006695333304234782</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01387113624931978</v>
+        <v>0.01387113624931968</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02115309270871689</v>
+        <v>0.02115309270875221</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02265125312760556</v>
+        <v>0.0226512531276055</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01903332211470048</v>
+        <v>0.01903332211470045</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01397741676973221</v>
+        <v>0.01397741676973218</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02112418147485818</v>
+        <v>0.02112418147485817</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02114331871874852</v>
+        <v>0.02114331871874848</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02101483860651966</v>
+        <v>0.02101483860651967</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02114474791046831</v>
+        <v>0.02114474791046825</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0137360517264385</v>
+        <v>0.0137360517264384</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02873972139763895</v>
+        <v>0.02873972139763884</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01398223841119848</v>
+        <v>0.01398223841119841</v>
       </c>
       <c r="C7" t="n">
         <v>0.01717972504490618</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01717820756702538</v>
+        <v>0.01717820756702531</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02073780407987721</v>
+        <v>0.0207378040798772</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01704972424259932</v>
+        <v>0.01704972424259929</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01715906872661202</v>
+        <v>0.01715906872661194</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01717820597048382</v>
+        <v>0.01717820597048375</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01704972585827349</v>
+        <v>0.01704972585827348</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01717820597048382</v>
+        <v>0.01717820597048375</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01532645048659993</v>
+        <v>0.01532645048659986</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01717820597048382</v>
+        <v>0.01717820597048375</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02342488824118188</v>
+        <v>0.02342488824118189</v>
       </c>
       <c r="C8" t="n">
         <v>0.001838559266967116</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003859388111929234</v>
+        <v>0.003859388111929223</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005263840850978629</v>
+        <v>0.005263840850978633</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005263840850978629</v>
+        <v>0.005263840850978633</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008594531603599895</v>
+        <v>0.008594531603599893</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005030115355362441</v>
+        <v>0.005030115355362413</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005263840850978629</v>
+        <v>0.005263840850978633</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008362714528278333</v>
+        <v>0.008362714528278312</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01459056070986313</v>
+        <v>0.01459056070986309</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004093496182518872</v>
+        <v>0.004093496182518841</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0233255023004836</v>
+        <v>0.02332550230048359</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003166328010071805</v>
+        <v>0.003166328010071804</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005316613021261303</v>
+        <v>0.005316613021261297</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005588851964255247</v>
+        <v>0.005588851964255249</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005588851964255247</v>
+        <v>0.005588851964255249</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009347416863625418</v>
+        <v>0.009347416863625384</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005794751544189096</v>
+        <v>0.005794751544189037</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005588851964255247</v>
+        <v>0.005588851964255249</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009701005605975055</v>
+        <v>0.009701005605975024</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0146561527161456</v>
+        <v>0.01465615271614557</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004704513222468911</v>
+        <v>0.004704513222468883</v>
       </c>
     </row>
   </sheetData>
@@ -2102,34 +2102,34 @@
         <v>0.01128357393799489</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06922041094361397</v>
+        <v>0.06922041094361404</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07801406630083317</v>
+        <v>0.07801406630083296</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01636399357343547</v>
+        <v>0.0163639935734353</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01636399357343547</v>
+        <v>0.0163639935734353</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04433107378834522</v>
+        <v>0.04433107378834481</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0521312215012491</v>
+        <v>0.05213122150124896</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01636399357343547</v>
+        <v>0.0163639935734353</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05145926794690549</v>
+        <v>0.05145926794690544</v>
       </c>
       <c r="K2" t="n">
         <v>0.01675636976287087</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0265152420105296</v>
+        <v>0.02651524201052957</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003146094322986239</v>
+        <v>0.003146094322986241</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002979088895688549</v>
+        <v>0.002979088895688551</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003146094322986239</v>
+        <v>0.003146094322986241</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003075395045564983</v>
+        <v>0.003075395045564974</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003075395045564983</v>
+        <v>0.003075395045564974</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00313136933027937</v>
+        <v>0.003131369330279371</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003146094322986239</v>
+        <v>0.003146094322986241</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003046948433119672</v>
+        <v>0.003046948433119684</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003146094322986239</v>
+        <v>0.003146094322986241</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003146094322986239</v>
+        <v>0.003146094322986241</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003146094322986239</v>
+        <v>0.003146094322986241</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008515917224158264</v>
+        <v>0.004565979397008239</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004578778506468109</v>
+        <v>0.004578778506466657</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004648345758812541</v>
+        <v>0.004648345758811663</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004275369189447742</v>
+        <v>0.00427536918944775</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004469808412403214</v>
+        <v>0.004469808412403213</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004551254404301374</v>
+        <v>0.008501192231451411</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008735331760449336</v>
+        <v>0.008735331760449364</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004466833507141675</v>
+        <v>0.008416771334291712</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004699090485448294</v>
+        <v>0.008529340452848469</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004536692421361271</v>
+        <v>0.004536692421361266</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004560458473420862</v>
+        <v>0.004560458473421359</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006410172232372143</v>
+        <v>0.006410172232372149</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006411766577229069</v>
+        <v>0.006411766577229055</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006410063110149798</v>
+        <v>0.006410063110149785</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006319348111678135</v>
+        <v>0.006319348111678126</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006319348111678135</v>
+        <v>0.006319348111678126</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006395447239665322</v>
+        <v>0.006395447239665297</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006410172232372143</v>
+        <v>0.006410172232372149</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006311026342505619</v>
+        <v>0.006311026342505605</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006410172232372143</v>
+        <v>0.006410172232372149</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006410172232372143</v>
+        <v>0.006410172232372149</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006410172232372143</v>
+        <v>0.006410172232372149</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01349486601666565</v>
+        <v>0.01349486601666559</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02061403201392831</v>
+        <v>0.02061403201388924</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02207685991460683</v>
+        <v>0.02207685991460684</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01856826553945302</v>
+        <v>0.01856826553945303</v>
       </c>
       <c r="F6" t="n">
         <v>0.01362606491262019</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0205882269916527</v>
+        <v>0.02058822699165265</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02060295198437887</v>
+        <v>0.02060295198437886</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02050380609449298</v>
+        <v>0.02050380609449295</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02060434892633347</v>
+        <v>0.02060434892633348</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01336282967055604</v>
+        <v>0.01336282967055603</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02802794214560899</v>
+        <v>0.02802794214560898</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0126695875870012</v>
+        <v>0.01266958758700118</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01553676547996039</v>
+        <v>0.01553676547996037</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01553517235037793</v>
+        <v>0.0155351723503779</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01874284733740767</v>
+        <v>0.01874284733740764</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01543602391664844</v>
+        <v>0.01543602391664843</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01552044614239665</v>
+        <v>0.01552044614239661</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01553517113510347</v>
+        <v>0.01553517113510346</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01543602524523693</v>
+        <v>0.0154360252452369</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01553517113510347</v>
+        <v>0.01553517113510346</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01380747955580113</v>
+        <v>0.01192688962821574</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01553517113510347</v>
+        <v>0.01553517113510346</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02362047751337475</v>
+        <v>0.02362047751337479</v>
       </c>
       <c r="C8" t="n">
         <v>0.002524932069377083</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004588738238050573</v>
+        <v>0.00458873823805058</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005445081705693998</v>
+        <v>0.005445081705694008</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005445081705693998</v>
+        <v>0.005445081705694008</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009043296347317722</v>
+        <v>0.009043296347317736</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005356426361282847</v>
+        <v>0.005356426361282859</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005445081705693998</v>
+        <v>0.005445081705694008</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009189336001955825</v>
+        <v>0.009189336001955848</v>
       </c>
       <c r="K8" t="n">
         <v>0.014701065178221</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00472180236052114</v>
+        <v>0.004721802360521147</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02334987487409508</v>
+        <v>0.02334987487409505</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003321032220250008</v>
+        <v>0.003321032220250006</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005501119341130269</v>
+        <v>0.005501119341130279</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005475317249701138</v>
+        <v>0.005475317249701144</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005475317249701137</v>
+        <v>0.005475317249701144</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009396565600021891</v>
+        <v>0.009396565600021898</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005814640476364388</v>
+        <v>0.005814640476364391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005475317249701138</v>
+        <v>0.005475317249701144</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009622982945345932</v>
+        <v>0.009622982945345934</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01459192760888926</v>
+        <v>0.01459192760888928</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004865729782529747</v>
+        <v>0.004865729782529743</v>
       </c>
     </row>
   </sheetData>
@@ -2498,31 +2498,31 @@
         <v>0.01361325948938709</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01441526830376925</v>
+        <v>0.01441526830376926</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09409248131360284</v>
+        <v>0.09409248131360295</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02251872941426057</v>
+        <v>0.02251872941426058</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02251872941426057</v>
+        <v>0.02251872941426058</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07585414718808418</v>
+        <v>0.07585414718808386</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1060271508964349</v>
+        <v>0.1060271508964351</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02251872941426057</v>
+        <v>0.02251872941426058</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1868336155604768</v>
+        <v>0.1868336155604766</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04094041563000357</v>
+        <v>0.04094041563000347</v>
       </c>
       <c r="L2" t="n">
         <v>0.1804926760457592</v>
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003134237111875764</v>
+        <v>0.003134237111875765</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002878265025402603</v>
+        <v>0.002878265025402605</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003134237111875764</v>
+        <v>0.003134237111875765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002956601956202141</v>
+        <v>0.002956601956202133</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002956601956202137</v>
+        <v>0.002956601956202133</v>
       </c>
       <c r="G3" t="n">
         <v>0.003113835371873374</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003134237111875764</v>
+        <v>0.003134237111875765</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002997445005418486</v>
+        <v>0.002997445005418483</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003134237111875764</v>
+        <v>0.003134237111875765</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003134237111875764</v>
+        <v>0.003134237111875765</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003134237111875764</v>
+        <v>0.003134237111875765</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008820575856277688</v>
+        <v>0.004585380425500463</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004439893908174246</v>
+        <v>0.004439893908174232</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00466306302887701</v>
+        <v>0.004663063028877053</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004211067312423101</v>
+        <v>0.004211067312423124</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004443361367064966</v>
+        <v>0.004443361367064962</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004564978685498073</v>
+        <v>0.004564978685498068</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00900856948493612</v>
+        <v>0.009008569484936117</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008683783749820399</v>
+        <v>0.004448588319043182</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008837206366585559</v>
+        <v>0.008837206366585554</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004546073621881436</v>
+        <v>0.004546073621881432</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004629969808570051</v>
+        <v>0.004629969808570052</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006691237222486925</v>
+        <v>0.006691237222486919</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006689988729976518</v>
+        <v>0.006689988729976511</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006691127214152838</v>
+        <v>0.006691127214152834</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006567159757514693</v>
+        <v>0.006567159757514682</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006567159757514693</v>
+        <v>0.006567159757514682</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006670835482484532</v>
+        <v>0.006670835482484526</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006691237222486925</v>
+        <v>0.006691237222486919</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006554445116029648</v>
+        <v>0.006554445116029643</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006691237222486925</v>
+        <v>0.006691237222486919</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006691237222486925</v>
+        <v>0.006691237222486919</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006691237222486925</v>
+        <v>0.006691237222486919</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01421976963576357</v>
+        <v>0.01421976963576355</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02184357606207982</v>
+        <v>0.02184357606207978</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0234092983496341</v>
+        <v>0.02340929834963404</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01962494226831294</v>
+        <v>0.01962494226831293</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01433189388483284</v>
+        <v>0.01433189388483281</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02181064808045768</v>
+        <v>0.02181064808045767</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02183104982046473</v>
+        <v>0.02183104982046469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02169425771400279</v>
+        <v>0.02169425771400276</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02183254565481754</v>
+        <v>0.02183254565481752</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01407838619871809</v>
+        <v>0.01407838619871806</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02978166841803347</v>
+        <v>0.02978166841803339</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01480361104059371</v>
+        <v>0.01480361104059372</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01827666176725146</v>
+        <v>0.01827666176725145</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01827791212088184</v>
+        <v>0.01827791212088185</v>
       </c>
       <c r="E7" t="n">
         <v>0.02215038534636387</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01814111645632009</v>
+        <v>0.01814111645632008</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01825750851975949</v>
+        <v>0.01825750851975948</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01827791025976187</v>
+        <v>0.01827791025976186</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01814111815330459</v>
+        <v>0.01814111815330457</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01827791025976187</v>
+        <v>0.01827791025976186</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01390314690024993</v>
+        <v>0.01390314690024994</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01827791025976187</v>
+        <v>0.01827791025976186</v>
       </c>
     </row>
     <row r="8">
@@ -2738,10 +2738,10 @@
         <v>0.02355536303549632</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003742652694071676</v>
+        <v>0.003742652694071674</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004325415778656323</v>
+        <v>0.00432541577865632</v>
       </c>
       <c r="E8" t="n">
         <v>0.005483197351800155</v>
@@ -2750,22 +2750,22 @@
         <v>0.005483197351800155</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00852192509776213</v>
+        <v>0.008521925097762116</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004325426698964342</v>
+        <v>0.004325426698964338</v>
       </c>
       <c r="I8" t="n">
         <v>0.005483197351800155</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006896458226316982</v>
+        <v>0.006896458226316984</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01433442154876642</v>
+        <v>0.0143344215487664</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002185859083031001</v>
+        <v>0.002185859083030998</v>
       </c>
     </row>
     <row r="9">
@@ -2778,34 +2778,34 @@
         <v>0.02331046676616175</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003760954704040577</v>
+        <v>0.003760954704040574</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005400839920840834</v>
+        <v>0.005400839920840832</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005584738468406233</v>
+        <v>0.005584738468406237</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005584738468406233</v>
+        <v>0.005584738468406237</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009261978533975057</v>
+        <v>0.009261978533975056</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005402655091661252</v>
+        <v>0.00540265509166125</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005584738468406233</v>
+        <v>0.005584738468406237</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009047142186338866</v>
+        <v>0.009047142186338859</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01454230855153834</v>
+        <v>0.01454230855153832</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004132131631778367</v>
+        <v>0.004132131631778365</v>
       </c>
     </row>
   </sheetData>
@@ -2894,28 +2894,28 @@
         <v>0.008886508093734759</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01317268604645613</v>
+        <v>0.01317268604645614</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01684615541312432</v>
+        <v>0.01684615541312433</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01779344540443877</v>
+        <v>0.01779344540443886</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01779344540443877</v>
+        <v>0.01779344540443886</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01930173780373413</v>
+        <v>0.0193017378037343</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02161078001053101</v>
+        <v>0.02161078001053103</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01779344540443877</v>
+        <v>0.01779344540443886</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05859999191388922</v>
+        <v>0.0585999919138892</v>
       </c>
       <c r="K2" t="n">
         <v>0.01456636157822958</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002972851186683708</v>
+        <v>0.002972851186683717</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002784270327579668</v>
+        <v>0.002784270327579669</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002972851186683708</v>
+        <v>0.002972851186683717</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002943242391238182</v>
+        <v>0.002943242391238181</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002943242391238182</v>
+        <v>0.002943242391238181</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002955016341762889</v>
+        <v>0.002955016341762888</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002972851186683708</v>
+        <v>0.002972851186683717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002852619155348078</v>
+        <v>0.002852619155348076</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002972851186683708</v>
+        <v>0.002972851186683717</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002972851186683708</v>
+        <v>0.002972851186683717</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002972851186683708</v>
+        <v>0.002972851186683717</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004260390574682109</v>
+        <v>0.004260390574682105</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004199964412999211</v>
+        <v>0.00419996441299923</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008031784316505178</v>
+        <v>0.004256200544849228</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00400454080677076</v>
+        <v>0.004004540806770756</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004151164644148567</v>
+        <v>0.004151164644148561</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004242555729761289</v>
+        <v>0.008007014548328639</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008202939558767131</v>
+        <v>0.00820293955876714</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004140158543346478</v>
+        <v>0.00790461736191383</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004385640482587943</v>
+        <v>0.004385640482587946</v>
       </c>
       <c r="K4" t="n">
         <v>0.004252079227031282</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004259471337629566</v>
+        <v>0.004259471337629541</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006109511391004164</v>
+        <v>0.006109511391004169</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006110713551229462</v>
+        <v>0.006110713551229464</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0061094078321025</v>
+        <v>0.006109407832102508</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006006213610329776</v>
+        <v>0.006006213610329785</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006006213610329776</v>
+        <v>0.006006213610329785</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006091676546083355</v>
+        <v>0.006091676546083362</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006109511391004164</v>
+        <v>0.006109511391004169</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005989279359668525</v>
+        <v>0.005989279359668529</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006109511391004164</v>
+        <v>0.006109511391004169</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006109511391004164</v>
+        <v>0.006109511391004169</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006109511391004164</v>
+        <v>0.006109511391004169</v>
       </c>
     </row>
     <row r="6">
@@ -3051,28 +3051,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01306866511017576</v>
+        <v>0.01306866511017578</v>
       </c>
       <c r="C6" t="n">
         <v>0.0199943187450795</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02140761927594572</v>
+        <v>0.0214076192759457</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0179820544801242</v>
+        <v>0.01798205448012418</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01317753143953856</v>
+        <v>0.01317753143953855</v>
       </c>
       <c r="G6" t="n">
         <v>0.01995761717232089</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01997545201725533</v>
+        <v>0.01997545201725531</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01985521998590606</v>
+        <v>0.01985521998590605</v>
       </c>
       <c r="J6" t="n">
         <v>0.01997680939851304</v>
@@ -3081,7 +3081,7 @@
         <v>0.01294036799744087</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02719016847761714</v>
+        <v>0.02719016847761711</v>
       </c>
     </row>
     <row r="7">
@@ -3091,16 +3091,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01237791235480483</v>
+        <v>0.01237791235480484</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01519428580433721</v>
+        <v>0.01519428580433723</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01519308474417127</v>
+        <v>0.01519308474417126</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01832149982247225</v>
+        <v>0.01832149982247227</v>
       </c>
       <c r="F7" t="n">
         <v>0.01507285100371937</v>
@@ -3109,19 +3109,19 @@
         <v>0.0151752487991911</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01519308364411192</v>
+        <v>0.01519308364411194</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01507285161277629</v>
+        <v>0.0150728516127763</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01519308364411192</v>
+        <v>0.01519308364411194</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01356196280573723</v>
+        <v>0.01164828019946499</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01519308364411192</v>
+        <v>0.01519308364411194</v>
       </c>
     </row>
     <row r="8">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02350549945617978</v>
+        <v>0.0235054994561798</v>
       </c>
       <c r="C8" t="n">
         <v>0.003630471259481205</v>
@@ -3146,22 +3146,22 @@
         <v>0.005433564885670241</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009572345349231692</v>
+        <v>0.009572345349231699</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005869733732258802</v>
+        <v>0.005869733732258805</v>
       </c>
       <c r="I8" t="n">
         <v>0.005433564885670241</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009386077305255326</v>
+        <v>0.009386077305255317</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01469007521125328</v>
+        <v>0.0146900752112533</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004494994219524949</v>
+        <v>0.004494994219524951</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02320506077260873</v>
+        <v>0.02320506077260875</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003642918945343532</v>
+        <v>0.003642918945343535</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005968908297821989</v>
+        <v>0.00596890829782199</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005485880696889408</v>
+        <v>0.005485880696889409</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005485880696889408</v>
+        <v>0.005485880696889409</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009576694942729108</v>
+        <v>0.00957669494272911</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005941619670253061</v>
+        <v>0.005941619670253063</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005485880696889408</v>
+        <v>0.005485880696889409</v>
       </c>
       <c r="J9" t="n">
         <v>0.009913562968758701</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0145518882911737</v>
+        <v>0.01455188829117372</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004718611999280246</v>
+        <v>0.004718611999280248</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008599788720060404</v>
+        <v>0.008599788720060399</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01346274811336178</v>
+        <v>0.0134627481133618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01608041960289702</v>
+        <v>0.016080419602897</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01548685597904245</v>
+        <v>0.01548685597904238</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01548685597904245</v>
+        <v>0.01548685597904238</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0151149782584145</v>
+        <v>0.01511497825841445</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01769093862546032</v>
+        <v>0.01769093862546029</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01548685597904245</v>
+        <v>0.01548685597904238</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01847570971537861</v>
+        <v>0.01847570971537865</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01287060428164855</v>
+        <v>0.01287060428164853</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01571103033876279</v>
+        <v>0.01571103033876277</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002954578612930089</v>
+        <v>0.002954578612930088</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002786988927392979</v>
+        <v>0.00278698892739298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002954578612930089</v>
+        <v>0.002954578612930088</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002926399416784665</v>
+        <v>0.002926399416784654</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002926399416784664</v>
+        <v>0.002926399416784655</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002940925079378593</v>
+        <v>0.002940925079378793</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002954578612930089</v>
+        <v>0.002954578612930088</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002862227079973064</v>
+        <v>0.002862227079973418</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002954578612930089</v>
+        <v>0.002954578612930088</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002954578612930089</v>
+        <v>0.002954578612930088</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002954578612930089</v>
+        <v>0.002954578612930088</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007986145282362321</v>
+        <v>0.007986145282362323</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004184109339604595</v>
+        <v>0.004184109339604589</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004227794892643457</v>
+        <v>0.004227794892643461</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004005968574783977</v>
+        <v>0.004005968574783979</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004150907830300541</v>
+        <v>0.004150907830300537</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007972491748810829</v>
+        <v>0.007972491748810819</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008161312477235574</v>
+        <v>0.008161312477235564</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004142130184297133</v>
+        <v>0.004142130184297121</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007979415100607007</v>
+        <v>0.007979415100607002</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004232294500588191</v>
+        <v>0.004232294500588166</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004227452599272739</v>
+        <v>0.004227452599272745</v>
       </c>
     </row>
     <row r="5">
@@ -3410,25 +3410,25 @@
         <v>0.006040010612943437</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00604143890546729</v>
+        <v>0.006041438905467288</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006039902446159964</v>
+        <v>0.006039902446159959</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005961110266741984</v>
+        <v>0.005961110266741973</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005961110266741984</v>
+        <v>0.005961110266741973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006026357079391937</v>
+        <v>0.006026357079391934</v>
       </c>
       <c r="H5" t="n">
         <v>0.006040010612943437</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005947659079986416</v>
+        <v>0.005947659079986405</v>
       </c>
       <c r="J5" t="n">
         <v>0.006040010612943437</v>
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01297529362770462</v>
+        <v>0.01297529362770465</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01983915304642059</v>
+        <v>0.01983915304642058</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02124338736754395</v>
+        <v>0.02124338736754393</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01787094065536517</v>
+        <v>0.01787094065536515</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01310810498754308</v>
+        <v>0.01310810498754307</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01980973644454876</v>
+        <v>0.01980973644454875</v>
       </c>
       <c r="H6" t="n">
         <v>0.01982338997811559</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01973103844514326</v>
+        <v>0.01973103844514325</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01982473582502027</v>
+        <v>0.01982473582502026</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01284808672218538</v>
+        <v>0.01284808672218539</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0269767992444398</v>
+        <v>0.02697679924443982</v>
       </c>
     </row>
     <row r="7">
@@ -3487,34 +3487,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01184816324457499</v>
+        <v>0.011848163244575</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0145185351998468</v>
+        <v>0.01451853519984681</v>
       </c>
       <c r="D7" t="n">
         <v>0.01451710791205327</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01750465994712832</v>
+        <v>0.01750465994712831</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01442475478912062</v>
+        <v>0.01442475478912063</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01450345337377146</v>
+        <v>0.01450345337377145</v>
       </c>
       <c r="H7" t="n">
         <v>0.01451710690732295</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01442475537436594</v>
+        <v>0.01442475537436595</v>
       </c>
       <c r="J7" t="n">
         <v>0.01451710690732295</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01297071088996181</v>
+        <v>0.01290797160938364</v>
       </c>
       <c r="L7" t="n">
         <v>0.01451710690732295</v>
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02344097197687573</v>
+        <v>0.0234409719768757</v>
       </c>
       <c r="C8" t="n">
         <v>0.003569242767451581</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005910841272076371</v>
+        <v>0.005910841272076368</v>
       </c>
       <c r="E8" t="n">
         <v>0.00527542936203775</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005275429362037751</v>
+        <v>0.00527542936203775</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009539081751066674</v>
+        <v>0.009539081751066665</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005908848551871917</v>
+        <v>0.005908848551871915</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00527542936203775</v>
+        <v>0.005275429362037749</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00969189468597426</v>
+        <v>0.009691894685974253</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01462786460577066</v>
+        <v>0.01462786460577065</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004770948543742895</v>
+        <v>0.004770948543742894</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02313751624076587</v>
+        <v>0.02313751624076586</v>
       </c>
       <c r="C9" t="n">
         <v>0.003586486207324619</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00593186037392016</v>
+        <v>0.005931860373920155</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005297596930931912</v>
+        <v>0.00529759693093191</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005297596930931912</v>
+        <v>0.00529759693093191</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009486547864386184</v>
+        <v>0.009486547864386177</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00593124442637413</v>
+        <v>0.005931244426374127</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005297596930931912</v>
+        <v>0.00529759693093191</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009677771141076119</v>
+        <v>0.009677771141076109</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0144667556255521</v>
+        <v>0.01446675562555209</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004783553925014899</v>
+        <v>0.004783553925014897</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01169407178780477</v>
+        <v>0.01169407178780471</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01399991781024968</v>
+        <v>0.01399991781024969</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02816559652470748</v>
+        <v>0.02816559652470734</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02124715671069841</v>
+        <v>0.02124715671069842</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02124715671069841</v>
+        <v>0.02124715671069842</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03599552325970799</v>
+        <v>0.03599552325970728</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08974580575605198</v>
+        <v>0.089745805756052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02124715671069841</v>
+        <v>0.02124715671069842</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02657857207788686</v>
+        <v>0.02657857207788678</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02002351076511489</v>
+        <v>0.02002351076511476</v>
       </c>
       <c r="L2" t="n">
-        <v>0.146478422057849</v>
+        <v>0.1464784220578487</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003045597705752435</v>
+        <v>0.003045597705752361</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002819185724277051</v>
+        <v>0.002819185724277052</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003045597705752435</v>
+        <v>0.003045597705752361</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002909068940805865</v>
+        <v>0.002909068940805868</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002909068940805865</v>
+        <v>0.002909068940805868</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003026538488224369</v>
+        <v>0.003026538488224328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003045597705752435</v>
+        <v>0.003045597705752361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002917340125959107</v>
+        <v>0.002917340125959142</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003045597705752435</v>
+        <v>0.003045597705752361</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003045597705752435</v>
+        <v>0.003045597705752361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003045597705752435</v>
+        <v>0.003045597705752361</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008447442212042052</v>
+        <v>0.004361730923878697</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004275105173268606</v>
+        <v>0.004275105173268638</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004359507655346522</v>
+        <v>0.004359507655346403</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004061802677096863</v>
+        <v>0.004061802677096871</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004234649794931344</v>
+        <v>0.004234649794931345</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008428382994513952</v>
+        <v>0.008428382994513864</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008624556688906488</v>
+        <v>0.008624556688906382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004233473344085521</v>
+        <v>0.008319184632248769</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00845056480605149</v>
+        <v>0.008450564806051379</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004331685449439429</v>
+        <v>0.004331685449439326</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00439673503791813</v>
+        <v>0.004396735037918096</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006425580897100065</v>
+        <v>0.006425580897100039</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006426126817819836</v>
+        <v>0.006426126817819834</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006425471598322769</v>
+        <v>0.00642547159832269</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006312963575285934</v>
+        <v>0.006312963575285941</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006312963575285934</v>
+        <v>0.006312963575285941</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006406521679571983</v>
+        <v>0.006406521679571912</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006425580897100065</v>
+        <v>0.006425580897100039</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006297323317306777</v>
+        <v>0.006297323317306779</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006425580897100065</v>
+        <v>0.006425580897100039</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006425580897100065</v>
+        <v>0.006425580897100039</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006425580897100065</v>
+        <v>0.006425580897100039</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0138249789472619</v>
+        <v>0.01382497894726175</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02122499971772424</v>
+        <v>0.02122499971772423</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02273883093634413</v>
+        <v>0.02273883093634406</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01907526166731154</v>
+        <v>0.01907526166731156</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01394014483693793</v>
+        <v>0.01394014483693796</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0211888690763531</v>
+        <v>0.02118886907635307</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02120792829388547</v>
+        <v>0.0212079282938855</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02107967071408786</v>
+        <v>0.0210796707140879</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02120937925471459</v>
+        <v>0.02120937925471455</v>
       </c>
       <c r="K6" t="n">
         <v>0.01368783687275609</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02892003623839454</v>
+        <v>0.02892003623839464</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01378842251211406</v>
+        <v>0.01378842251211398</v>
       </c>
       <c r="C7" t="n">
         <v>0.0169923128387813</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01699176761066363</v>
+        <v>0.01699176761066359</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0205600994905708</v>
+        <v>0.02056009949057083</v>
       </c>
       <c r="F7" t="n">
         <v>0.01686350774116003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01697270770053345</v>
+        <v>0.01697270770053341</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01699176691806153</v>
+        <v>0.01699176691806151</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01686350933826825</v>
+        <v>0.01686350933826828</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01699176691806153</v>
+        <v>0.01699176691806151</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01506043536879847</v>
+        <v>0.01513573688005702</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01699176691806153</v>
+        <v>0.01699176691806151</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02349378267962533</v>
+        <v>0.02349378267962528</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003704821485575325</v>
+        <v>0.003704821485575327</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005750062879498972</v>
+        <v>0.005750062879498949</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005407482986501695</v>
+        <v>0.005407482986501699</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005407482986501695</v>
+        <v>0.005407482986501698</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009276796416252987</v>
+        <v>0.009276796416252956</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004558469504504035</v>
+        <v>0.004558469504504017</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005407482986501695</v>
+        <v>0.005407482986501699</v>
       </c>
       <c r="J8" t="n">
-        <v>0.010133912908002</v>
+        <v>0.01013391290800202</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01465158805226538</v>
+        <v>0.01465158805226533</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002760216168259006</v>
+        <v>0.002760216168258973</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02322485960990345</v>
+        <v>0.02322485960990338</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003718578644304687</v>
+        <v>0.003718578644304691</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005924258246818736</v>
+        <v>0.005924258246818663</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005493912547239493</v>
+        <v>0.005493912547239498</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005493912547239493</v>
+        <v>0.005493912547239498</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009489255481609078</v>
+        <v>0.009489255481609064</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005440469474818464</v>
+        <v>0.005440469474818393</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005493912547239494</v>
+        <v>0.005493912547239499</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01020385195563605</v>
+        <v>0.01020385195563603</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01457701323522163</v>
+        <v>0.0145770132352216</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004305034823266512</v>
+        <v>0.00430503482326649</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.009224635767217347</v>
+        <v>0.009224635767217302</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01339024999273036</v>
+        <v>0.01339024999273035</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01622628238611925</v>
+        <v>0.01622628238611923</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01743459616672002</v>
+        <v>0.01743459616671991</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01743459616672002</v>
+        <v>0.01743459616671991</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0154439965268568</v>
+        <v>0.01544399652685653</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01795602488678419</v>
+        <v>0.01795602488678411</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01743459616672002</v>
+        <v>0.01743459616671991</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0191341924879677</v>
+        <v>0.01913419248796768</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01421667979447941</v>
+        <v>0.01421667979447921</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01567988978571772</v>
+        <v>0.01567988978571765</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002949231022718584</v>
+        <v>0.00294923102271855</v>
       </c>
       <c r="C3" t="n">
         <v>0.002764351900169945</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002949231022718584</v>
+        <v>0.00294923102271855</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002934839717943013</v>
+        <v>0.002934839717943011</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002934839717943013</v>
+        <v>0.002934839717943012</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002931539216082094</v>
+        <v>0.002931539216082064</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002949231022718584</v>
+        <v>0.00294923102271855</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002829897850590911</v>
+        <v>0.002829897850590896</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002949231022718584</v>
+        <v>0.00294923102271855</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002949231022718584</v>
+        <v>0.00294923102271855</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002949231022718584</v>
+        <v>0.00294923102271855</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007962199281257911</v>
+        <v>0.004216371331814192</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004161848994556395</v>
+        <v>0.004161848994556424</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004215189211770888</v>
+        <v>0.004215173240882235</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003970185482568504</v>
+        <v>0.003970185482568499</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004109062950914607</v>
+        <v>0.004109062950914603</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004198679525177699</v>
+        <v>0.004198679525177698</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008135453483146933</v>
+        <v>0.008135453483146924</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004097038159686528</v>
+        <v>0.007842866109130231</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004326671718739099</v>
+        <v>0.007955387992859541</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004211409481256989</v>
+        <v>0.004211409481256984</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004210316876003835</v>
+        <v>0.004210316876003826</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006041149430154906</v>
+        <v>0.006041149430154887</v>
       </c>
       <c r="C5" t="n">
         <v>0.006042567243285214</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00604104606799876</v>
+        <v>0.00604104606799875</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005942210787692713</v>
+        <v>0.005942210787692719</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005942210787692713</v>
+        <v>0.005942210787692719</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006023457623518402</v>
+        <v>0.006023457623518393</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006041149430154906</v>
+        <v>0.006041149430154887</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005921816258027229</v>
+        <v>0.005921816258027237</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006041149430154906</v>
+        <v>0.006041149430154887</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006041149430154906</v>
+        <v>0.006041149430154887</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006041149430154906</v>
+        <v>0.006041149430154887</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01296702402139773</v>
+        <v>0.01296702402139767</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01983650683477288</v>
+        <v>0.01983650683477283</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02123392121911803</v>
+        <v>0.02123392121911797</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01784090012469771</v>
+        <v>0.01784090012469772</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01307696150241383</v>
+        <v>0.01307696150241377</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01979643752223965</v>
+        <v>0.0197964375222395</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01981412932888951</v>
+        <v>0.01981412932888947</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01969479615674847</v>
+        <v>0.01969479615674838</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01981547498103782</v>
+        <v>0.01981547498103777</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01283983552501397</v>
+        <v>0.01283983552501392</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0269665033680159</v>
+        <v>0.02696650336801577</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01225706130292637</v>
+        <v>0.01225706130292634</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01504236124457711</v>
+        <v>0.01504236124457707</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01504094445095187</v>
+        <v>0.01504094445095183</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01813415144522965</v>
+        <v>0.01813415144522961</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01492160971197768</v>
+        <v>0.01492160971197766</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01502325162481029</v>
+        <v>0.01502325162481025</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01504094343144679</v>
+        <v>0.01504094343144676</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01492161025931912</v>
+        <v>0.0149216102593191</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01504094343144679</v>
+        <v>0.01504094343144676</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01153553864620365</v>
+        <v>0.01342795162183306</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01504094343144679</v>
+        <v>0.01504094343144676</v>
       </c>
     </row>
     <row r="8">
@@ -4319,34 +4319,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02323642499930584</v>
+        <v>0.02323642499930583</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003664570564393438</v>
+        <v>0.00366457056439344</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005921161149191081</v>
+        <v>0.005921161149191083</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005425908427801275</v>
+        <v>0.005425908427801276</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005425908427801275</v>
+        <v>0.005425908427801276</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009625032532799947</v>
+        <v>0.009625032532799943</v>
       </c>
       <c r="H8" t="n">
         <v>0.005917041739546148</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005425908427801275</v>
+        <v>0.005425908427801276</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01022452011362427</v>
+        <v>0.01022452011362425</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01474979350075398</v>
+        <v>0.01474979350075402</v>
       </c>
       <c r="L8" t="n">
         <v>0.004824379987865416</v>
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02294485690600418</v>
+        <v>0.02294485690600415</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003679550088389666</v>
+        <v>0.003679550088389667</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005944319602135281</v>
+        <v>0.005944319602135289</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00547348795459268</v>
+        <v>0.005473487954592677</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005473487954592679</v>
+        <v>0.005473487954592677</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009575947102335768</v>
+        <v>0.009575947102335759</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005942842802964721</v>
+        <v>0.005942842802964718</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00547348795459268</v>
+        <v>0.005473487954592677</v>
       </c>
       <c r="J9" t="n">
         <v>0.01021110932888176</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01460589696209733</v>
+        <v>0.01460589696209734</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004836004371265591</v>
+        <v>0.004836004371265586</v>
       </c>
     </row>
   </sheetData>
@@ -4475,31 +4475,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008833502214377795</v>
+        <v>0.008833502214377812</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01340488412654964</v>
+        <v>0.01340488412654961</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01555125037519058</v>
+        <v>0.01555125037519059</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01544068238039767</v>
+        <v>0.01544068238039765</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01544068238039767</v>
+        <v>0.01544068238039765</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01483202660468371</v>
+        <v>0.01483202660468359</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01730087504122373</v>
+        <v>0.01730087504122375</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01544068238039767</v>
+        <v>0.01544068238039765</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01841327637492717</v>
+        <v>0.01841327637492719</v>
       </c>
       <c r="K2" t="n">
         <v>0.01369328576275756</v>
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002929637956866331</v>
+        <v>0.002929637956866342</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002763037465401226</v>
+        <v>0.002763037465401214</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002929637956866331</v>
+        <v>0.002929637956866342</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002912322339560772</v>
+        <v>0.002912322339560784</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002912322339560768</v>
+        <v>0.002912322339560784</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002916038518521151</v>
+        <v>0.002916038518521165</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002929637956866331</v>
+        <v>0.002929637956866342</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002837630225288185</v>
+        <v>0.002837630225288197</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002929637956866331</v>
+        <v>0.002929637956866343</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002929637956866331</v>
+        <v>0.002929637956866342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002929637956866331</v>
+        <v>0.002929637956866342</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007941797884393833</v>
+        <v>0.004206773930442491</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004156556941733455</v>
+        <v>0.004156556941733487</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004198343656867866</v>
+        <v>0.004198343656867869</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003981712980355164</v>
+        <v>0.003981712980355172</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004124132778254893</v>
+        <v>0.00412413277825489</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007928198446048664</v>
+        <v>0.007928198446048661</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008112974609429948</v>
+        <v>0.008112974609429955</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004114766198864345</v>
+        <v>0.007849790152815693</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007933171863355161</v>
+        <v>0.004315851312380988</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004205815573628691</v>
+        <v>0.004205815573628694</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0041997951427887</v>
+        <v>0.004199795142788242</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005983760044628243</v>
+        <v>0.005983760044628248</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005985231435880719</v>
+        <v>0.005985231435880711</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005983651936477078</v>
+        <v>0.005983651936477083</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00590819695209829</v>
+        <v>0.0059081969520983</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00590819695209829</v>
+        <v>0.0059081969520983</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005970160606283052</v>
+        <v>0.005970160606283048</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005983760044628243</v>
+        <v>0.005983760044628248</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0058917523130501</v>
+        <v>0.005891752313050103</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005983760044628243</v>
+        <v>0.005983760044628248</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005983760044628243</v>
+        <v>0.005983760044628248</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005983760044628243</v>
+        <v>0.005983760044628248</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01288898076382283</v>
+        <v>0.01288898076382286</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01970557430605754</v>
+        <v>0.01970557430605756</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02109651277543056</v>
+        <v>0.02109651277543061</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01775107931940262</v>
+        <v>0.01775107931940266</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01302233161598251</v>
+        <v>0.01302233161598253</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01967331707499278</v>
+        <v>0.0196733170749928</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01968691651335348</v>
+        <v>0.0196869165133535</v>
       </c>
       <c r="I6" t="n">
         <v>0.01959490878175981</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01968825250239343</v>
+        <v>0.01968825250239345</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01276270561720566</v>
+        <v>0.01276270561720567</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02678792883781973</v>
+        <v>0.02678792883781977</v>
       </c>
     </row>
     <row r="7">
@@ -4675,16 +4675,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01179402822379609</v>
+        <v>0.0117940282237961</v>
       </c>
       <c r="C7" t="n">
         <v>0.01445150966247422</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0144500392571872</v>
+        <v>0.01445003925718719</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01742301000547364</v>
+        <v>0.01742301000547363</v>
       </c>
       <c r="F7" t="n">
         <v>0.01435802997669885</v>
@@ -4696,13 +4696,13 @@
         <v>0.01445003827122175</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01435803053964359</v>
+        <v>0.01435803053964361</v>
       </c>
       <c r="J7" t="n">
         <v>0.01445003827122175</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01284870078576851</v>
+        <v>0.01284870078576852</v>
       </c>
       <c r="L7" t="n">
         <v>0.01445003827122175</v>
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02254760088685317</v>
+        <v>0.02254760088685314</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003634212883086296</v>
+        <v>0.003634212883086292</v>
       </c>
       <c r="D8" t="n">
         <v>0.005893052839348194</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005254670181525626</v>
+        <v>0.005254670181525633</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005254670181525626</v>
+        <v>0.005254670181525633</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009457240640813215</v>
+        <v>0.009457240640813207</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005886570219566328</v>
+        <v>0.005886570219566332</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005254670181525626</v>
+        <v>0.005254670181525633</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009648985736305628</v>
+        <v>0.009648985736305633</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01462521013351358</v>
+        <v>0.01462521013351356</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004750703837320697</v>
+        <v>0.004750703837320691</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02226141399629059</v>
+        <v>0.02226141399629056</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003649732857622858</v>
+        <v>0.003649732857622854</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005907021547349736</v>
+        <v>0.005907021547349739</v>
       </c>
       <c r="E9" t="n">
         <v>0.005276638701728803</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005276638701728803</v>
+        <v>0.005276638701728801</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009402236841495064</v>
+        <v>0.009402236841495068</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005904569626487572</v>
+        <v>0.00590456962648758</v>
       </c>
       <c r="I9" t="n">
         <v>0.005276638701728803</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009634813883799895</v>
+        <v>0.009634813883799893</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01447579957737414</v>
+        <v>0.0144757995773741</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004761874627042942</v>
+        <v>0.004761874627042939</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1391148701834882</v>
+        <v>0.1391148701834879</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0538416872524413</v>
+        <v>0.05384168725244137</v>
       </c>
       <c r="D2" t="n">
-        <v>0.273025973099858</v>
+        <v>0.2730259730998582</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0538416872524413</v>
+        <v>0.05384168725244137</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0538416872524413</v>
+        <v>0.05384168725244137</v>
       </c>
       <c r="G2" t="n">
         <v>0.2104575628769693</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2406288622654864</v>
+        <v>0.240628862265487</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0538416872524413</v>
+        <v>0.05384168725244137</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2086654510090272</v>
+        <v>0.2086654510090269</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09563489094235425</v>
+        <v>0.09563489094235451</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2241597077176096</v>
+        <v>0.2241597077176095</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003585972859797614</v>
+        <v>0.003585972859797604</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003163828868890313</v>
+        <v>0.00316382886889029</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003585972859797614</v>
+        <v>0.003585972859797604</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003225686266417531</v>
+        <v>0.003225686266417517</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003225686266417531</v>
+        <v>0.003225686266417516</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00356128314058858</v>
+        <v>0.00356128314058856</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003585972859797614</v>
+        <v>0.003585972859797604</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00342160727726144</v>
+        <v>0.003421607277261437</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003585972859797614</v>
+        <v>0.003585972859797604</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003585972859797614</v>
+        <v>0.003585972859797604</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003585972859797614</v>
+        <v>0.003585972859797604</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01051081418104346</v>
+        <v>0.01051081418104345</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004956032068951351</v>
+        <v>0.004956032068951321</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005638396659484529</v>
+        <v>0.005638396659484406</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004811673799687016</v>
+        <v>0.004811673799686998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005195692425632425</v>
+        <v>0.005195692425632403</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005361519172670853</v>
+        <v>0.01048612446183441</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005439301866535454</v>
+        <v>0.01065320682249955</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0103464485985073</v>
+        <v>0.01034644859850727</v>
       </c>
       <c r="J4" t="n">
         <v>0.01055784778773907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005266159413164518</v>
+        <v>0.005266159413164497</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005641116911568056</v>
+        <v>0.005641116911568037</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007661843513957557</v>
+        <v>0.007661843513957546</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007497477931421395</v>
+        <v>0.007497477931421371</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007661705338640653</v>
+        <v>0.007661705338640645</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007492694051283804</v>
+        <v>0.007492694051283773</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007492694051283804</v>
+        <v>0.007492694051283773</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007637153794748522</v>
+        <v>0.00763715379474851</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007661843513957557</v>
+        <v>0.007661843513957546</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007497477931421395</v>
+        <v>0.007497477931421371</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007661843513957557</v>
+        <v>0.007661843513957546</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007661843513957557</v>
+        <v>0.007661843513957546</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007661843513957557</v>
+        <v>0.007661843513957546</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0156629215515872</v>
+        <v>0.01566292155158719</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02383019208818143</v>
+        <v>0.02383019208818147</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02572551973840933</v>
+        <v>0.02572551973840937</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02155107139117199</v>
+        <v>0.02155107139117203</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01575997235062026</v>
+        <v>0.01575997235062027</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02397263684604434</v>
+        <v>0.02397263684604432</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0239973265652526</v>
+        <v>0.02399732656525266</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02383296098271717</v>
+        <v>0.02383296098271719</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02399896451425807</v>
+        <v>0.0239989645142581</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01550810569960822</v>
+        <v>0.01550810569960823</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03270330951326951</v>
+        <v>0.03270330951326954</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01879896543215798</v>
+        <v>0.01879896543215796</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02312946429967275</v>
+        <v>0.02312946429967272</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02329383371807996</v>
+        <v>0.02329383371807995</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02831644134345025</v>
+        <v>0.02831644134345024</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0231294605455878</v>
+        <v>0.02312946054558778</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02326914016299987</v>
+        <v>0.02326914016299984</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0232938298822089</v>
+        <v>0.02329382988220889</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02312946429967275</v>
+        <v>0.02312946429967272</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0232938298822089</v>
+        <v>0.02329382988220889</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02068948938050701</v>
+        <v>0.02068948938050702</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0232938298822089</v>
+        <v>0.02329382988220889</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007322864621737295</v>
+        <v>0.00732286462173729</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004726023062654856</v>
+        <v>0.004726023062654862</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004299481204293894</v>
+        <v>0.004299481204293898</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004726023062654856</v>
+        <v>0.004726023062654862</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004726023062654856</v>
+        <v>0.004726023062654862</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005831367330374052</v>
+        <v>0.005831367330374059</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005691895508352724</v>
+        <v>0.005691895508352715</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004726023062654856</v>
+        <v>0.004726023062654862</v>
       </c>
       <c r="J8" t="n">
         <v>0.006081963288904435</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008411120575777007</v>
+        <v>0.008411120575777</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.002784198090420588</v>
+        <v>0.005987889051848053</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008991642024241849</v>
+        <v>0.008991642024241856</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005265952404507296</v>
+        <v>0.005265952404507299</v>
       </c>
       <c r="D9" t="n">
         <v>0.007760399728689408</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005265952404507296</v>
+        <v>0.005265952404507299</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005265952404507296</v>
+        <v>0.005265952404507299</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00836757260768884</v>
+        <v>0.008367572607688837</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008331764293233894</v>
+        <v>0.008331764293233885</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005265952404507296</v>
+        <v>0.005265952404507299</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008487887393052231</v>
+        <v>0.008487887393052233</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009434988285585833</v>
+        <v>0.009434988285585822</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004885104527802984</v>
+        <v>0.008451226165008683</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.104943068574218</v>
+        <v>0.1049430685742179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06766194198148107</v>
+        <v>0.06766194198148108</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2358628664672275</v>
+        <v>0.2358628664672263</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06766194198148107</v>
+        <v>0.06766194198148108</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06766194198148107</v>
+        <v>0.06766194198148108</v>
       </c>
       <c r="G2" t="n">
-        <v>0.18444270348268</v>
+        <v>0.1844427034826804</v>
       </c>
       <c r="H2" t="n">
         <v>0.2028644527964765</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06766194198148107</v>
+        <v>0.06766194198148108</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1409540307219802</v>
+        <v>0.1409540307219801</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08413267438081073</v>
+        <v>0.08413267438081082</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5978612668528823</v>
+        <v>0.2391211046126758</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003539714169772111</v>
+        <v>0.003539714169772108</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003178985245783681</v>
+        <v>0.003178985245783679</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003539714169772111</v>
+        <v>0.003539714169772108</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003234562344303577</v>
+        <v>0.003234562344303572</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003234562344303579</v>
+        <v>0.003234562344303572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003516993835112834</v>
+        <v>0.003516993835112833</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003539714169772111</v>
+        <v>0.003539714169772108</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003388137973469622</v>
+        <v>0.003388137973469606</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003539714169772111</v>
+        <v>0.003539714169772108</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003539714169772111</v>
+        <v>0.003539714169772108</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003539714169772111</v>
+        <v>0.003539714169772108</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00526829381291496</v>
+        <v>0.01005081775641375</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004912532531765324</v>
+        <v>0.004912532531765322</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005472242899997732</v>
+        <v>0.005472242899997957</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004774998643654478</v>
+        <v>0.004774998643654481</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005097255581573023</v>
+        <v>0.005097255581573016</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005245573478255688</v>
+        <v>0.01002809742175449</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0101685742649238</v>
+        <v>0.01016857426492378</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00511671761661246</v>
+        <v>0.009899241560111264</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005432950410411769</v>
+        <v>0.01008554451445164</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005165330721408149</v>
+        <v>0.005165330721408136</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00564935953461293</v>
+        <v>0.00564935953461294</v>
       </c>
     </row>
     <row r="5">
@@ -5387,28 +5387,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007263848247137995</v>
+        <v>0.007263848247137993</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007112272050835506</v>
+        <v>0.007112272050835501</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007263720039739074</v>
+        <v>0.00726372003973907</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007105748190588057</v>
+        <v>0.007105748190588059</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007105748190588057</v>
+        <v>0.007105748190588059</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007241127912478726</v>
+        <v>0.007241127912478722</v>
       </c>
       <c r="H5" t="n">
         <v>0.007263848247137995</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007112272050835506</v>
+        <v>0.007112272050835501</v>
       </c>
       <c r="J5" t="n">
         <v>0.007263848247137995</v>
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01463319913106688</v>
+        <v>0.01463319913106683</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02212465762316745</v>
+        <v>0.02212465762319039</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02386659762887017</v>
+        <v>0.02386659762887013</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02003356302341981</v>
+        <v>0.02003356302341979</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01472022522297505</v>
+        <v>0.01472022522297503</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02225809438280906</v>
+        <v>0.02225809438280903</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02228081471746824</v>
+        <v>0.02228081471746818</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02212923852116585</v>
+        <v>0.02212923852116583</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02228231769275346</v>
+        <v>0.02228231769275341</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01449114074529015</v>
+        <v>0.0144911407452901</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03026938868039055</v>
+        <v>0.03026938868039045</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01669726572208794</v>
+        <v>0.01669726572208793</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02044516606832151</v>
+        <v>0.02044516606832145</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02059674570514728</v>
+        <v>0.02059674570514727</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02494507863180438</v>
+        <v>0.02494507863180431</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02044516303271706</v>
+        <v>0.020445163032717</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02057402192996469</v>
+        <v>0.02057402192996468</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02059674226462399</v>
+        <v>0.02059674226462394</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02044516606832151</v>
+        <v>0.02044516606832145</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02059674226462399</v>
+        <v>0.02059674226462394</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01568660435176061</v>
+        <v>0.01568660435176058</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02059674226462399</v>
+        <v>0.02059674226462394</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007950143445173403</v>
+        <v>0.00795014344517341</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004249156280351905</v>
+        <v>0.004249156280351909</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004624197785104195</v>
+        <v>0.004624197785104221</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004249156280351905</v>
+        <v>0.004249156280351909</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004249156280351905</v>
+        <v>0.004249156280351909</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00602167224201014</v>
+        <v>0.006021672242010144</v>
       </c>
       <c r="H8" t="n">
-        <v>0.006124088506774297</v>
+        <v>0.006124088506774305</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004249156280351905</v>
+        <v>0.004249156280351909</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007284927984042937</v>
+        <v>0.007284927984042932</v>
       </c>
       <c r="K8" t="n">
         <v>0.008381683408955169</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.001989864227535388</v>
+        <v>0.005227016244638773</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009219898886012826</v>
+        <v>0.009219898886012831</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005069710299990758</v>
+        <v>0.005069710299990759</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007865415047581207</v>
+        <v>0.007865415047581226</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005069710299990758</v>
+        <v>0.005069710299990759</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005069710299990758</v>
+        <v>0.005069710299990759</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008420961889288892</v>
+        <v>0.008420961889288894</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008480117815001319</v>
+        <v>0.008480117815001326</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005069710299990758</v>
+        <v>0.005069710299990759</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008950140552259969</v>
+        <v>0.008950140552259978</v>
       </c>
       <c r="K9" t="n">
         <v>0.009395767968513711</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00811463054654899</v>
+        <v>0.008114630546548991</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08776368811570277</v>
+        <v>0.08776368811570233</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09756063451059137</v>
+        <v>0.09756063451059105</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1924140202161272</v>
+        <v>0.192414020216127</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09756063451059137</v>
+        <v>0.09756063451059105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09756063451059137</v>
+        <v>0.09756063451059105</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1574808400970187</v>
+        <v>0.1574808400970181</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1862555838382428</v>
+        <v>0.1862555838382432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09756063451059137</v>
+        <v>0.09756063451059105</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09753531858912888</v>
+        <v>0.09753531858912873</v>
       </c>
       <c r="K2" t="n">
-        <v>0.071550387044932</v>
+        <v>0.0715503870449315</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5217264020533658</v>
+        <v>0.5217264020533671</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003599396281762039</v>
+        <v>0.003599396281762028</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003307031656187686</v>
+        <v>0.00330703165618767</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003599396281762039</v>
+        <v>0.003599396281762028</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003359604503387275</v>
+        <v>0.003359604503387268</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003359604503387277</v>
+        <v>0.003359604503387264</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003579824434736069</v>
+        <v>0.003579824434736064</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003599396281762039</v>
+        <v>0.003599396281762028</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003468203790704691</v>
+        <v>0.003468203790704676</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003599396281762039</v>
+        <v>0.003599396281762028</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003599396281762039</v>
+        <v>0.003599396281762028</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003599396281762039</v>
+        <v>0.003599396281762028</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005339820376747727</v>
+        <v>0.005339820376747732</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005108324348298477</v>
+        <v>0.005108324348298458</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009975629492061376</v>
+        <v>0.009975629492061348</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00496895564304476</v>
+        <v>0.004968955643044739</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005215872255264575</v>
+        <v>0.005215872255264566</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00532024852972178</v>
+        <v>0.005320248529721776</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01005211065707605</v>
+        <v>0.01005211065707601</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009801098356132723</v>
+        <v>0.009801098356132704</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009961181850405454</v>
+        <v>0.005495131403949905</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005246173330510326</v>
+        <v>0.005246173330510314</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00548107702409615</v>
+        <v>0.005481077024096153</v>
       </c>
     </row>
     <row r="5">
@@ -5786,34 +5786,34 @@
         <v>0.007257507230589356</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007126314739532016</v>
+        <v>0.007126314739531989</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007257376852313786</v>
+        <v>0.007257376852313775</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007119303694337381</v>
+        <v>0.007119303694337371</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007119303694337381</v>
+        <v>0.007119303694337371</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007237935383563395</v>
+        <v>0.007237935383563378</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007257507230589356</v>
+        <v>0.00725750723058935</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007126314739532016</v>
+        <v>0.007126314739531989</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007257507230589356</v>
+        <v>0.00725750723058935</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007257507230589356</v>
+        <v>0.00725750723058935</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007257507230589356</v>
+        <v>0.00725750723058935</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01452718238871776</v>
+        <v>0.01452718238871773</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02191484442898829</v>
+        <v>0.02191484442898824</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0236112389311654</v>
+        <v>0.02361123893116535</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01985762932591807</v>
+        <v>0.01985762932591801</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01463038196363291</v>
+        <v>0.01463038196363285</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02203153279180148</v>
+        <v>0.02203153279180143</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02205110463882795</v>
+        <v>0.02205110463882788</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02191991214777009</v>
+        <v>0.02191991214777004</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02205258330488886</v>
+        <v>0.02205258330488883</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01438742167016048</v>
+        <v>0.01438742167016044</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02991047056898464</v>
+        <v>0.02991047056898453</v>
       </c>
     </row>
     <row r="7">
@@ -5866,34 +5866,34 @@
         <v>0.01576276292081625</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0192480879215691</v>
+        <v>0.01924808792156908</v>
       </c>
       <c r="D7" t="n">
         <v>0.01937928291366226</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02342147124305046</v>
+        <v>0.02342147124305042</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01924808516765411</v>
+        <v>0.01924808516765407</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01935970856560045</v>
+        <v>0.01935970856560049</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01937928041262643</v>
+        <v>0.01937928041262644</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0192480879215691</v>
+        <v>0.01924808792156908</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01937928041262643</v>
+        <v>0.01937928041262644</v>
       </c>
       <c r="K7" t="n">
         <v>0.01728385702663745</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01937928041262643</v>
+        <v>0.01937928041262644</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008136190966557388</v>
+        <v>0.008136190966557396</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003271926246964263</v>
+        <v>0.003271926246964272</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005376934177072458</v>
+        <v>0.00537693417707246</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003271926246964263</v>
+        <v>0.003271926246964272</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003271926246964263</v>
+        <v>0.003271926246964272</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006420527866448042</v>
+        <v>0.006420527866448027</v>
       </c>
       <c r="H8" t="n">
-        <v>0.006136701345871656</v>
+        <v>0.006136701345871664</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003271926246964263</v>
+        <v>0.003271926246964272</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008112966522508447</v>
+        <v>0.008112966522508452</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008444106010709355</v>
+        <v>0.008444106010709374</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0007414050132747498</v>
+        <v>-0.0007414050132747006</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009187816330979608</v>
+        <v>0.009187816330979629</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004580021250846752</v>
+        <v>0.004580021250846747</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00806411634667639</v>
+        <v>0.008064116346676399</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004580021250846752</v>
+        <v>0.004580021250846747</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004580021250846752</v>
+        <v>0.004580021250846747</v>
       </c>
       <c r="G9" t="n">
         <v>0.008481600938192</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008377211110522901</v>
+        <v>0.008377211110522906</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004580021250846752</v>
+        <v>0.004580021250846747</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009179149806945432</v>
+        <v>0.009179149806945437</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009313320602993159</v>
+        <v>0.009313320602993174</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005580308599473426</v>
+        <v>0.00558030859947344</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0327613315931145</v>
+        <v>0.03276133159311452</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02790546019177459</v>
+        <v>0.02790546019177457</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07935207103928553</v>
+        <v>0.07935207103928546</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02790546019177459</v>
+        <v>0.02790546019177457</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02790546019177459</v>
+        <v>0.02790546019177457</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06970936614136568</v>
+        <v>0.06970936614136561</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08308123159615231</v>
+        <v>0.08308123159615222</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02790546019177459</v>
+        <v>0.02790546019177457</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09412969759987104</v>
+        <v>0.09412969759987087</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04902086187525927</v>
+        <v>0.04902086187525919</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09995635124337331</v>
+        <v>0.6271645655508225</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003178701277571726</v>
+        <v>0.003178701277571714</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002848588281451594</v>
+        <v>0.002848588281451593</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003178701277571726</v>
+        <v>0.003178701277571714</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002902308631379997</v>
+        <v>0.002902308631379996</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002902308631379997</v>
+        <v>0.002902308631379995</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003157916680599015</v>
+        <v>0.003157916680599008</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003178701277571726</v>
+        <v>0.003178701277571714</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003039193972430723</v>
+        <v>0.00303919397243072</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003178701277571726</v>
+        <v>0.003178701277571714</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003178701277571726</v>
+        <v>0.003178701277571714</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003178701277571726</v>
+        <v>0.003178701277571714</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004637653367962985</v>
+        <v>0.00463765336796298</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004382652059430107</v>
+        <v>0.004382652059430114</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004694595295326799</v>
+        <v>0.009091870125213107</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00425506810025495</v>
+        <v>0.004255068100254933</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004481507899805899</v>
+        <v>0.004481507899805895</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009029528469560963</v>
+        <v>0.004616868770990269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009168636410090171</v>
+        <v>0.009168636410090142</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008910805761392682</v>
+        <v>0.004498146062821992</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009079934774326925</v>
+        <v>0.009079934774326904</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004614064616626072</v>
+        <v>0.00461406461662607</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004887604005420123</v>
+        <v>0.004887604005420106</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006660103686643914</v>
+        <v>0.006660103686643911</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006520596381502917</v>
+        <v>0.00652059638150292</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006659973662169469</v>
+        <v>0.006659973662169466</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006514601018772537</v>
+        <v>0.00651460101877254</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006514601018772537</v>
+        <v>0.00651460101877254</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006639319089671208</v>
+        <v>0.0066393190896712</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006660103686643914</v>
+        <v>0.006660103686643911</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006520596381502917</v>
+        <v>0.00652059638150292</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006660103686643914</v>
+        <v>0.006660103686643911</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006660103686643914</v>
+        <v>0.006660103686643911</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006660103686643914</v>
+        <v>0.006660103686643911</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01414525098244917</v>
+        <v>0.01414525098244918</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02150824407310464</v>
+        <v>0.02150824407308385</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02320839337117284</v>
+        <v>0.02320839337117285</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01945566315214509</v>
+        <v>0.01945566315214512</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01424019234682473</v>
+        <v>0.01424019234682474</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02163106636707201</v>
+        <v>0.02163106636707204</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02165185096404451</v>
+        <v>0.02165185096404455</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02151234365890374</v>
+        <v>0.02151234365890376</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02165332622598233</v>
+        <v>0.02165332622598235</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01400581203390164</v>
+        <v>0.01400581203390165</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02949312233646109</v>
+        <v>0.0294931223364611</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01498851350541785</v>
+        <v>0.01498851350541782</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01834948789947871</v>
+        <v>0.01834948789947868</v>
       </c>
       <c r="D7" t="n">
         <v>0.01848899638218161</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02238896790243692</v>
+        <v>0.02238896790243691</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0183494857233105</v>
+        <v>0.01834948572331048</v>
       </c>
       <c r="G7" t="n">
         <v>0.01846821060764698</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01848899520461969</v>
+        <v>0.01848899520461968</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01834948789947871</v>
+        <v>0.01834948789947868</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01848899520461969</v>
+        <v>0.01848899520461968</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01408126360635279</v>
+        <v>0.01646080285592762</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01848899520461969</v>
+        <v>0.01848899520461968</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00928012908937224</v>
+        <v>0.009280129089372239</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004893688963477473</v>
+        <v>0.004893688963477475</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00807105661076879</v>
+        <v>0.008071056610768785</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004893688963477473</v>
+        <v>0.004893688963477475</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004893688963477473</v>
+        <v>0.004893688963477475</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008389020455942113</v>
+        <v>0.008389020455942106</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008200911512743663</v>
+        <v>0.008200911512743658</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004893688963477473</v>
+        <v>0.004893688963477475</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007996036209368857</v>
+        <v>0.007996036209368852</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008868038087464039</v>
+        <v>0.008868038087464033</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.002811561197319163</v>
+        <v>0.007947591564693941</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009462555040397341</v>
+        <v>0.009462555040397332</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005073561365780419</v>
+        <v>0.005073561365780416</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008970155115494446</v>
+        <v>0.008970155115494441</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005073561365780419</v>
+        <v>0.005073561365780418</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005073561365780419</v>
+        <v>0.005073561365780418</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009093214246023159</v>
+        <v>0.009093214246023152</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009024544877753168</v>
+        <v>0.009024544877753161</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005073561365780419</v>
+        <v>0.005073561365780418</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008940264805696528</v>
+        <v>0.00894026480569652</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009294765713085807</v>
+        <v>0.009294765713085795</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008921251385104058</v>
+        <v>0.004547287843635997</v>
       </c>
     </row>
   </sheetData>
@@ -6458,31 +6458,31 @@
         <v>0.02175975174209291</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02881846791083753</v>
+        <v>0.0288184679108375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02508978662580442</v>
+        <v>0.02508978662580441</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02881846791083753</v>
+        <v>0.0288184679108375</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02881846791083753</v>
+        <v>0.0288184679108375</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0326478739429651</v>
+        <v>0.03264787394296472</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02338128531681547</v>
+        <v>0.02338128531681549</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02881846791083753</v>
+        <v>0.0288184679108375</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04804716679327262</v>
+        <v>0.04804716679327257</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0346904758654383</v>
+        <v>0.03469047586543835</v>
       </c>
       <c r="L2" t="n">
         <v>0.03450736559124172</v>
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003023121666215104</v>
+        <v>0.003023121666215111</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002769534828303371</v>
+        <v>0.002769534828303366</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003023121666215104</v>
+        <v>0.003023121666215111</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002814031025775842</v>
+        <v>0.00281403102577584</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002814031025775842</v>
+        <v>0.002814031025775844</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003004675392598079</v>
+        <v>0.00300467539259807</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003023121666215104</v>
+        <v>0.003023121666215111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002898736496983739</v>
+        <v>0.002898736496983734</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003023121666215104</v>
+        <v>0.003023121666215111</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003023121666215104</v>
+        <v>0.003023121666215111</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003023121666215104</v>
+        <v>0.003023121666215111</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004350169596388078</v>
+        <v>0.008159205874820179</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004177804443473763</v>
+        <v>0.004177804443473755</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00433723593919894</v>
+        <v>0.004337223349218465</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004059032565156761</v>
+        <v>0.004059032565156756</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004219734434578772</v>
+        <v>0.004219734434578771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004331723322771043</v>
+        <v>0.004331723322771051</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008233008210039599</v>
+        <v>0.004339230064632065</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004225784427156713</v>
+        <v>0.004225784427156704</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004465853465612329</v>
+        <v>0.008166487083746555</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004358017916205672</v>
+        <v>0.004358017916205682</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004569693519145108</v>
+        <v>0.004569693519145106</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006094315009200283</v>
+        <v>0.006094315009200282</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005969929839968916</v>
+        <v>0.005969929839968909</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00609419274947823</v>
+        <v>0.006094192749478223</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005964922023470447</v>
+        <v>0.005964922023470441</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005964922023470447</v>
+        <v>0.005964922023470441</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00607586873558325</v>
+        <v>0.006075868735583255</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006094315009200283</v>
+        <v>0.006094315009200282</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005969929839968916</v>
+        <v>0.005969929839968909</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006094315009200283</v>
+        <v>0.006094315009200282</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006094315009200283</v>
+        <v>0.006094315009200282</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006094315009200283</v>
+        <v>0.006094315009200282</v>
       </c>
     </row>
     <row r="6">
@@ -6615,13 +6615,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01287086162323129</v>
+        <v>0.01287086162323128</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01946142787871205</v>
+        <v>0.01946142787871204</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02098221092601409</v>
+        <v>0.02098221092601404</v>
       </c>
       <c r="E6" t="n">
         <v>0.01762436726679435</v>
@@ -6630,22 +6630,22 @@
         <v>0.01295652082659204</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01957068721552069</v>
+        <v>0.01957068721552067</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01958913348913693</v>
+        <v>0.0195891334891369</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01946474831990637</v>
+        <v>0.01946474831990636</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01959045382222865</v>
+        <v>0.01959045382222862</v>
       </c>
       <c r="K6" t="n">
         <v>0.01274606627414211</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02660693022598957</v>
+        <v>0.02660693022598952</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01272084175929256</v>
+        <v>0.01272084175929255</v>
       </c>
       <c r="C7" t="n">
         <v>0.01547911827656925</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01560350473270653</v>
+        <v>0.0156035047327065</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01880564911250854</v>
+        <v>0.0188056491125085</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01547911764350884</v>
+        <v>0.01547911764350882</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01558505717218361</v>
+        <v>0.01558505717218359</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01560350344580065</v>
+        <v>0.01560350344580061</v>
       </c>
       <c r="I7" t="n">
         <v>0.01547911827656925</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01560350344580065</v>
+        <v>0.01560350344580061</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01386551529613094</v>
+        <v>0.01386551529613092</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01560350344580065</v>
+        <v>0.01560350344580061</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009343795728268057</v>
+        <v>0.00934379572826805</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00468347082525269</v>
+        <v>0.004683470825252689</v>
       </c>
       <c r="D8" t="n">
         <v>0.009251636784808949</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00468347082525269</v>
+        <v>0.004683470825252689</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00468347082525269</v>
+        <v>0.004683470825252689</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009056436620129513</v>
+        <v>0.00905643662012951</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009356181777878047</v>
+        <v>0.009356181777878048</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00468347082525269</v>
+        <v>0.004683470825252689</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008712995601732798</v>
+        <v>0.008712995601732797</v>
       </c>
       <c r="K8" t="n">
         <v>0.008987636610891395</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009536123712041983</v>
+        <v>0.009536123712041987</v>
       </c>
     </row>
     <row r="9">
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009392829758784386</v>
+        <v>0.009392829758784379</v>
       </c>
       <c r="C9" t="n">
         <v>0.00491398342091572</v>
@@ -6750,22 +6750,22 @@
         <v>0.00491398342091572</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009273310504310881</v>
+        <v>0.009273310504310872</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009398194296842599</v>
+        <v>0.009398194296842598</v>
       </c>
       <c r="I9" t="n">
         <v>0.00491398342091572</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009136285286219618</v>
+        <v>0.009136285286219615</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009247806112359855</v>
+        <v>0.009247806112359858</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009286091152965916</v>
+        <v>0.009471287334346741</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02887701635229302</v>
+        <v>0.028877016352293</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03298354752315544</v>
+        <v>0.0329835475231556</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02206612185215429</v>
+        <v>0.02206612185215431</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03298354752315544</v>
+        <v>0.0329835475231556</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03298354752315544</v>
+        <v>0.0329835475231556</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03138785712446826</v>
+        <v>0.03138785712446859</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02290286623630387</v>
+        <v>0.02290286623630395</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03298354752315544</v>
+        <v>0.0329835475231556</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04243467535427996</v>
+        <v>0.04243467535427994</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03102770929193001</v>
+        <v>0.03102770929193007</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03258869011403049</v>
+        <v>0.02129708797322414</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003023365350841577</v>
+        <v>0.003023365350841571</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002794379493100897</v>
+        <v>0.002794379493100903</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003023365350841577</v>
+        <v>0.003023365350841572</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002837442766727393</v>
+        <v>0.002837442766727402</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002837442766727393</v>
+        <v>0.002837442766727399</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003006138379415567</v>
+        <v>0.003006138379415602</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003023365350841577</v>
+        <v>0.003023365350841571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002907047065125838</v>
+        <v>0.002907047065125854</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003023365350841577</v>
+        <v>0.003023365350841571</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003023365350841577</v>
+        <v>0.003023365350841571</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003023365350841577</v>
+        <v>0.003023365350841571</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004367945307934238</v>
+        <v>0.00436794530793416</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004212955830051962</v>
+        <v>0.004212955830051986</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008101645509858674</v>
+        <v>0.004339076602679372</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004093408962331745</v>
+        <v>0.004093408962331635</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004246300659858487</v>
+        <v>0.004246300659858501</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004350718336508184</v>
+        <v>0.008091295792636323</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008165132582706607</v>
+        <v>0.008165132582706626</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004251627022218461</v>
+        <v>0.004251627022218497</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004478872332341007</v>
+        <v>0.008100587531608144</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004369891743021826</v>
+        <v>0.004369891743021787</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004361185220375671</v>
+        <v>0.004361185220375674</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006080838358402892</v>
+        <v>0.006080838358402954</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00596452007268722</v>
+        <v>0.005964520072687235</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006080715094619025</v>
+        <v>0.006080715094619043</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005959467004290392</v>
+        <v>0.005959467004290406</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005959467004290392</v>
+        <v>0.005959467004290406</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006063611386977003</v>
+        <v>0.006063611386976984</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006080838358402892</v>
+        <v>0.006080838358402954</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00596452007268722</v>
+        <v>0.005964520072687235</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006080838358402892</v>
+        <v>0.006080838358402954</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006080838358402892</v>
+        <v>0.006080838358402954</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006080838358402892</v>
+        <v>0.006080838358402954</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01283922925504524</v>
+        <v>0.01283922925504522</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01941254156251824</v>
+        <v>0.0194125415625342</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02092006317633736</v>
+        <v>0.02092006317633737</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0175823973324991</v>
+        <v>0.01758239733249911</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0129321277819771</v>
+        <v>0.01293212778197711</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01951499960871464</v>
+        <v>0.01951499960871461</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01953222658013942</v>
+        <v>0.01953222658013944</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01941590829442485</v>
+        <v>0.01941590829442489</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01953354194613483</v>
+        <v>0.01953354194613476</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01271490339352049</v>
+        <v>0.01271490339352046</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0265236219457638</v>
+        <v>0.02652362194576379</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01230375487164657</v>
+        <v>0.01230375487164658</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01495249813803363</v>
+        <v>0.01495249813803366</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01506881760707009</v>
+        <v>0.01506881760707011</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01814332085972175</v>
+        <v>0.01814332085972177</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01495249753774575</v>
+        <v>0.01495249753774577</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01505158945232337</v>
+        <v>0.01505158945232338</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01506881642374938</v>
+        <v>0.01506881642374939</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01495249813803363</v>
+        <v>0.01495249813803366</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01506881642374938</v>
+        <v>0.01506881642374939</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01346672939892636</v>
+        <v>0.0134017306565816</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01506881642374938</v>
+        <v>0.01506881642374939</v>
       </c>
     </row>
     <row r="8">
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00902368485925918</v>
+        <v>0.00902368485925917</v>
       </c>
       <c r="C8" t="n">
         <v>0.004358639537517712</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009202541985922765</v>
+        <v>0.009202541985922748</v>
       </c>
       <c r="E8" t="n">
         <v>0.004358639537517712</v>
@@ -7106,22 +7106,22 @@
         <v>0.004358639537517712</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008965224474216412</v>
+        <v>0.008965224474216375</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009234010039784499</v>
+        <v>0.009234010039784498</v>
       </c>
       <c r="I8" t="n">
         <v>0.004358639537517712</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008727706261879162</v>
+        <v>0.008727706261879156</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00894081214695509</v>
+        <v>0.008940812146955088</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008996834090697783</v>
+        <v>0.008996834090697774</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009184111246338266</v>
+        <v>0.009184111246338269</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004654688787740711</v>
+        <v>0.004654688787740715</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009256968243133703</v>
+        <v>0.009256968243133677</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004654688787740711</v>
+        <v>0.004654688787740715</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004654688787740711</v>
+        <v>0.004654688787740715</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009158557930957338</v>
+        <v>0.009158557930957328</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009270082505341693</v>
+        <v>0.009270082505341703</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004654688787740711</v>
+        <v>0.004654688787740715</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009063880054194947</v>
+        <v>0.009063880054194954</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009150390711969283</v>
+        <v>0.009150390711969254</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009173598388347647</v>
+        <v>0.009288452294689329</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08673351714236066</v>
+        <v>0.08673351714236073</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04493427183697214</v>
+        <v>0.04493427183697208</v>
       </c>
       <c r="D2" t="n">
-        <v>0.24980716578453</v>
+        <v>0.2498071657845301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04493427183697214</v>
+        <v>0.04493427183697208</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04493427183697214</v>
+        <v>0.04493427183697208</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1744451155552436</v>
+        <v>0.1744451155552434</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2167937925810002</v>
+        <v>0.2167937925810005</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04493427183697214</v>
+        <v>0.04493427183697208</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1312766443698883</v>
+        <v>0.1312766443698885</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07849757828280216</v>
+        <v>0.07849757828280238</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5887969925996276</v>
+        <v>0.5887969925996278</v>
       </c>
     </row>
     <row r="3">
@@ -7290,25 +7290,25 @@
         <v>0.003469570395138781</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003063145670503256</v>
+        <v>0.003063145670503266</v>
       </c>
       <c r="D3" t="n">
         <v>0.003469570395138781</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003123320544463994</v>
+        <v>0.003123320544464001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003123320544463993</v>
+        <v>0.003123320544464001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003445643437026873</v>
+        <v>0.003445643437026879</v>
       </c>
       <c r="H3" t="n">
         <v>0.003469570395138781</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003310050060660286</v>
+        <v>0.003310050060660299</v>
       </c>
       <c r="J3" t="n">
         <v>0.003469570395138781</v>
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00516413704985766</v>
+        <v>0.005164137049857663</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004770614399906127</v>
+        <v>0.004770614399906134</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005438178960343183</v>
+        <v>0.005438178960343188</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004633093309874268</v>
+        <v>0.004633093309874257</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004981631955836569</v>
+        <v>0.004981631955836566</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01007079729882212</v>
+        <v>0.01007079729882213</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0102588231778008</v>
+        <v>0.01025882317780081</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005004616715379164</v>
+        <v>0.009935203922455541</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01015774817893869</v>
+        <v>0.0101577481789387</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005059746069090916</v>
+        <v>0.005059746069090917</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005395421609713239</v>
+        <v>0.005395421609713245</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007378049193504471</v>
+        <v>0.007378049193504472</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007218528859025972</v>
+        <v>0.007218528859025991</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007377913960162882</v>
+        <v>0.007377913960162888</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007212910401732183</v>
+        <v>0.007212910401732199</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007212910401732183</v>
+        <v>0.007212910401732199</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007354122235392565</v>
+        <v>0.007354122235392569</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007378049193504471</v>
+        <v>0.007378049193504472</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007218528859025972</v>
+        <v>0.007218528859025991</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007378049193504471</v>
+        <v>0.007378049193504472</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007378049193504471</v>
+        <v>0.007378049193504472</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007378049193504471</v>
+        <v>0.007378049193504472</v>
       </c>
     </row>
     <row r="6">
@@ -7410,34 +7410,34 @@
         <v>0.01523682526626956</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02317834474800454</v>
+        <v>0.02317834474803046</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02502203381098244</v>
+        <v>0.02502203381098245</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02096214891376338</v>
+        <v>0.02096214891376341</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01533093898583042</v>
+        <v>0.01533093898583045</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02331755375008846</v>
+        <v>0.02331755375008848</v>
       </c>
       <c r="H6" t="n">
         <v>0.02334148070819991</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02318196037372188</v>
+        <v>0.02318196037372192</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02334307350491076</v>
+        <v>0.02334307350491079</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01508627713053112</v>
+        <v>0.01508627713053113</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03180747101726842</v>
+        <v>0.03180747101726845</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01788045444338765</v>
+        <v>0.01788045444338766</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02197962029006285</v>
+        <v>0.02197962029006289</v>
       </c>
       <c r="D7" t="n">
-        <v>0.022139143624846</v>
+        <v>0.02213914362484603</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02689405200793729</v>
+        <v>0.02689405200793732</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02197961665113829</v>
+        <v>0.02197961665113833</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02211521366642938</v>
+        <v>0.0221152136664294</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02213914062454131</v>
+        <v>0.02213914062454134</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02197962029006285</v>
+        <v>0.02197962029006289</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02213914062454131</v>
+        <v>0.02213914062454134</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01957153274584441</v>
+        <v>0.01967164238794614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02213914062454131</v>
+        <v>0.02213914062454134</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008385640056386293</v>
+        <v>0.008385640056386296</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004787158701966241</v>
+        <v>0.004787158701966239</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00440471861158793</v>
+        <v>0.00440471861158794</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004787158701966241</v>
+        <v>0.004787158701966239</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004787158701966241</v>
+        <v>0.004787158701966239</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006366373878318766</v>
+        <v>0.006366373878318764</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005648108116405621</v>
+        <v>0.005648108116405623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004787158701966241</v>
+        <v>0.004787158701966239</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007585889599934996</v>
+        <v>0.007585889599934997</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008597647218543999</v>
+        <v>0.008597647218544001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007242344078327293</v>
+        <v>-0.0011773487290259</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00932513708582104</v>
+        <v>0.009325137085821045</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00520340252913525</v>
+        <v>0.005203402529135251</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007703888309297881</v>
+        <v>0.007703888309297884</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00520340252913525</v>
+        <v>0.005203402529135251</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00520340252913525</v>
+        <v>0.005203402529135251</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008488101018339673</v>
+        <v>0.008488101018339678</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008214445047337295</v>
+        <v>0.008214445047337289</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00520340252913525</v>
+        <v>0.005203402529135251</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009000421417716613</v>
+        <v>0.009000421417716615</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00941157387337388</v>
+        <v>0.009411573873373881</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008861727225021016</v>
+        <v>0.00543885083500222</v>
       </c>
     </row>
   </sheetData>
@@ -7646,34 +7646,34 @@
         <v>0.0173821324475647</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02597240465654512</v>
+        <v>0.02597240465654515</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1792344821579918</v>
+        <v>0.179234482157992</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02597240465654512</v>
+        <v>0.02597240465654515</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02597240465654512</v>
+        <v>0.02597240465654515</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0902997888284998</v>
+        <v>0.09029978882849982</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04129318457170685</v>
+        <v>0.04129318457170681</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02597240465654512</v>
+        <v>0.02597240465654515</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06094671935578518</v>
+        <v>0.06094671935578515</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03063789967721395</v>
+        <v>0.03063789967721392</v>
       </c>
       <c r="L2" t="n">
-        <v>3.155388334040372</v>
+        <v>0.040184214210318</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003231725787291971</v>
+        <v>0.003231725787291963</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002913853845559097</v>
+        <v>0.002913853845559084</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003231725787291971</v>
+        <v>0.003231725787291963</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002963873796889763</v>
+        <v>0.002963873796889757</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002963873796889763</v>
+        <v>0.002963873796889756</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003210645873803338</v>
+        <v>0.003210645873803328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003231725787291966</v>
+        <v>0.003231725787291963</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003090513624850908</v>
+        <v>0.003090513624850904</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003231725787291971</v>
+        <v>0.003231725787291963</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003231725787291971</v>
+        <v>0.003231725787291963</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003231725787291971</v>
+        <v>0.003231725787291963</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004663002843558242</v>
+        <v>0.009831812323990826</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00438112157099211</v>
+        <v>0.004381121570992107</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004919519214363554</v>
+        <v>0.004919519214363205</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00425849719173957</v>
+        <v>0.004258497191739548</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004505958387913149</v>
+        <v>0.004505958387913143</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009810732410502225</v>
+        <v>0.004641922930069595</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009886472895901645</v>
+        <v>0.00988647289590165</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009690600161549785</v>
+        <v>0.009690600161549759</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009819739556503827</v>
+        <v>0.004793058743410691</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004589076103694145</v>
+        <v>0.004589076103694159</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005848444470608971</v>
+        <v>0.005848444470608964</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006556755070343846</v>
+        <v>0.006556755070343841</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006415542907902773</v>
+        <v>0.00641554290790278</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006556632788674494</v>
+        <v>0.006556632788674472</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0064094392890958</v>
+        <v>0.006409439289095808</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0064094392890958</v>
+        <v>0.006409439289095808</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006535675156855215</v>
+        <v>0.006535675156855216</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006556755070343846</v>
+        <v>0.006556755070343841</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006415542907902773</v>
+        <v>0.00641554290790278</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006556755070343846</v>
+        <v>0.006556755070343841</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006556755070343846</v>
+        <v>0.006556755070343841</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006556755070343846</v>
+        <v>0.006556755070343841</v>
       </c>
     </row>
     <row r="6">
@@ -7803,28 +7803,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01366344583948111</v>
+        <v>0.01366344583948113</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02066423463788571</v>
+        <v>0.02066423463790549</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02229155977147348</v>
+        <v>0.02229155977147342</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01871021864513011</v>
+        <v>0.0187102186451301</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0137451917238659</v>
+        <v>0.01374519172386587</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02078865107800063</v>
+        <v>0.02078865107800061</v>
       </c>
       <c r="H6" t="n">
         <v>0.02080973099148889</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02066851882904821</v>
+        <v>0.02066851882904819</v>
       </c>
       <c r="J6" t="n">
         <v>0.02081113544123126</v>
@@ -7833,7 +7833,7 @@
         <v>0.01353069992388202</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0282746233954117</v>
+        <v>0.02827462339541171</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01427880256689411</v>
+        <v>0.01427880256689409</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01741821702332887</v>
+        <v>0.01741821702332885</v>
       </c>
       <c r="D7" t="n">
         <v>0.01755942862756329</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02120398439021828</v>
+        <v>0.02120398439021827</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01741821247439631</v>
+        <v>0.01741821247439629</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0175383492722813</v>
+        <v>0.01753834927228129</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01755942918576994</v>
+        <v>0.0175594291857699</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01741821702332887</v>
+        <v>0.01741821702332885</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01755942918576994</v>
+        <v>0.0175594291857699</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01565862100399888</v>
+        <v>0.01342853482750031</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01755942918576994</v>
+        <v>0.0175594291857699</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009715111909510691</v>
+        <v>0.009715111909510693</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004948592334444266</v>
+        <v>0.004948592334444261</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005308837545693664</v>
+        <v>0.005308837545693668</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004948592334444266</v>
+        <v>0.004948592334444261</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004948592334444266</v>
+        <v>0.004948592334444261</v>
       </c>
       <c r="G8" t="n">
         <v>0.007826501931213255</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009187010805302709</v>
+        <v>0.009187010805302705</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004948592334444266</v>
+        <v>0.004948592334444261</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00871392055777242</v>
+        <v>0.008713920557772417</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009363064895512656</v>
+        <v>0.009363064895512661</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009224829667109923</v>
+        <v>-0.05831798092190792</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009691538824272485</v>
+        <v>0.00969153882427248</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005122621060059621</v>
+        <v>0.005122621060059619</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007897014520903457</v>
+        <v>0.00789701452090345</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005122621060059621</v>
+        <v>0.005122621060059619</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005122621060059621</v>
+        <v>0.005122621060059619</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008913273665309567</v>
+        <v>0.008913273665309574</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00947715874713344</v>
+        <v>0.009477158747133436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005122621060059621</v>
+        <v>0.005122621060059619</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009284232256510511</v>
+        <v>0.009284232256510505</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009548183495905192</v>
+        <v>0.009548183495905195</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009492392709911705</v>
+        <v>-0.01796619340823453</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen acidification results.xlsx
+++ b/Results/Hydrogen/hydrogen acidification results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1857340927966087</v>
+        <v>0.1857340927966097</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09701696200747935</v>
+        <v>0.09701696200747925</v>
       </c>
       <c r="D2" t="n">
-        <v>0.312129678209386</v>
+        <v>0.3121296782093867</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09701696200747935</v>
+        <v>0.09701696200747925</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09701696200747935</v>
+        <v>0.09701696200747925</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2480335106839734</v>
+        <v>0.248033510683973</v>
       </c>
       <c r="H2" t="n">
-        <v>0.449880209955913</v>
+        <v>0.4498802099559128</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09701696200747935</v>
+        <v>0.09701696200747925</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2327693227070053</v>
+        <v>0.2327693227070064</v>
       </c>
       <c r="K2" t="n">
         <v>0.1267865409028706</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2394934131306479</v>
+        <v>0.9928481639916348</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003914306244165961</v>
+        <v>0.003914306244165959</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00357816245313333</v>
+        <v>0.003578162453133327</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003914306244165961</v>
+        <v>0.003914306244165959</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003645440212022925</v>
+        <v>0.003645440212022916</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003645440212022919</v>
+        <v>0.003645440212022916</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003893578033175781</v>
+        <v>0.003893578033175798</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003914306244165961</v>
+        <v>0.003914306244165959</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003776331094216981</v>
+        <v>0.003776331094216983</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003914306244165961</v>
+        <v>0.003914306244165959</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003914306244165961</v>
+        <v>0.003914306244165959</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003914306244165961</v>
+        <v>0.003914306244165959</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006002747738987907</v>
+        <v>0.006002747738987898</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005621131586167589</v>
+        <v>0.005621131586167556</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006253680033066898</v>
+        <v>0.006253692663250144</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005456617870408663</v>
+        <v>0.005456617870408661</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005848174496503688</v>
+        <v>0.005848174496503681</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01171762250569444</v>
+        <v>0.01171762250569443</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01193158230737015</v>
+        <v>0.01193158230737016</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005864772589038929</v>
+        <v>0.01160037556673561</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006215214556559606</v>
+        <v>0.01177008422520834</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005882980368756916</v>
+        <v>0.005882980368756914</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006272075705435198</v>
+        <v>0.006272075705435197</v>
       </c>
     </row>
     <row r="5">
@@ -638,25 +638,25 @@
         <v>0.008481529061823232</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008343553911874274</v>
+        <v>0.008343553911874264</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008481373679581931</v>
+        <v>0.008481373679581921</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008338972503004681</v>
+        <v>0.008338972503004666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008338972503004681</v>
+        <v>0.008338972503004666</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008460800850833087</v>
+        <v>0.008460800850833079</v>
       </c>
       <c r="H5" t="n">
         <v>0.008481529061823232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008343553911874274</v>
+        <v>0.008343553911874264</v>
       </c>
       <c r="J5" t="n">
         <v>0.008481529061823232</v>
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01728627851729874</v>
+        <v>0.01728627851729872</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02638653445321616</v>
+        <v>0.02638653445324726</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02844298523747891</v>
+        <v>0.02844298523747883</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02385952968094735</v>
+        <v>0.02385952968094731</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01743857599249401</v>
+        <v>0.01743857599249397</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02650615702620016</v>
+        <v>0.02650615702620014</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02652688523719001</v>
+        <v>0.02652688523718993</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0263889100872414</v>
+        <v>0.02638891008724136</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02652870128071151</v>
+        <v>0.02652870128071146</v>
       </c>
       <c r="K6" t="n">
         <v>0.01711462950339104</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03617947164262653</v>
+        <v>0.03617947164262652</v>
       </c>
     </row>
     <row r="7">
@@ -718,34 +718,34 @@
         <v>0.02264740886382465</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02801408680434025</v>
+        <v>0.02801408680434021</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02815206362428436</v>
+        <v>0.02815206362428433</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03436633290144033</v>
+        <v>0.03436633290144032</v>
       </c>
       <c r="F7" t="n">
         <v>0.02801408011519041</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02813133374329904</v>
+        <v>0.02813133374329899</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0281520619542892</v>
+        <v>0.02815206195428917</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02801408680434025</v>
+        <v>0.02801408680434021</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0281520619542892</v>
+        <v>0.02815206195428916</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02496264503762673</v>
+        <v>0.0212207207034663</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0281520619542892</v>
+        <v>0.02815206195428917</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006748262312231723</v>
+        <v>0.006748262312231656</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004214783797620491</v>
+        <v>0.004214783797620481</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004147608422264329</v>
+        <v>0.004147608422264312</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004214783797620491</v>
+        <v>0.004214783797620481</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004214783797620491</v>
+        <v>0.004214783797620481</v>
       </c>
       <c r="G8" t="n">
         <v>0.005615900277369541</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002278615155344388</v>
+        <v>0.002278615155344393</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004214783797620491</v>
+        <v>0.004214783797620481</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006108547361710694</v>
+        <v>0.006108547361710685</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008123322068307265</v>
+        <v>0.008123322068307294</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006214099283694667</v>
+        <v>0.006214099283694661</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008886826971756995</v>
+        <v>0.008886826971757003</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005246693453395964</v>
+        <v>0.005246693453395962</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007827769645855631</v>
+        <v>0.007827769645855624</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005246693453395964</v>
+        <v>0.005246693453395962</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005246693453395964</v>
+        <v>0.005246693453395962</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008411137965197669</v>
+        <v>0.008411137965197652</v>
       </c>
       <c r="H9" t="n">
-        <v>0.007074158089975173</v>
+        <v>0.007074158089975171</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005246693453395964</v>
+        <v>0.005246693453395962</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008628006249577413</v>
+        <v>0.008628006249577406</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009447013566813621</v>
+        <v>0.009447013566813612</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008672573748275576</v>
+        <v>0.003127080960542495</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01567948043014004</v>
+        <v>0.01567948043014008</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03039589348898135</v>
+        <v>0.03039589348898138</v>
       </c>
       <c r="D2" t="n">
         <v>0.02972091806296256</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03039589348898135</v>
+        <v>0.03039589348898138</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03039589348898135</v>
+        <v>0.03039589348898138</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03511499962506962</v>
+        <v>0.03511499962506964</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02888744275140718</v>
+        <v>0.02888744275140725</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03039589348898135</v>
+        <v>0.03039589348898138</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03976421165000667</v>
+        <v>0.03976421165000668</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02945402794500931</v>
+        <v>0.02945402794500926</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0225738121706574</v>
+        <v>0.02257381217065741</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003035219710756906</v>
+        <v>0.003035219710756911</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002798293720050252</v>
+        <v>0.002798293720050253</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003035219710756906</v>
+        <v>0.003035219710756911</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002842412302599349</v>
+        <v>0.002842412302599362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00284241230259935</v>
+        <v>0.002842412302599358</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003017760240580161</v>
+        <v>0.003017760240580163</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003035219710756906</v>
+        <v>0.003035219710756911</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00291742589977653</v>
+        <v>0.002917425899776541</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003035219710756906</v>
+        <v>0.003035219710756911</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003035219710756906</v>
+        <v>0.003035219710756911</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003035219710756906</v>
+        <v>0.003035219710756911</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008116621742232292</v>
+        <v>0.004373863918641688</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004214929986536801</v>
+        <v>0.004214929986536825</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008141999116131855</v>
+        <v>0.008141999116131844</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004094901296630741</v>
+        <v>0.004094901296630732</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004255966777580435</v>
+        <v>0.004255966777580431</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004356404448464948</v>
+        <v>0.008099162272055564</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008216597585221372</v>
+        <v>0.008216597585221403</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004256070107661307</v>
+        <v>0.004256070107661316</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008139755141598161</v>
+        <v>0.004491464895689109</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004377765042779955</v>
+        <v>0.004377765042779844</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004374541506231499</v>
+        <v>0.004374541506231509</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006126251383387488</v>
+        <v>0.006126251383387508</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006008457572407116</v>
+        <v>0.006008457572407119</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006126128266375206</v>
+        <v>0.006126128266375226</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006003034691770649</v>
+        <v>0.006003034691770658</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006003034691770649</v>
+        <v>0.006003034691770658</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00610879191321075</v>
+        <v>0.006108791913210752</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006126251383387488</v>
+        <v>0.006126251383387508</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006008457572407116</v>
+        <v>0.006008457572407119</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006126251383387488</v>
+        <v>0.006126251383387508</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006126251383387488</v>
+        <v>0.006126251383387508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006126251383387488</v>
+        <v>0.006126251383387508</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01291855669580204</v>
+        <v>0.01291855669580205</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01954247762443433</v>
+        <v>0.01954247762445089</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02106268942042385</v>
+        <v>0.02106268942042393</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01769803136190738</v>
+        <v>0.01769803136190742</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01301142087295287</v>
+        <v>0.0130114208729529</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01964652214984474</v>
+        <v>0.01964652214984483</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01966398162002184</v>
+        <v>0.01966398162002188</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01954618780904114</v>
+        <v>0.0195461878090412</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01966530728945392</v>
+        <v>0.01966530728945393</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01279325696471601</v>
+        <v>0.01279325696471606</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02671014199677074</v>
+        <v>0.02671014199677083</v>
       </c>
     </row>
     <row r="7">
@@ -1114,34 +1114,34 @@
         <v>0.01239168899590093</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01506415616407563</v>
+        <v>0.01506415616407565</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01518195125234826</v>
+        <v>0.01518195125234827</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01828405845929872</v>
+        <v>0.01828405845929875</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01506415547105375</v>
+        <v>0.01506415547105373</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01516449050487924</v>
+        <v>0.01516449050487927</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01518194997505599</v>
+        <v>0.015181949975056</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01506415616407563</v>
+        <v>0.01506415616407565</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01518194997505599</v>
+        <v>0.015181949975056</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01356526234275721</v>
+        <v>0.01356526234275723</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01518194997505599</v>
+        <v>0.015181949975056</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009388527262897817</v>
+        <v>0.009388527262897814</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004447795831448497</v>
+        <v>0.004447795831448502</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009022070137413648</v>
+        <v>0.00902207013741365</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004447795831448497</v>
+        <v>0.004447795831448502</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004447795831448497</v>
+        <v>0.004447795831448502</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008897115634265693</v>
+        <v>0.008897115634265682</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009120575280819642</v>
+        <v>0.009120575280819629</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004447795831448497</v>
+        <v>0.004447795831448502</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008835078673566312</v>
+        <v>0.008835078673566317</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009009201200431725</v>
+        <v>0.009009201200431702</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009278461369751682</v>
+        <v>0.009278461369751656</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009347104620078454</v>
+        <v>0.009347104620078449</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004703600067320934</v>
+        <v>0.004703600067320939</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009197864033112603</v>
+        <v>0.0091978640331126</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004703600067320934</v>
+        <v>0.004703600067320939</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004703600067320934</v>
+        <v>0.004703600067320939</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009144532246432016</v>
+        <v>0.009144532246432014</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009238405291424695</v>
+        <v>0.009238405291424676</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004703600067320934</v>
+        <v>0.004703600067320939</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009121976017102008</v>
+        <v>0.009121976017102001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009192638211618346</v>
+        <v>0.009192638211618333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00928137967001337</v>
+        <v>0.009302510205977188</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03380694518029965</v>
+        <v>0.03380694518029961</v>
       </c>
       <c r="C2" t="n">
         <v>0.1796038114713068</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1726839442366328</v>
+        <v>0.1726839442366329</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05526593035883265</v>
+        <v>0.05526593035883259</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05526593035883265</v>
+        <v>0.05526593035883259</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1195733209147189</v>
+        <v>0.119573320914719</v>
       </c>
       <c r="H2" t="n">
         <v>0.1328431577757918</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05526593035883265</v>
+        <v>0.05526593035883259</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1981289972521836</v>
+        <v>0.1981289972521833</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0593676715137434</v>
+        <v>0.05936767151374327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.193628380556668</v>
+        <v>0.1936283805566678</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003525626344098732</v>
+        <v>0.00352562634409874</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003369076271382522</v>
+        <v>0.00336907627138252</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003525626344098732</v>
+        <v>0.003525626344098738</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003291929898167018</v>
+        <v>0.003291929898167041</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003291929898167021</v>
+        <v>0.003291929898167039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003504826951850786</v>
+        <v>0.00350482695185081</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003525626344098732</v>
+        <v>0.003525626344098741</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003386360955834095</v>
+        <v>0.003386360955834096</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003525626344098732</v>
+        <v>0.003525626344098741</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003525626344098732</v>
+        <v>0.003525626344098738</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003525626344098732</v>
+        <v>0.003525626344098738</v>
       </c>
     </row>
     <row r="4">
@@ -1387,34 +1387,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005287124720452591</v>
+        <v>0.009828287873760907</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005393701607407597</v>
+        <v>0.005393701607407599</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005450994599426765</v>
+        <v>0.005451009025788044</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00487384937765369</v>
+        <v>0.004873849377653687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005142603731810345</v>
+        <v>0.005142603731810338</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009807488481512952</v>
+        <v>0.005266325328204641</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01003722146933663</v>
+        <v>0.01003722146933664</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00968902248549626</v>
+        <v>0.005147859332187953</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009855281323432961</v>
+        <v>0.009855281323432975</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005214709407349303</v>
+        <v>0.005214709407349304</v>
       </c>
       <c r="L4" t="n">
         <v>0.005329192701179531</v>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007290632401697219</v>
+        <v>0.007290632401697222</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00729225421091863</v>
+        <v>0.007292254210918637</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00729051346446004</v>
+        <v>0.007290513464460034</v>
       </c>
       <c r="E5" t="n">
         <v>0.007150737664041037</v>
@@ -1442,22 +1442,22 @@
         <v>0.007150737664041037</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00726983300944926</v>
+        <v>0.007269833009449263</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007290632401697219</v>
+        <v>0.007290632401697222</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007151367013432576</v>
+        <v>0.007151367013432585</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007290632401697219</v>
+        <v>0.007290632401697222</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007290632401697219</v>
+        <v>0.007290632401697222</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007290632401697219</v>
+        <v>0.007290632401697222</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01498275071342004</v>
+        <v>0.01498275071342009</v>
       </c>
       <c r="C6" t="n">
         <v>0.02287714872987531</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02451082523577915</v>
+        <v>0.02451082523577922</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02057781586618872</v>
+        <v>0.02057781586618873</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01509333499588111</v>
+        <v>0.01509333499588113</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02285363402530168</v>
+        <v>0.0228536340253017</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02287443341755667</v>
+        <v>0.02287443341755672</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02273516802928498</v>
+        <v>0.022735168029285</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02287598435895783</v>
+        <v>0.0228759843589579</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01483615865562231</v>
+        <v>0.01483615865562233</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03111795589348185</v>
+        <v>0.0311179558934819</v>
       </c>
     </row>
     <row r="7">
@@ -1507,16 +1507,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01646695537523477</v>
+        <v>0.01646695537523476</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02031392267203295</v>
+        <v>0.02031392267203296</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02031230267918093</v>
+        <v>0.02031230267918097</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02461048084090031</v>
+        <v>0.0246104808409003</v>
       </c>
       <c r="F7" t="n">
         <v>0.02017303272752701</v>
@@ -1525,19 +1525,19 @@
         <v>0.02029150147056359</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02031230086281151</v>
+        <v>0.02031230086281154</v>
       </c>
       <c r="I7" t="n">
         <v>0.0201730354745469</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02031230086281151</v>
+        <v>0.02031230086281154</v>
       </c>
       <c r="K7" t="n">
         <v>0.01808429334943042</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02031230086281151</v>
+        <v>0.02031230086281154</v>
       </c>
     </row>
     <row r="8">
@@ -1550,34 +1550,34 @@
         <v>0.02332096655863214</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006448317613038141</v>
+        <v>0.0006448317613038142</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002897751283397398</v>
+        <v>0.002897751283397394</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005077736034473472</v>
+        <v>0.005077736034473469</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005077736034473472</v>
+        <v>0.005077736034473469</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00782917819127728</v>
+        <v>0.007829178191277288</v>
       </c>
       <c r="H8" t="n">
         <v>0.004166554379894866</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005077736034473472</v>
+        <v>0.005077736034473469</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006907857879169934</v>
+        <v>0.006907857879169933</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01416655500659431</v>
+        <v>0.01416655500659432</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002184669129782991</v>
+        <v>0.002184669129782993</v>
       </c>
     </row>
     <row r="9">
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0233372334484217</v>
+        <v>0.02333723344842173</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002851171155555857</v>
+        <v>0.002851171155555859</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005039668304565222</v>
+        <v>0.005039668304565219</v>
       </c>
       <c r="E9" t="n">
         <v>0.005613963781961166</v>
@@ -1602,7 +1602,7 @@
         <v>0.005613963781961166</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009142329310190742</v>
+        <v>0.009142329310190746</v>
       </c>
       <c r="H9" t="n">
         <v>0.005558713107085119</v>
@@ -1614,10 +1614,10 @@
         <v>0.009197711727701405</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01461783325797914</v>
+        <v>0.01461783325797915</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004279232942128708</v>
+        <v>0.004279232942128711</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02368919567650015</v>
+        <v>0.02368919567650017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1073403050958526</v>
+        <v>0.1073403050958527</v>
       </c>
       <c r="D2" t="n">
         <v>0.1159948583435174</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03738099926705999</v>
+        <v>0.03738099926706007</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03738099926705999</v>
+        <v>0.03738099926706007</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0731397771453436</v>
+        <v>0.07313977714534416</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07644959280814317</v>
+        <v>0.07644959280814323</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03738099926705999</v>
+        <v>0.03738099926706007</v>
       </c>
       <c r="J2" t="n">
         <v>0.1182180631447172</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02919021197172969</v>
+        <v>0.02919021197172971</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06412245224694856</v>
+        <v>0.06412245224694857</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003297116172674249</v>
+        <v>0.0032971161726743</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003133656530015697</v>
+        <v>0.0031336565300157</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003297116172674249</v>
+        <v>0.003297116172674299</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003204193080899479</v>
+        <v>0.003204193080899493</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003204193080899484</v>
+        <v>0.003204193080899493</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003277978928802478</v>
+        <v>0.003277978928802489</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003297116172674249</v>
+        <v>0.003297116172674299</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003168636060463981</v>
+        <v>0.003168636060463988</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003297116172674248</v>
+        <v>0.0032971161726743</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003297116172674249</v>
+        <v>0.003297116172674299</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003297116172674249</v>
+        <v>0.003297116172674299</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008916945434904198</v>
+        <v>0.008916945434904242</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004873388415008173</v>
+        <v>0.00487338841500815</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008959630890162858</v>
+        <v>0.008959630890162957</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004503516305476466</v>
+        <v>0.00450351630547647</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004711983421112703</v>
+        <v>0.004711983421112708</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004815660684748536</v>
+        <v>0.008897808191032428</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009145660911213684</v>
+        <v>0.009145660911213715</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004706317816410059</v>
+        <v>0.004706317816410063</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004993597722587927</v>
+        <v>0.004993597722587919</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004779969338866846</v>
+        <v>0.004779969338866885</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004838102413252049</v>
+        <v>0.004838102413252074</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006695333304234782</v>
+        <v>0.006695333304234797</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006696852378657189</v>
+        <v>0.006696852378657191</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006695225390118414</v>
+        <v>0.006695225390118373</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006573858994226876</v>
+        <v>0.006573858994226884</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006573858994226876</v>
+        <v>0.006573858994226884</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006676196060362993</v>
+        <v>0.006676196060362981</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006695333304234782</v>
+        <v>0.006695333304234797</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006566853192024479</v>
+        <v>0.006566853192024481</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006695333304234782</v>
+        <v>0.006695333304234797</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006695333304234782</v>
+        <v>0.006695333304234797</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006695333304234782</v>
+        <v>0.006695333304234797</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01387113624931968</v>
+        <v>0.01387113624931974</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02115309270875221</v>
+        <v>0.02115309270871691</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0226512531276055</v>
+        <v>0.02265125312760553</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01903332211470045</v>
+        <v>0.01903332211470048</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01397741676973218</v>
+        <v>0.0139774167697322</v>
       </c>
       <c r="G6" t="n">
         <v>0.02112418147485817</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02114331871874848</v>
+        <v>0.02114331871874852</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02101483860651967</v>
+        <v>0.02101483860651964</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02114474791046825</v>
+        <v>0.0211447479104683</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0137360517264384</v>
+        <v>0.01373605172643842</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02873972139763884</v>
+        <v>0.02873972139763888</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01398223841119841</v>
+        <v>0.01398223841119845</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01717972504490618</v>
+        <v>0.01717972504490617</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01717820756702531</v>
+        <v>0.01717820756702538</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0207378040798772</v>
+        <v>0.02073780407987722</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01704972424259929</v>
+        <v>0.01704972424259933</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01715906872661194</v>
+        <v>0.01715906872661197</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01717820597048375</v>
+        <v>0.01717820597048382</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01704972585827348</v>
+        <v>0.01704972585827349</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01717820597048375</v>
+        <v>0.01717820597048382</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01532645048659986</v>
+        <v>0.01532645048659987</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01717820597048375</v>
+        <v>0.01717820597048382</v>
       </c>
     </row>
     <row r="8">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02342488824118189</v>
+        <v>0.0234248882411819</v>
       </c>
       <c r="C8" t="n">
         <v>0.001838559266967116</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003859388111929223</v>
+        <v>0.003859388111929238</v>
       </c>
       <c r="E8" t="n">
         <v>0.005263840850978633</v>
@@ -1958,22 +1958,22 @@
         <v>0.005263840850978633</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008594531603599893</v>
+        <v>0.008594531603599877</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005030115355362413</v>
+        <v>0.005030115355362423</v>
       </c>
       <c r="I8" t="n">
         <v>0.005263840850978633</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008362714528278312</v>
+        <v>0.008362714528278314</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01459056070986309</v>
+        <v>0.01459056070986313</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004093496182518841</v>
+        <v>0.004093496182518857</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02332550230048359</v>
+        <v>0.02332550230048358</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003166328010071804</v>
+        <v>0.003166328010071805</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005316613021261297</v>
+        <v>0.005316613021261283</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005588851964255249</v>
+        <v>0.005588851964255253</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005588851964255249</v>
+        <v>0.005588851964255253</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009347416863625384</v>
+        <v>0.009347416863625394</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005794751544189037</v>
+        <v>0.005794751544189069</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005588851964255249</v>
+        <v>0.005588851964255253</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009701005605975024</v>
+        <v>0.009701005605975038</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01465615271614557</v>
+        <v>0.01465615271614559</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004704513222468883</v>
+        <v>0.0047045132224689</v>
       </c>
     </row>
   </sheetData>
@@ -2102,31 +2102,31 @@
         <v>0.01128357393799489</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06922041094361404</v>
+        <v>0.06922041094361399</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07801406630083296</v>
+        <v>0.07801406630083289</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0163639935734353</v>
+        <v>0.01636399357343529</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0163639935734353</v>
+        <v>0.01636399357343529</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04433107378834481</v>
+        <v>0.04433107378834505</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05213122150124896</v>
+        <v>0.05213122150124894</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0163639935734353</v>
+        <v>0.01636399357343529</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05145926794690544</v>
+        <v>0.05145926794690546</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01675636976287087</v>
+        <v>0.01675636976287083</v>
       </c>
       <c r="L2" t="n">
         <v>0.02651524201052957</v>
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003146094322986241</v>
+        <v>0.003146094322986228</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002979088895688551</v>
+        <v>0.002979088895688546</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003146094322986241</v>
+        <v>0.003146094322986229</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003075395045564974</v>
+        <v>0.003075395045564969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003075395045564974</v>
+        <v>0.00307539504556497</v>
       </c>
       <c r="G3" t="n">
         <v>0.003131369330279371</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003146094322986241</v>
+        <v>0.003146094322986229</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003046948433119684</v>
+        <v>0.003046948433119685</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003146094322986241</v>
+        <v>0.003146094322986229</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003146094322986241</v>
+        <v>0.003146094322986229</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003146094322986241</v>
+        <v>0.003146094322986229</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004565979397008239</v>
+        <v>0.004565979397008225</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004578778506466657</v>
+        <v>0.004578778506466664</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004648345758811663</v>
+        <v>0.00464832922718732</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00427536918944775</v>
+        <v>0.004275369189447729</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004469808412403213</v>
+        <v>0.004469808412403201</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008501192231451411</v>
+        <v>0.008501192231451408</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008735331760449364</v>
+        <v>0.008735331760449347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008416771334291712</v>
+        <v>0.008416771334291705</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008529340452848469</v>
+        <v>0.008529340452848458</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004536692421361266</v>
+        <v>0.004536692421361135</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004560458473421359</v>
+        <v>0.004560458473420871</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006410172232372149</v>
+        <v>0.006410172232372145</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006411766577229055</v>
+        <v>0.006411766577229056</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006410063110149785</v>
+        <v>0.006410063110149774</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006319348111678126</v>
+        <v>0.006319348111678115</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006319348111678126</v>
+        <v>0.006319348111678115</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006395447239665297</v>
+        <v>0.006395447239665294</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006410172232372149</v>
+        <v>0.006410172232372145</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006311026342505605</v>
+        <v>0.006311026342505598</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006410172232372149</v>
+        <v>0.006410172232372145</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006410172232372149</v>
+        <v>0.006410172232372145</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006410172232372149</v>
+        <v>0.006410172232372145</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01349486601666559</v>
+        <v>0.01349486601666558</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02061403201388924</v>
+        <v>0.02061403201392828</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02207685991460684</v>
+        <v>0.02207685991460681</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01856826553945303</v>
+        <v>0.01856826553945301</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01362606491262019</v>
+        <v>0.01362606491262016</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02058822699165265</v>
+        <v>0.02058822699165264</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02060295198437886</v>
+        <v>0.02060295198437887</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02050380609449295</v>
+        <v>0.02050380609449293</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02060434892633348</v>
+        <v>0.02060434892633346</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01336282967055603</v>
+        <v>0.01336282967055601</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02802794214560898</v>
+        <v>0.02802794214560894</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01266958758700118</v>
+        <v>0.01266958758700119</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01553676547996037</v>
+        <v>0.01553676547996035</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0155351723503779</v>
+        <v>0.01553517235037789</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01874284733740764</v>
+        <v>0.01874284733740763</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01543602391664843</v>
+        <v>0.01543602391664841</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01552044614239661</v>
+        <v>0.01552044614239658</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01553517113510346</v>
+        <v>0.01553517113510345</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0154360252452369</v>
+        <v>0.01543602524523689</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01553517113510346</v>
+        <v>0.01553517113510345</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01192688962821574</v>
+        <v>0.01380747955580111</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01553517113510346</v>
+        <v>0.01553517113510345</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02362047751337479</v>
+        <v>0.02362047751337477</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002524932069377083</v>
+        <v>0.002524932069377079</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00458873823805058</v>
+        <v>0.004588738238050573</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005445081705694008</v>
+        <v>0.005445081705694002</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005445081705694008</v>
+        <v>0.005445081705694002</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009043296347317736</v>
+        <v>0.009043296347317729</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005356426361282859</v>
+        <v>0.005356426361282855</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005445081705694008</v>
+        <v>0.005445081705694002</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009189336001955848</v>
+        <v>0.009189336001955832</v>
       </c>
       <c r="K8" t="n">
-        <v>0.014701065178221</v>
+        <v>0.01470106517822098</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004721802360521147</v>
+        <v>0.004721802360521143</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02334987487409505</v>
+        <v>0.02334987487409507</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003321032220250006</v>
+        <v>0.003321032220250003</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005501119341130279</v>
+        <v>0.005501119341130271</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005475317249701144</v>
+        <v>0.005475317249701139</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005475317249701144</v>
+        <v>0.005475317249701139</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009396565600021898</v>
+        <v>0.009396565600021896</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005814640476364391</v>
+        <v>0.005814640476364389</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005475317249701144</v>
+        <v>0.005475317249701139</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009622982945345934</v>
+        <v>0.009622982945345932</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01459192760888928</v>
+        <v>0.01459192760888927</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004865729782529743</v>
+        <v>0.004865729782529741</v>
       </c>
     </row>
   </sheetData>
@@ -2498,34 +2498,34 @@
         <v>0.01361325948938709</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01441526830376926</v>
+        <v>0.01441526830376927</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09409248131360295</v>
+        <v>0.09409248131360289</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02251872941426058</v>
+        <v>0.02251872941426052</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02251872941426058</v>
+        <v>0.02251872941426052</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07585414718808386</v>
+        <v>0.07585414718808449</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1060271508964351</v>
+        <v>0.1060271508964349</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02251872941426058</v>
+        <v>0.02251872941426052</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1868336155604766</v>
+        <v>0.1868336155604768</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04094041563000347</v>
+        <v>0.04094041563000355</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1804926760457592</v>
+        <v>0.1804926760457591</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003134237111875765</v>
+        <v>0.003134237111875768</v>
       </c>
       <c r="C3" t="n">
         <v>0.002878265025402605</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003134237111875765</v>
+        <v>0.003134237111875768</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002956601956202133</v>
+        <v>0.002956601956202138</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002956601956202133</v>
+        <v>0.002956601956202138</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003113835371873374</v>
+        <v>0.003113835371873376</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003134237111875765</v>
+        <v>0.003134237111875768</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002997445005418483</v>
+        <v>0.002997445005418485</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003134237111875765</v>
+        <v>0.003134237111875768</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003134237111875765</v>
+        <v>0.003134237111875768</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003134237111875765</v>
+        <v>0.003134237111875768</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004585380425500463</v>
+        <v>0.004585380425500466</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004439893908174232</v>
+        <v>0.0044398939081742</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004663063028877053</v>
+        <v>0.00466304793658026</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004211067312423124</v>
+        <v>0.004211067312423112</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004443361367064962</v>
+        <v>0.004443361367064963</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004564978685498068</v>
+        <v>0.004564978685498076</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009008569484936117</v>
+        <v>0.009008569484936115</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004448588319043182</v>
+        <v>0.008683783749820401</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008837206366585554</v>
+        <v>0.004761427874000619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004546073621881432</v>
+        <v>0.004546073621881436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004629969808570052</v>
+        <v>0.004629969808570055</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006691237222486919</v>
+        <v>0.006691237222486927</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006689988729976511</v>
+        <v>0.006689988729976521</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006691127214152834</v>
+        <v>0.006691127214152839</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006567159757514682</v>
+        <v>0.006567159757514687</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006567159757514682</v>
+        <v>0.006567159757514687</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006670835482484526</v>
+        <v>0.006670835482484535</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006691237222486919</v>
+        <v>0.006691237222486927</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006554445116029643</v>
+        <v>0.006554445116029646</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006691237222486919</v>
+        <v>0.006691237222486927</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006691237222486919</v>
+        <v>0.006691237222486927</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006691237222486919</v>
+        <v>0.006691237222486927</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01421976963576355</v>
+        <v>0.01421976963576358</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02184357606207978</v>
+        <v>0.02184357606210947</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02340929834963404</v>
+        <v>0.02340929834963407</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01962494226831293</v>
+        <v>0.01962494226831298</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01433189388483281</v>
+        <v>0.01433189388483284</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02181064808045767</v>
+        <v>0.0218106480804577</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02183104982046469</v>
+        <v>0.02183104982046476</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02169425771400276</v>
+        <v>0.02169425771400282</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02183254565481752</v>
+        <v>0.02183254565481754</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01407838619871806</v>
+        <v>0.01407838619871809</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02978166841803339</v>
+        <v>0.02978166841803345</v>
       </c>
     </row>
     <row r="7">
@@ -2695,34 +2695,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01480361104059372</v>
+        <v>0.0148036110405937</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01827666176725145</v>
+        <v>0.01827666176725144</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01827791212088185</v>
+        <v>0.01827791212088182</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02215038534636387</v>
+        <v>0.02215038534636382</v>
       </c>
       <c r="F7" t="n">
         <v>0.01814111645632008</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01825750851975948</v>
+        <v>0.01825750851975949</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01827791025976186</v>
+        <v>0.01827791025976187</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01814111815330457</v>
+        <v>0.01814111815330458</v>
       </c>
       <c r="J7" t="n">
         <v>0.01827791025976186</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01390314690024994</v>
+        <v>0.01626488843032971</v>
       </c>
       <c r="L7" t="n">
         <v>0.01827791025976186</v>
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02355536303549632</v>
+        <v>0.02355536303549637</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003742652694071674</v>
+        <v>0.003742652694071677</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00432541577865632</v>
+        <v>0.004325415778656329</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005483197351800155</v>
+        <v>0.005483197351800161</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005483197351800155</v>
+        <v>0.005483197351800161</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008521925097762116</v>
+        <v>0.008521925097762126</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004325426698964338</v>
+        <v>0.004325426698964346</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005483197351800155</v>
+        <v>0.005483197351800161</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006896458226316984</v>
+        <v>0.006896458226316981</v>
       </c>
       <c r="K8" t="n">
         <v>0.0143344215487664</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002185859083030998</v>
+        <v>0.002185859083031004</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02331046676616175</v>
+        <v>0.02331046676616177</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003760954704040574</v>
+        <v>0.003760954704040576</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005400839920840832</v>
+        <v>0.005400839920840834</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005584738468406237</v>
+        <v>0.005584738468406234</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005584738468406237</v>
+        <v>0.005584738468406234</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009261978533975056</v>
+        <v>0.009261978533975059</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00540265509166125</v>
+        <v>0.005402655091661252</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005584738468406237</v>
+        <v>0.005584738468406234</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009047142186338859</v>
+        <v>0.00904714218633886</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01454230855153832</v>
+        <v>0.01454230855153831</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004132131631778365</v>
+        <v>0.00413213163177837</v>
       </c>
     </row>
   </sheetData>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008886508093734759</v>
+        <v>0.008886508093734754</v>
       </c>
       <c r="C2" t="n">
         <v>0.01317268604645614</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01684615541312433</v>
+        <v>0.01684615541312434</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01779344540443886</v>
+        <v>0.01779344540443877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01779344540443886</v>
+        <v>0.01779344540443877</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0193017378037343</v>
+        <v>0.019301737803734</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02161078001053103</v>
+        <v>0.02161078001053101</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01779344540443886</v>
+        <v>0.01779344540443877</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0585999919138892</v>
+        <v>0.05859999191388923</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01456636157822958</v>
+        <v>0.01456636157822957</v>
       </c>
       <c r="L2" t="n">
         <v>0.03265936879183572</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002972851186683717</v>
+        <v>0.002972851186683715</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002784270327579669</v>
+        <v>0.002784270327579673</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002972851186683717</v>
+        <v>0.002972851186683715</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002943242391238181</v>
+        <v>0.00294324239123818</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002943242391238181</v>
+        <v>0.00294324239123818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002955016341762888</v>
+        <v>0.002955016341762893</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002972851186683717</v>
+        <v>0.002972851186683715</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002852619155348076</v>
+        <v>0.002852619155348074</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002972851186683717</v>
+        <v>0.002972851186683715</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002972851186683717</v>
+        <v>0.002972851186683715</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002972851186683717</v>
+        <v>0.002972851186683715</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004260390574682105</v>
+        <v>0.004260390574682121</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00419996441299923</v>
+        <v>0.004199964412999212</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004256200544849228</v>
+        <v>0.008031784316505195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004004540806770756</v>
+        <v>0.004004540806770754</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004151164644148561</v>
+        <v>0.004151164644148569</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008007014548328639</v>
+        <v>0.004242555729761292</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00820293955876714</v>
+        <v>0.008202939558767127</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00790461736191383</v>
+        <v>0.007904617361913831</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004385640482587946</v>
+        <v>0.008020229597162098</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004252079227031282</v>
+        <v>0.004252079227031285</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004259471337629541</v>
+        <v>0.004259471337629542</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006109511391004169</v>
+        <v>0.006109511391004171</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006110713551229464</v>
+        <v>0.006110713551229466</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006109407832102508</v>
+        <v>0.006109407832102504</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006006213610329785</v>
+        <v>0.00600621361032978</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006006213610329785</v>
+        <v>0.00600621361032978</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006091676546083362</v>
+        <v>0.00609167654608336</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006109511391004169</v>
+        <v>0.006109511391004171</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005989279359668529</v>
+        <v>0.005989279359668537</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006109511391004169</v>
+        <v>0.006109511391004171</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006109511391004169</v>
+        <v>0.006109511391004171</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006109511391004169</v>
+        <v>0.006109511391004171</v>
       </c>
     </row>
     <row r="6">
@@ -3051,28 +3051,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01306866511017578</v>
+        <v>0.01306866511017576</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0199943187450795</v>
+        <v>0.01999431874504807</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0214076192759457</v>
+        <v>0.02140761927594572</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01798205448012418</v>
+        <v>0.01798205448012416</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01317753143953855</v>
+        <v>0.01317753143953853</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01995761717232089</v>
+        <v>0.01995761717232088</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01997545201725531</v>
+        <v>0.01997545201725529</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01985521998590605</v>
+        <v>0.01985521998590604</v>
       </c>
       <c r="J6" t="n">
         <v>0.01997680939851304</v>
@@ -3081,7 +3081,7 @@
         <v>0.01294036799744087</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02719016847761711</v>
+        <v>0.0271901684776171</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01237791235480484</v>
+        <v>0.01237791235480485</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01519428580433723</v>
+        <v>0.01519428580433721</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01519308474417126</v>
+        <v>0.01519308474417125</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01832149982247227</v>
+        <v>0.01832149982247226</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01507285100371937</v>
+        <v>0.01507285100371939</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0151752487991911</v>
+        <v>0.01517524879919111</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01519308364411194</v>
+        <v>0.01519308364411193</v>
       </c>
       <c r="I7" t="n">
         <v>0.0150728516127763</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01519308364411194</v>
+        <v>0.01519308364411193</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01164828019946499</v>
+        <v>0.01356196280573723</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01519308364411194</v>
+        <v>0.01519308364411193</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0235054994561798</v>
+        <v>0.02350549945617978</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003630471259481205</v>
+        <v>0.003630471259481202</v>
       </c>
       <c r="D8" t="n">
         <v>0.005937405221861314</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005433564885670241</v>
+        <v>0.005433564885670246</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005433564885670241</v>
+        <v>0.005433564885670245</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009572345349231699</v>
+        <v>0.009572345349231693</v>
       </c>
       <c r="H8" t="n">
         <v>0.005869733732258805</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005433564885670241</v>
+        <v>0.005433564885670246</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009386077305255317</v>
+        <v>0.009386077305255322</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0146900752112533</v>
+        <v>0.01469007521125327</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004494994219524951</v>
+        <v>0.004494994219524952</v>
       </c>
     </row>
     <row r="9">
@@ -3174,34 +3174,34 @@
         <v>0.02320506077260875</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003642918945343535</v>
+        <v>0.003642918945343541</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00596890829782199</v>
+        <v>0.005968908297821989</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005485880696889409</v>
+        <v>0.00548588069688941</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005485880696889409</v>
+        <v>0.00548588069688941</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00957669494272911</v>
+        <v>0.009576694942729102</v>
       </c>
       <c r="H9" t="n">
         <v>0.005941619670253063</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005485880696889409</v>
+        <v>0.00548588069688941</v>
       </c>
       <c r="J9" t="n">
         <v>0.009913562968758701</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01455188829117372</v>
+        <v>0.01455188829117369</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004718611999280248</v>
+        <v>0.004718611999280247</v>
       </c>
     </row>
   </sheetData>
@@ -3287,34 +3287,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008599788720060399</v>
+        <v>0.008599788720060356</v>
       </c>
       <c r="C2" t="n">
         <v>0.0134627481133618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.016080419602897</v>
+        <v>0.01608041960289697</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01548685597904238</v>
+        <v>0.01548685597904239</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01548685597904238</v>
+        <v>0.01548685597904239</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01511497825841445</v>
+        <v>0.01511497825841449</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01769093862546029</v>
+        <v>0.01769093862546027</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01548685597904238</v>
+        <v>0.01548685597904239</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01847570971537865</v>
+        <v>0.01847570971537862</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01287060428164853</v>
+        <v>0.01287060428164847</v>
       </c>
       <c r="L2" t="n">
         <v>0.01571103033876277</v>
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002954578612930088</v>
+        <v>0.002954578612930028</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00278698892739298</v>
+        <v>0.002786988927392983</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002954578612930088</v>
+        <v>0.002954578612930028</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002926399416784654</v>
+        <v>0.002926399416784656</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002926399416784655</v>
+        <v>0.002926399416784656</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002940925079378793</v>
+        <v>0.002940925079378511</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002954578612930088</v>
+        <v>0.002954578612930028</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002862227079973418</v>
+        <v>0.002862227079973048</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002954578612930088</v>
+        <v>0.002954578612930028</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002954578612930088</v>
+        <v>0.002954578612930028</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002954578612930088</v>
+        <v>0.002954578612930028</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007986145282362323</v>
+        <v>0.007986145282362286</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004184109339604589</v>
+        <v>0.004184109339604566</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004227794892643461</v>
+        <v>0.004227794892643436</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004005968574783979</v>
+        <v>0.004005968574783978</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004150907830300537</v>
+        <v>0.004150907830300555</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007972491748810819</v>
+        <v>0.00797249174881081</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008161312477235564</v>
+        <v>0.004229244888797616</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004142130184297121</v>
+        <v>0.007893793749405287</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007979415100607002</v>
+        <v>0.004345379793010388</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004232294500588166</v>
+        <v>0.004232294500588195</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004227452599272745</v>
+        <v>0.004227452599272688</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006040010612943437</v>
+        <v>0.006040010612943432</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006041438905467288</v>
+        <v>0.00604143890546729</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006039902446159959</v>
+        <v>0.006039902446159946</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005961110266741973</v>
+        <v>0.00596111026674198</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005961110266741973</v>
+        <v>0.00596111026674198</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006026357079391934</v>
+        <v>0.006026357079391904</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006040010612943437</v>
+        <v>0.006040010612943432</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005947659079986405</v>
+        <v>0.00594765907998642</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006040010612943437</v>
+        <v>0.006040010612943432</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006040010612943437</v>
+        <v>0.006040010612943432</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006040010612943437</v>
+        <v>0.006040010612943432</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01297529362770465</v>
+        <v>0.01297529362770462</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01983915304642058</v>
+        <v>0.01983915304645631</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02124338736754393</v>
+        <v>0.02124338736754389</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01787094065536515</v>
+        <v>0.01787094065536516</v>
       </c>
       <c r="F6" t="n">
         <v>0.01310810498754307</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01980973644454875</v>
+        <v>0.01980973644454877</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01982338997811559</v>
+        <v>0.01982338997811558</v>
       </c>
       <c r="I6" t="n">
         <v>0.01973103844514325</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01982473582502026</v>
+        <v>0.01982473582502019</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01284808672218539</v>
+        <v>0.01284808672218536</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02697679924443982</v>
+        <v>0.02697679924443983</v>
       </c>
     </row>
     <row r="7">
@@ -3490,34 +3490,34 @@
         <v>0.011848163244575</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01451853519984681</v>
+        <v>0.01451853519984682</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01451710791205327</v>
+        <v>0.01451710791205329</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01750465994712831</v>
+        <v>0.01750465994712833</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01442475478912063</v>
+        <v>0.01442475478912065</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01450345337377145</v>
+        <v>0.01450345337377146</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01451710690732295</v>
+        <v>0.01451710690732292</v>
       </c>
       <c r="I7" t="n">
         <v>0.01442475537436595</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01451710690732295</v>
+        <v>0.01451710690732292</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01290797160938364</v>
+        <v>0.01297071088996187</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01451710690732295</v>
+        <v>0.01451710690732292</v>
       </c>
     </row>
     <row r="8">
@@ -3530,34 +3530,34 @@
         <v>0.0234409719768757</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003569242767451581</v>
+        <v>0.003569242767451584</v>
       </c>
       <c r="D8" t="n">
         <v>0.005910841272076368</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00527542936203775</v>
+        <v>0.005275429362037753</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00527542936203775</v>
+        <v>0.005275429362037753</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009539081751066665</v>
+        <v>0.009539081751066649</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005908848551871915</v>
+        <v>0.005908848551871904</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005275429362037749</v>
+        <v>0.005275429362037753</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009691894685974253</v>
+        <v>0.009691894685974256</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01462786460577065</v>
+        <v>0.01462786460577064</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004770948543742894</v>
+        <v>0.004770948543742899</v>
       </c>
     </row>
     <row r="9">
@@ -3570,34 +3570,34 @@
         <v>0.02313751624076586</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003586486207324619</v>
+        <v>0.003586486207324622</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005931860373920155</v>
+        <v>0.00593186037392018</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00529759693093191</v>
+        <v>0.005297596930931913</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00529759693093191</v>
+        <v>0.005297596930931913</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009486547864386177</v>
+        <v>0.009486547864386165</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005931244426374127</v>
+        <v>0.005931244426374114</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00529759693093191</v>
+        <v>0.005297596930931913</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009677771141076109</v>
+        <v>0.009677771141076121</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01446675562555209</v>
+        <v>0.01446675562555208</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004783553925014897</v>
+        <v>0.004783553925014875</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01169407178780471</v>
+        <v>0.01169407178780477</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01399991781024969</v>
+        <v>0.01399991781024967</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02816559652470734</v>
+        <v>0.02816559652470747</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02124715671069842</v>
+        <v>0.02124715671069845</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02124715671069842</v>
+        <v>0.02124715671069845</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03599552325970728</v>
+        <v>0.03599552325970767</v>
       </c>
       <c r="H2" t="n">
-        <v>0.089745805756052</v>
+        <v>0.0897458057560522</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02124715671069842</v>
+        <v>0.02124715671069845</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02657857207788678</v>
+        <v>0.02657857207788682</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02002351076511476</v>
+        <v>0.0200235107651149</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1464784220578487</v>
+        <v>0.1464784220578489</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003045597705752361</v>
+        <v>0.003045597705752457</v>
       </c>
       <c r="C3" t="n">
         <v>0.002819185724277052</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003045597705752361</v>
+        <v>0.003045597705752457</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002909068940805868</v>
+        <v>0.002909068940805864</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002909068940805868</v>
+        <v>0.002909068940805865</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003026538488224328</v>
+        <v>0.003026538488224297</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003045597705752361</v>
+        <v>0.003045597705752457</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002917340125959142</v>
+        <v>0.002917340125959149</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003045597705752361</v>
+        <v>0.003045597705752457</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003045597705752361</v>
+        <v>0.003045597705752457</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003045597705752361</v>
+        <v>0.003045597705752457</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004361730923878697</v>
+        <v>0.004361730923878836</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004275105173268638</v>
+        <v>0.004275105173268603</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004359507655346403</v>
+        <v>0.004359507655346498</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004061802677096871</v>
+        <v>0.004061802677096864</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004234649794931345</v>
+        <v>0.004234649794931339</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008428382994513864</v>
+        <v>0.00434267170635069</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008624556688906382</v>
+        <v>0.008624556688906462</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008319184632248769</v>
+        <v>0.004233473344085519</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008450564806051379</v>
+        <v>0.004476756872744275</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004331685449439326</v>
+        <v>0.004331685449439452</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004396735037918096</v>
+        <v>0.004396735037918118</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006425580897100039</v>
+        <v>0.006425580897100104</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006426126817819834</v>
+        <v>0.006426126817819828</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00642547159832269</v>
+        <v>0.006425471598322803</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006312963575285941</v>
+        <v>0.006312963575285931</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006312963575285941</v>
+        <v>0.006312963575285931</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006406521679571912</v>
+        <v>0.006406521679572017</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006425580897100039</v>
+        <v>0.006425580897100104</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006297323317306779</v>
+        <v>0.006297323317306774</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006425580897100039</v>
+        <v>0.006425580897100104</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006425580897100039</v>
+        <v>0.006425580897100104</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006425580897100039</v>
+        <v>0.006425580897100104</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01382497894726175</v>
+        <v>0.01382497894726185</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02122499971772423</v>
+        <v>0.02122499971769535</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02273883093634406</v>
+        <v>0.02273883093634413</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01907526166731156</v>
+        <v>0.01907526166731154</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01394014483693796</v>
+        <v>0.01394014483693795</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02118886907635307</v>
+        <v>0.0211888690763532</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0212079282938855</v>
+        <v>0.02120792829388548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0210796707140879</v>
+        <v>0.02107967071408789</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02120937925471455</v>
+        <v>0.02120937925471463</v>
       </c>
       <c r="K6" t="n">
         <v>0.01368783687275609</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02892003623839464</v>
+        <v>0.02892003623839472</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01378842251211398</v>
+        <v>0.01378842251211405</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0169923128387813</v>
+        <v>0.01699231283878128</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01699176761066359</v>
+        <v>0.01699176761066366</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02056009949057083</v>
+        <v>0.02056009949057078</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01686350774116003</v>
+        <v>0.01686350774116001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01697270770053341</v>
+        <v>0.01697270770053345</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01699176691806151</v>
+        <v>0.01699176691806153</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01686350933826828</v>
+        <v>0.01686350933826823</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01699176691806151</v>
+        <v>0.01699176691806153</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01513573688005702</v>
+        <v>0.01513573688005704</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01699176691806151</v>
+        <v>0.01699176691806153</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02349378267962528</v>
+        <v>0.02349378267962536</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003704821485575327</v>
+        <v>0.003704821485575324</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005750062879498949</v>
+        <v>0.005750062879498967</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005407482986501699</v>
+        <v>0.005407482986501695</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005407482986501698</v>
+        <v>0.005407482986501695</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009276796416252956</v>
+        <v>0.009276796416253003</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004558469504504017</v>
+        <v>0.004558469504504043</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005407482986501699</v>
+        <v>0.005407482986501695</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01013391290800202</v>
+        <v>0.01013391290800199</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01465158805226533</v>
+        <v>0.01465158805226539</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002760216168258973</v>
+        <v>0.002760216168259015</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02322485960990338</v>
+        <v>0.02322485960990349</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003718578644304691</v>
+        <v>0.003718578644304688</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005924258246818663</v>
+        <v>0.005924258246818734</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005493912547239498</v>
+        <v>0.005493912547239495</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005493912547239498</v>
+        <v>0.005493912547239495</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009489255481609064</v>
+        <v>0.009489255481609071</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005440469474818393</v>
+        <v>0.005440469474818475</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005493912547239499</v>
+        <v>0.005493912547239495</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01020385195563603</v>
+        <v>0.01020385195563604</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0145770132352216</v>
+        <v>0.01457701323522165</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00430503482326649</v>
+        <v>0.004305034823266526</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.009224635767217302</v>
+        <v>0.009224635767217295</v>
       </c>
       <c r="C2" t="n">
         <v>0.01339024999273035</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01622628238611923</v>
+        <v>0.0162262823861192</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01743459616671991</v>
+        <v>0.01743459616671993</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01743459616671991</v>
+        <v>0.01743459616671993</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01544399652685653</v>
+        <v>0.01544399652685609</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01795602488678411</v>
+        <v>0.01795602488678408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01743459616671991</v>
+        <v>0.01743459616671993</v>
       </c>
       <c r="J2" t="n">
         <v>0.01913419248796768</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01421667979447921</v>
+        <v>0.01421667979447918</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01567988978571765</v>
+        <v>0.01567988978571763</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00294923102271855</v>
+        <v>0.002949231022718562</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002764351900169945</v>
+        <v>0.002764351900169939</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00294923102271855</v>
+        <v>0.002949231022718562</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002934839717943011</v>
+        <v>0.002934839717943014</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002934839717943012</v>
+        <v>0.002934839717943014</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002931539216082064</v>
+        <v>0.002931539216082069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00294923102271855</v>
+        <v>0.002949231022718562</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002829897850590896</v>
+        <v>0.00282989785059091</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00294923102271855</v>
+        <v>0.002949231022718562</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00294923102271855</v>
+        <v>0.002949231022718562</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00294923102271855</v>
+        <v>0.002949231022718562</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004216371331814192</v>
+        <v>0.007962199281257871</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004161848994556424</v>
+        <v>0.004161848994556375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004215173240882235</v>
+        <v>0.004215189211771274</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003970185482568499</v>
+        <v>0.003970185482568505</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004109062950914603</v>
+        <v>0.004109062950914592</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004198679525177698</v>
+        <v>0.004198679525177687</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008135453483146924</v>
+        <v>0.008135453483146923</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007842866109130231</v>
+        <v>0.007842866109130212</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007955387992859541</v>
+        <v>0.004326671718739084</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004211409481256984</v>
+        <v>0.004211409481256898</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004210316876003826</v>
+        <v>0.004210316876003821</v>
       </c>
     </row>
     <row r="5">
@@ -4202,19 +4202,19 @@
         <v>0.006041149430154887</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006042567243285214</v>
+        <v>0.006042567243285206</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00604104606799875</v>
+        <v>0.006041046067998744</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005942210787692719</v>
+        <v>0.00594221078769272</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005942210787692719</v>
+        <v>0.00594221078769272</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006023457623518393</v>
+        <v>0.006023457623518385</v>
       </c>
       <c r="H5" t="n">
         <v>0.006041149430154887</v>
@@ -4242,28 +4242,28 @@
         <v>0.01296702402139767</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01983650683477283</v>
+        <v>0.01983650683477279</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02123392121911797</v>
+        <v>0.02123392121911791</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01784090012469772</v>
+        <v>0.01784090012469769</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01307696150241377</v>
+        <v>0.01307696150241378</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0197964375222395</v>
+        <v>0.01979643752223955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01981412932888947</v>
+        <v>0.01981412932888942</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01969479615674838</v>
+        <v>0.01969479615674836</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01981547498103777</v>
+        <v>0.0198154749810377</v>
       </c>
       <c r="K6" t="n">
         <v>0.01283983552501392</v>
@@ -4279,16 +4279,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01225706130292634</v>
+        <v>0.01225706130292632</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01504236124457707</v>
+        <v>0.01504236124457706</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01504094445095183</v>
+        <v>0.0150409444509518</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01813415144522961</v>
+        <v>0.0181341514452296</v>
       </c>
       <c r="F7" t="n">
         <v>0.01492160971197766</v>
@@ -4297,19 +4297,19 @@
         <v>0.01502325162481025</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01504094343144676</v>
+        <v>0.01504094343144674</v>
       </c>
       <c r="I7" t="n">
         <v>0.0149216102593191</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01504094343144676</v>
+        <v>0.01504094343144674</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01342795162183306</v>
+        <v>0.01153553864620362</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01504094343144676</v>
+        <v>0.01504094343144674</v>
       </c>
     </row>
     <row r="8">
@@ -4325,31 +4325,31 @@
         <v>0.00366457056439344</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005921161149191083</v>
+        <v>0.005921161149191078</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005425908427801276</v>
+        <v>0.005425908427801274</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005425908427801276</v>
+        <v>0.005425908427801274</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009625032532799943</v>
+        <v>0.009625032532799949</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005917041739546148</v>
+        <v>0.005917041739546142</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005425908427801276</v>
+        <v>0.005425908427801274</v>
       </c>
       <c r="J8" t="n">
         <v>0.01022452011362425</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01474979350075402</v>
+        <v>0.01474979350075399</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004824379987865416</v>
+        <v>0.004824379987865414</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02294485690600415</v>
+        <v>0.02294485690600417</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003679550088389667</v>
+        <v>0.003679550088389666</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005944319602135289</v>
+        <v>0.005944319602135286</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005473487954592677</v>
+        <v>0.005473487954592678</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005473487954592677</v>
+        <v>0.005473487954592678</v>
       </c>
       <c r="G9" t="n">
         <v>0.009575947102335759</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005942842802964718</v>
+        <v>0.005942842802964715</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005473487954592677</v>
+        <v>0.005473487954592678</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01021110932888176</v>
+        <v>0.01021110932888175</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01460589696209734</v>
+        <v>0.01460589696209732</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004836004371265586</v>
+        <v>0.004836004371265585</v>
       </c>
     </row>
   </sheetData>
@@ -4475,31 +4475,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008833502214377812</v>
+        <v>0.008833502214377795</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01340488412654961</v>
+        <v>0.01340488412654959</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01555125037519059</v>
+        <v>0.01555125037519057</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01544068238039765</v>
+        <v>0.01544068238039763</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01544068238039765</v>
+        <v>0.01544068238039763</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01483202660468359</v>
+        <v>0.01483202660468358</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01730087504122375</v>
+        <v>0.01730087504122372</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01544068238039765</v>
+        <v>0.01544068238039763</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01841327637492719</v>
+        <v>0.01841327637492716</v>
       </c>
       <c r="K2" t="n">
         <v>0.01369328576275756</v>
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002929637956866342</v>
+        <v>0.002929637956866334</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002763037465401214</v>
+        <v>0.002763037465401209</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002929637956866342</v>
+        <v>0.002929637956866334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002912322339560784</v>
+        <v>0.002912322339560774</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002912322339560784</v>
+        <v>0.002912322339560774</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002916038518521165</v>
+        <v>0.002916038518521154</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002929637956866342</v>
+        <v>0.002929637956866334</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002837630225288197</v>
+        <v>0.002837630225288185</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002929637956866343</v>
+        <v>0.002929637956866334</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002929637956866342</v>
+        <v>0.002929637956866334</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002929637956866342</v>
+        <v>0.002929637956866334</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004206773930442491</v>
+        <v>0.00794179788439385</v>
       </c>
       <c r="C4" t="n">
         <v>0.004156556941733487</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004198343656867869</v>
+        <v>0.004198327495270646</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003981712980355172</v>
+        <v>0.00398171298035517</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00412413277825489</v>
+        <v>0.004124132778254892</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007928198446048661</v>
+        <v>0.004193174492097304</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008112974609429955</v>
+        <v>0.008112974609429941</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007849790152815693</v>
+        <v>0.004114766198864343</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004315851312380988</v>
+        <v>0.007933171863355154</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004205815573628694</v>
+        <v>0.004205815573628684</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004199795142788242</v>
+        <v>0.004199795142788689</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005983760044628248</v>
+        <v>0.005983760044628242</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005985231435880711</v>
+        <v>0.005985231435880706</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005983651936477083</v>
+        <v>0.005983651936477088</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0059081969520983</v>
+        <v>0.005908196952098289</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0059081969520983</v>
+        <v>0.005908196952098289</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005970160606283048</v>
+        <v>0.005970160606283053</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005983760044628248</v>
+        <v>0.005983760044628242</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005891752313050103</v>
+        <v>0.005891752313050095</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005983760044628248</v>
+        <v>0.005983760044628242</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005983760044628248</v>
+        <v>0.005983760044628242</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005983760044628248</v>
+        <v>0.005983760044628242</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01288898076382286</v>
+        <v>0.01288898076382283</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01970557430605756</v>
+        <v>0.01970557430602284</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02109651277543061</v>
+        <v>0.02109651277543055</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01775107931940266</v>
+        <v>0.0177510793194026</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01302233161598253</v>
+        <v>0.01302233161598251</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0196733170749928</v>
+        <v>0.01967331707499279</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0196869165133535</v>
+        <v>0.01968691651335347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01959490878175981</v>
+        <v>0.0195949087817598</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01968825250239345</v>
+        <v>0.0196882525023934</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01276270561720567</v>
+        <v>0.01276270561720565</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02678792883781977</v>
+        <v>0.02678792883781971</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0117940282237961</v>
+        <v>0.01179402822379606</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01445150966247422</v>
+        <v>0.0144515096624742</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01445003925718719</v>
+        <v>0.01445003925718718</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01742301000547363</v>
+        <v>0.01742301000547359</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01435802997669885</v>
+        <v>0.01435802997669883</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01443643883287656</v>
+        <v>0.01443643883287654</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01445003827122175</v>
+        <v>0.01445003827122173</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01435803053964361</v>
+        <v>0.01435803053964356</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01445003827122175</v>
+        <v>0.01445003827122173</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01284870078576852</v>
+        <v>0.0128487007857685</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01445003827122175</v>
+        <v>0.01445003827122173</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02254760088685314</v>
+        <v>0.02254760088685317</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003634212883086292</v>
+        <v>0.00363421288308629</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005893052839348194</v>
+        <v>0.00589305283934819</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005254670181525633</v>
+        <v>0.00525467018152562</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005254670181525633</v>
+        <v>0.00525467018152562</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009457240640813207</v>
+        <v>0.009457240640813205</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005886570219566332</v>
+        <v>0.005886570219566339</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005254670181525633</v>
+        <v>0.00525467018152562</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009648985736305633</v>
+        <v>0.009648985736305637</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01462521013351356</v>
+        <v>0.01462521013351357</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004750703837320691</v>
+        <v>0.004750703837320687</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02226141399629056</v>
+        <v>0.02226141399629057</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003649732857622854</v>
+        <v>0.003649732857622855</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005907021547349739</v>
+        <v>0.005907021547349733</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005276638701728803</v>
+        <v>0.0052766387017288</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005276638701728801</v>
+        <v>0.0052766387017288</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009402236841495068</v>
+        <v>0.009402236841495064</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00590456962648758</v>
+        <v>0.00590456962648757</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005276638701728803</v>
+        <v>0.0052766387017288</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009634813883799893</v>
+        <v>0.00963481388379989</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0144757995773741</v>
+        <v>0.01447579957737411</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004761874627042939</v>
+        <v>0.004761874627042947</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1391148701834879</v>
+        <v>0.139114870183489</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05384168725244137</v>
+        <v>0.05384168725244126</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2730259730998582</v>
+        <v>0.2730259730998579</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05384168725244137</v>
+        <v>0.05384168725244126</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05384168725244137</v>
+        <v>0.05384168725244126</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2104575628769693</v>
+        <v>0.2104575628769696</v>
       </c>
       <c r="H2" t="n">
-        <v>0.240628862265487</v>
+        <v>0.2406288622654865</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05384168725244137</v>
+        <v>0.05384168725244126</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2086654510090269</v>
+        <v>0.2086654510090266</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09563489094235451</v>
+        <v>0.09563489094235468</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2241597077176095</v>
+        <v>0.2241597077176096</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003585972859797604</v>
+        <v>0.003585972859797619</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00316382886889029</v>
+        <v>0.003163828868890294</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003585972859797604</v>
+        <v>0.003585972859797619</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003225686266417517</v>
+        <v>0.003225686266417523</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003225686266417516</v>
+        <v>0.003225686266417523</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00356128314058856</v>
+        <v>0.003561283140588568</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003585972859797604</v>
+        <v>0.003585972859797619</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003421607277261437</v>
+        <v>0.003421607277261441</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003585972859797604</v>
+        <v>0.003585972859797619</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003585972859797604</v>
+        <v>0.003585972859797619</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003585972859797604</v>
+        <v>0.003585972859797619</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01051081418104345</v>
+        <v>0.005386208891879901</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004956032068951321</v>
+        <v>0.004956032068951335</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005638396659484406</v>
+        <v>0.005638405954819944</v>
       </c>
       <c r="E4" t="n">
         <v>0.004811673799686998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005195692425632403</v>
+        <v>0.005195692425632405</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01048612446183441</v>
+        <v>0.005361519172670845</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01065320682249955</v>
+        <v>0.01065320682249958</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01034644859850727</v>
+        <v>0.0103464485985073</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01055784778773907</v>
+        <v>0.005584138652997544</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005266159413164497</v>
+        <v>0.005266159413164483</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005641116911568037</v>
+        <v>0.005641116911568059</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007661843513957546</v>
+        <v>0.007661843513957541</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007497477931421371</v>
+        <v>0.007497477931421381</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007661705338640645</v>
+        <v>0.007661705338640658</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007492694051283773</v>
+        <v>0.007492694051283783</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007492694051283773</v>
+        <v>0.007492694051283783</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00763715379474851</v>
+        <v>0.007637153794748516</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007661843513957546</v>
+        <v>0.007661843513957541</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007497477931421371</v>
+        <v>0.007497477931421381</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007661843513957546</v>
+        <v>0.007661843513957541</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007661843513957546</v>
+        <v>0.007661843513957541</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007661843513957546</v>
+        <v>0.007661843513957541</v>
       </c>
     </row>
     <row r="6">
@@ -5031,25 +5031,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01566292155158719</v>
+        <v>0.0156629215515872</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02383019208818147</v>
+        <v>0.02383019208820953</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02572551973840937</v>
+        <v>0.02572551973840935</v>
       </c>
       <c r="E6" t="n">
         <v>0.02155107139117203</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01575997235062027</v>
+        <v>0.01575997235062026</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02397263684604432</v>
+        <v>0.02397263684604433</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02399732656525266</v>
+        <v>0.02399732656525265</v>
       </c>
       <c r="I6" t="n">
         <v>0.02383296098271719</v>
@@ -5061,7 +5061,7 @@
         <v>0.01550810569960823</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03270330951326954</v>
+        <v>0.03270330951326953</v>
       </c>
     </row>
     <row r="7">
@@ -5074,31 +5074,31 @@
         <v>0.01879896543215796</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02312946429967272</v>
+        <v>0.02312946429967274</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02329383371807995</v>
+        <v>0.02329383371807998</v>
       </c>
       <c r="E7" t="n">
         <v>0.02831644134345024</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02312946054558778</v>
+        <v>0.02312946054558781</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02326914016299984</v>
+        <v>0.02326914016299987</v>
       </c>
       <c r="H7" t="n">
         <v>0.02329382988220889</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02312946429967272</v>
+        <v>0.02312946429967274</v>
       </c>
       <c r="J7" t="n">
         <v>0.02329382988220889</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02068948938050702</v>
+        <v>0.02068948938050704</v>
       </c>
       <c r="L7" t="n">
         <v>0.02329382988220889</v>
@@ -5111,13 +5111,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00732286462173729</v>
+        <v>0.007322864621737297</v>
       </c>
       <c r="C8" t="n">
         <v>0.004726023062654862</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004299481204293898</v>
+        <v>0.004299481204293913</v>
       </c>
       <c r="E8" t="n">
         <v>0.004726023062654862</v>
@@ -5126,22 +5126,22 @@
         <v>0.004726023062654862</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005831367330374059</v>
+        <v>0.005831367330374048</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005691895508352715</v>
+        <v>0.005691895508352732</v>
       </c>
       <c r="I8" t="n">
         <v>0.004726023062654862</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006081963288904435</v>
+        <v>0.006081963288904445</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008411120575777</v>
+        <v>0.008411120575777019</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005987889051848053</v>
+        <v>0.005987889051848066</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008991642024241856</v>
+        <v>0.008991642024241851</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005265952404507299</v>
+        <v>0.005265952404507298</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007760399728689408</v>
+        <v>0.007760399728689417</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005265952404507299</v>
+        <v>0.005265952404507298</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005265952404507299</v>
+        <v>0.005265952404507298</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008367572607688837</v>
+        <v>0.008367572607688839</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008331764293233885</v>
+        <v>0.00833176429323389</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005265952404507299</v>
+        <v>0.005265952404507298</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008487887393052233</v>
+        <v>0.008487887393052247</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009434988285585822</v>
+        <v>0.009434988285585829</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008451226165008683</v>
+        <v>0.004885104527802984</v>
       </c>
     </row>
   </sheetData>
@@ -5270,34 +5270,34 @@
         <v>0.1049430685742179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06766194198148108</v>
+        <v>0.06766194198148101</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2358628664672263</v>
+        <v>0.2358628664672273</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06766194198148108</v>
+        <v>0.06766194198148101</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06766194198148108</v>
+        <v>0.06766194198148101</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1844427034826804</v>
+        <v>0.1844427034826812</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2028644527964765</v>
+        <v>0.2028644527964759</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06766194198148108</v>
+        <v>0.06766194198148101</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1409540307219801</v>
+        <v>0.1409540307219803</v>
       </c>
       <c r="K2" t="n">
         <v>0.08413267438081082</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2391211046126758</v>
+        <v>0.2391211046126759</v>
       </c>
     </row>
     <row r="3">
@@ -5310,34 +5310,34 @@
         <v>0.003539714169772108</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003178985245783679</v>
+        <v>0.003178985245783681</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003539714169772108</v>
+        <v>0.003539714169772106</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003234562344303572</v>
+        <v>0.003234562344303571</v>
       </c>
       <c r="F3" t="n">
         <v>0.003234562344303572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003516993835112833</v>
+        <v>0.003516993835112846</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003539714169772108</v>
+        <v>0.003539714169772106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003388137973469606</v>
+        <v>0.003388137973469608</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003539714169772108</v>
+        <v>0.003539714169772106</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003539714169772108</v>
+        <v>0.003539714169772106</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003539714169772108</v>
+        <v>0.003539714169772106</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01005081775641375</v>
+        <v>0.005268293812914962</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004912532531765322</v>
+        <v>0.004912532531765321</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005472242899997957</v>
+        <v>0.005472242899997735</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004774998643654481</v>
+        <v>0.004774998643654482</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005097255581573016</v>
+        <v>0.00509725558157303</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01002809742175449</v>
+        <v>0.005245573478255682</v>
       </c>
       <c r="H4" t="n">
         <v>0.01016857426492378</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009899241560111264</v>
+        <v>0.009899241560111257</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01008554451445164</v>
+        <v>0.005432950410411666</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005165330721408136</v>
+        <v>0.005165330721408149</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00564935953461294</v>
+        <v>0.005649359534612936</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007263848247137993</v>
+        <v>0.007263848247138021</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007112272050835501</v>
+        <v>0.007112272050835504</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00726372003973907</v>
+        <v>0.007263720039739076</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007105748190588059</v>
+        <v>0.007105748190588063</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007105748190588059</v>
+        <v>0.007105748190588063</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007241127912478722</v>
+        <v>0.007241127912478723</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007263848247137995</v>
+        <v>0.007263848247138019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007112272050835501</v>
+        <v>0.007112272050835504</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007263848247137995</v>
+        <v>0.007263848247138019</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007263848247137995</v>
+        <v>0.007263848247138019</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007263848247137995</v>
+        <v>0.007263848247138019</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01463319913106683</v>
+        <v>0.01463319913106686</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02212465762319039</v>
+        <v>0.02212465762319044</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02386659762887013</v>
+        <v>0.02386659762887017</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02003356302341979</v>
+        <v>0.02003356302341983</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01472022522297503</v>
+        <v>0.01472022522297506</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02225809438280903</v>
+        <v>0.02225809438280905</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02228081471746818</v>
+        <v>0.02228081471746822</v>
       </c>
       <c r="I6" t="n">
         <v>0.02212923852116583</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02228231769275341</v>
+        <v>0.02228231769275346</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0144911407452901</v>
+        <v>0.01449114074529013</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03026938868039045</v>
+        <v>0.03026938868039052</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01669726572208793</v>
+        <v>0.01669726572208795</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02044516606832145</v>
+        <v>0.02044516606832149</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02059674570514727</v>
+        <v>0.02059674570514729</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02494507863180431</v>
+        <v>0.02494507863180435</v>
       </c>
       <c r="F7" t="n">
-        <v>0.020445163032717</v>
+        <v>0.02044516303271704</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02057402192996468</v>
+        <v>0.02057402192996471</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02059674226462394</v>
+        <v>0.020596742264624</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02044516606832145</v>
+        <v>0.02044516606832149</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02059674226462394</v>
+        <v>0.020596742264624</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01568660435176058</v>
+        <v>0.01833737168852324</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02059674226462394</v>
+        <v>0.020596742264624</v>
       </c>
     </row>
     <row r="8">
@@ -5510,34 +5510,34 @@
         <v>0.00795014344517341</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004249156280351909</v>
+        <v>0.004249156280351913</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004624197785104221</v>
+        <v>0.004624197785104198</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004249156280351909</v>
+        <v>0.004249156280351913</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004249156280351909</v>
+        <v>0.004249156280351913</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006021672242010144</v>
+        <v>0.006021672242010131</v>
       </c>
       <c r="H8" t="n">
-        <v>0.006124088506774305</v>
+        <v>0.006124088506774317</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004249156280351909</v>
+        <v>0.004249156280351913</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007284927984042932</v>
+        <v>0.007284927984042939</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008381683408955169</v>
+        <v>0.00838168340895518</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005227016244638773</v>
+        <v>0.00522701624463877</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009219898886012831</v>
+        <v>0.009219898886012838</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005069710299990759</v>
+        <v>0.005069710299990762</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007865415047581226</v>
+        <v>0.007865415047581217</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005069710299990759</v>
+        <v>0.005069710299990762</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005069710299990759</v>
+        <v>0.005069710299990762</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008420961889288894</v>
+        <v>0.00842096188928889</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008480117815001326</v>
+        <v>0.008480117815001329</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005069710299990759</v>
+        <v>0.005069710299990762</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008950140552259978</v>
+        <v>0.008950140552259981</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009395767968513711</v>
+        <v>0.009395767968513727</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008114630546548991</v>
+        <v>0.005180764545433817</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08776368811570233</v>
+        <v>0.08776368811570272</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09756063451059105</v>
+        <v>0.09756063451059127</v>
       </c>
       <c r="D2" t="n">
-        <v>0.192414020216127</v>
+        <v>0.1924140202161272</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09756063451059105</v>
+        <v>0.09756063451059127</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09756063451059105</v>
+        <v>0.09756063451059127</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1574808400970181</v>
+        <v>0.1574808400970188</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1862555838382432</v>
+        <v>0.1862555838382431</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09756063451059105</v>
+        <v>0.09756063451059127</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09753531858912873</v>
+        <v>0.09753531858912884</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0715503870449315</v>
+        <v>0.07155038704493133</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5217264020533671</v>
+        <v>0.1626555975894998</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003599396281762028</v>
+        <v>0.003599396281762079</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00330703165618767</v>
+        <v>0.003307031656187676</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003599396281762028</v>
+        <v>0.003599396281762078</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003359604503387268</v>
+        <v>0.003359604503387267</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003359604503387264</v>
+        <v>0.003359604503387265</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003579824434736064</v>
+        <v>0.003579824434736068</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003599396281762028</v>
+        <v>0.003599396281762078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003468203790704676</v>
+        <v>0.003468203790704683</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003599396281762028</v>
+        <v>0.003599396281762078</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003599396281762028</v>
+        <v>0.003599396281762078</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003599396281762028</v>
+        <v>0.003599396281762078</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005339820376747732</v>
+        <v>0.005339820376747765</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005108324348298458</v>
+        <v>0.005108324348298509</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009975629492061348</v>
+        <v>0.005485697223340827</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004968955643044739</v>
+        <v>0.004968955643044747</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005215872255264566</v>
+        <v>0.005215872255264563</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005320248529721776</v>
+        <v>0.009912719000164142</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01005211065707601</v>
+        <v>0.01005211065707606</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009801098356132704</v>
+        <v>0.005208627885690391</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005495131403949905</v>
+        <v>0.009961181850405463</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005246173330510314</v>
+        <v>0.005246173330510323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005481077024096153</v>
+        <v>0.005481077024096164</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007257507230589356</v>
+        <v>0.007257507230589378</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007126314739531989</v>
+        <v>0.007126314739532</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007257376852313775</v>
+        <v>0.007257376852313793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007119303694337371</v>
+        <v>0.007119303694337373</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007119303694337371</v>
+        <v>0.007119303694337373</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007237935383563378</v>
+        <v>0.007237935383563389</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00725750723058935</v>
+        <v>0.007257507230589372</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007126314739531989</v>
+        <v>0.007126314739532</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00725750723058935</v>
+        <v>0.007257507230589372</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00725750723058935</v>
+        <v>0.007257507230589372</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00725750723058935</v>
+        <v>0.007257507230589372</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01452718238871773</v>
+        <v>0.01452718238871777</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02191484442898824</v>
+        <v>0.02191484442898829</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02361123893116535</v>
+        <v>0.02361123893116539</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01985762932591801</v>
+        <v>0.01985762932591806</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01463038196363285</v>
+        <v>0.01463038196363289</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02203153279180143</v>
+        <v>0.02203153279180148</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02205110463882788</v>
+        <v>0.02205110463882796</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02191991214777004</v>
+        <v>0.02191991214777008</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02205258330488883</v>
+        <v>0.02205258330488889</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01438742167016044</v>
+        <v>0.01438742167016049</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02991047056898453</v>
+        <v>0.0299104705689846</v>
       </c>
     </row>
     <row r="7">
@@ -5863,28 +5863,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01576276292081625</v>
+        <v>0.01576276292081628</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01924808792156908</v>
+        <v>0.01924808792156912</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01937928291366226</v>
+        <v>0.01937928291366228</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02342147124305042</v>
+        <v>0.02342147124305044</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01924808516765407</v>
+        <v>0.01924808516765413</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01935970856560049</v>
+        <v>0.01935970856560046</v>
       </c>
       <c r="H7" t="n">
         <v>0.01937928041262644</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01924808792156908</v>
+        <v>0.01924808792156912</v>
       </c>
       <c r="J7" t="n">
         <v>0.01937928041262644</v>
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008136190966557396</v>
+        <v>0.008136190966557403</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003271926246964272</v>
+        <v>0.003271926246964267</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00537693417707246</v>
+        <v>0.00537693417707247</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003271926246964272</v>
+        <v>0.003271926246964267</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003271926246964272</v>
+        <v>0.003271926246964267</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006420527866448027</v>
+        <v>0.006420527866448041</v>
       </c>
       <c r="H8" t="n">
-        <v>0.006136701345871664</v>
+        <v>0.006136701345871672</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003271926246964272</v>
+        <v>0.003271926246964267</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008112966522508452</v>
+        <v>0.008112966522508463</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008444106010709374</v>
+        <v>0.008444106010709386</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0007414050132747006</v>
+        <v>-0.0007414050132747219</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009187816330979629</v>
+        <v>0.009187816330979634</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004580021250846747</v>
+        <v>0.004580021250846755</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008064116346676399</v>
+        <v>0.008064116346676404</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004580021250846747</v>
+        <v>0.004580021250846755</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004580021250846747</v>
+        <v>0.004580021250846755</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008481600938192</v>
+        <v>0.008481600938192011</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008377211110522906</v>
+        <v>0.00837721111052292</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004580021250846747</v>
+        <v>0.004580021250846755</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009179149806945437</v>
+        <v>0.009179149806945447</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009313320602993174</v>
+        <v>0.00931332060299318</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00558030859947344</v>
+        <v>0.005580308599473447</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03276133159311452</v>
+        <v>0.03276133159311482</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02790546019177457</v>
+        <v>0.02790546019177458</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07935207103928546</v>
+        <v>0.07935207103928549</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02790546019177457</v>
+        <v>0.02790546019177458</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02790546019177457</v>
+        <v>0.02790546019177458</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06970936614136561</v>
+        <v>0.06970936614136553</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08308123159615222</v>
+        <v>0.08308123159615224</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02790546019177457</v>
+        <v>0.02790546019177458</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09412969759987087</v>
+        <v>0.09412969759987096</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04902086187525919</v>
+        <v>0.04902086187525933</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6271645655508225</v>
+        <v>0.6271645655508229</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003178701277571714</v>
+        <v>0.003178701277571728</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002848588281451593</v>
+        <v>0.002848588281451587</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003178701277571714</v>
+        <v>0.003178701277571728</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002902308631379996</v>
+        <v>0.002902308631379984</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002902308631379995</v>
+        <v>0.002902308631379986</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003157916680599008</v>
+        <v>0.00315791668059901</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003178701277571714</v>
+        <v>0.003178701277571728</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00303919397243072</v>
+        <v>0.003039193972430729</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003178701277571714</v>
+        <v>0.003178701277571728</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003178701277571714</v>
+        <v>0.003178701277571728</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003178701277571714</v>
+        <v>0.003178701277571728</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00463765336796298</v>
+        <v>0.009050313066533663</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004382652059430114</v>
+        <v>0.004382652059430125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009091870125213107</v>
+        <v>0.009091870125213109</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004255068100254933</v>
+        <v>0.004255068100254939</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004481507899805895</v>
+        <v>0.00448150789980589</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004616868770990269</v>
+        <v>0.009029528469560962</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009168636410090142</v>
+        <v>0.004646831018279519</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004498146062821992</v>
+        <v>0.008910805761392665</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009079934774326904</v>
+        <v>0.009079934774326906</v>
       </c>
       <c r="K4" t="n">
         <v>0.00461406461662607</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004887604005420106</v>
+        <v>0.00488760400542011</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006660103686643911</v>
+        <v>0.00666010368664391</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00652059638150292</v>
+        <v>0.006520596381502908</v>
       </c>
       <c r="D5" t="n">
         <v>0.006659973662169466</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00651460101877254</v>
+        <v>0.006514601018772535</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00651460101877254</v>
+        <v>0.006514601018772535</v>
       </c>
       <c r="G5" t="n">
         <v>0.0066393190896712</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006660103686643911</v>
+        <v>0.00666010368664391</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00652059638150292</v>
+        <v>0.006520596381502908</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006660103686643911</v>
+        <v>0.00666010368664391</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006660103686643911</v>
+        <v>0.00666010368664391</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006660103686643911</v>
+        <v>0.00666010368664391</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01414525098244918</v>
+        <v>0.01414525098244919</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02150824407308385</v>
+        <v>0.02150824407308388</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02320839337117285</v>
+        <v>0.02320839337117289</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01945566315214512</v>
+        <v>0.01945566315214514</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01424019234682474</v>
+        <v>0.01424019234682472</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02163106636707204</v>
+        <v>0.02163106636707205</v>
       </c>
       <c r="H6" t="n">
         <v>0.02165185096404455</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02151234365890376</v>
+        <v>0.02151234365890379</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02165332622598235</v>
+        <v>0.02165332622598232</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01400581203390165</v>
+        <v>0.01400581203390163</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0294931223364611</v>
+        <v>0.02949312233646115</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01498851350541782</v>
+        <v>0.01498851350541784</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01834948789947868</v>
+        <v>0.0183494878994787</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01848899638218161</v>
+        <v>0.01848899638218162</v>
       </c>
       <c r="E7" t="n">
         <v>0.02238896790243691</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01834948572331048</v>
+        <v>0.01834948572331049</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01846821060764698</v>
+        <v>0.01846821060764699</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01848899520461968</v>
+        <v>0.0184889952046197</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01834948789947868</v>
+        <v>0.0183494878994787</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01848899520461968</v>
+        <v>0.0184889952046197</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01646080285592762</v>
+        <v>0.01646080285592763</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01848899520461968</v>
+        <v>0.0184889952046197</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009280129089372239</v>
+        <v>0.009280129089372233</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004893688963477475</v>
+        <v>0.004893688963477473</v>
       </c>
       <c r="D8" t="n">
         <v>0.008071056610768785</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004893688963477475</v>
+        <v>0.004893688963477473</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004893688963477475</v>
+        <v>0.004893688963477473</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008389020455942106</v>
+        <v>0.008389020455942111</v>
       </c>
       <c r="H8" t="n">
         <v>0.008200911512743658</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004893688963477475</v>
+        <v>0.004893688963477473</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007996036209368852</v>
+        <v>0.007996036209368857</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008868038087464033</v>
+        <v>0.008868038087464031</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007947591564693941</v>
+        <v>-0.002811561197319163</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009462555040397332</v>
+        <v>0.009462555040397339</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005073561365780416</v>
+        <v>0.00507356136578042</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008970155115494441</v>
+        <v>0.008970155115494439</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005073561365780418</v>
+        <v>0.00507356136578042</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005073561365780418</v>
+        <v>0.00507356136578042</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009093214246023152</v>
+        <v>0.009093214246023164</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009024544877753161</v>
+        <v>0.009024544877753159</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005073561365780418</v>
+        <v>0.00507356136578042</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00894026480569652</v>
+        <v>0.008940264805696516</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009294765713085795</v>
+        <v>0.009294765713085792</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004547287843635997</v>
+        <v>0.00454728784363599</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02175975174209291</v>
+        <v>0.02175975174209293</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0288184679108375</v>
+        <v>0.02881846791083752</v>
       </c>
       <c r="D2" t="n">
         <v>0.02508978662580441</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0288184679108375</v>
+        <v>0.02881846791083752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0288184679108375</v>
+        <v>0.02881846791083752</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03264787394296472</v>
+        <v>0.03264787394296526</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02338128531681549</v>
+        <v>0.0233812853168155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0288184679108375</v>
+        <v>0.02881846791083752</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04804716679327257</v>
+        <v>0.04804716679327266</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03469047586543835</v>
+        <v>0.03469047586543834</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03450736559124172</v>
+        <v>0.03450736559124173</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003023121666215111</v>
+        <v>0.003023121666215105</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002769534828303366</v>
+        <v>0.002769534828303367</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003023121666215111</v>
+        <v>0.003023121666215105</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00281403102577584</v>
+        <v>0.002814031025775841</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002814031025775844</v>
+        <v>0.002814031025775845</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00300467539259807</v>
+        <v>0.00300467539259808</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003023121666215111</v>
+        <v>0.003023121666215105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002898736496983734</v>
+        <v>0.002898736496983737</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003023121666215111</v>
+        <v>0.003023121666215105</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003023121666215111</v>
+        <v>0.003023121666215105</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003023121666215111</v>
+        <v>0.003023121666215105</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008159205874820179</v>
+        <v>0.008159205874820191</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004177804443473755</v>
+        <v>0.004177804443473761</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004337223349218465</v>
+        <v>0.004337235939198951</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004059032565156756</v>
+        <v>0.004059032565156761</v>
       </c>
       <c r="F4" t="n">
         <v>0.004219734434578771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004331723322771051</v>
+        <v>0.00814075960120317</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004339230064632065</v>
+        <v>0.008233008210039618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004225784427156704</v>
+        <v>0.008034820705588822</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008166487083746555</v>
+        <v>0.004465853465612334</v>
       </c>
       <c r="K4" t="n">
         <v>0.004358017916205682</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004569693519145106</v>
+        <v>0.004569693519145109</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006094315009200282</v>
+        <v>0.006094315009200281</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005969929839968909</v>
+        <v>0.005969929839968912</v>
       </c>
       <c r="D5" t="n">
         <v>0.006094192749478223</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005964922023470441</v>
+        <v>0.005964922023470447</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005964922023470441</v>
+        <v>0.005964922023470447</v>
       </c>
       <c r="G5" t="n">
         <v>0.006075868735583255</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006094315009200282</v>
+        <v>0.006094315009200281</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005969929839968909</v>
+        <v>0.005969929839968912</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006094315009200282</v>
+        <v>0.006094315009200281</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006094315009200282</v>
+        <v>0.006094315009200281</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006094315009200282</v>
+        <v>0.006094315009200281</v>
       </c>
     </row>
     <row r="6">
@@ -6618,13 +6618,13 @@
         <v>0.01287086162323128</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01946142787871204</v>
+        <v>0.01946142787871202</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02098221092601404</v>
+        <v>0.02098221092601406</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01762436726679435</v>
+        <v>0.01762436726679434</v>
       </c>
       <c r="F6" t="n">
         <v>0.01295652082659204</v>
@@ -6633,19 +6633,19 @@
         <v>0.01957068721552067</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0195891334891369</v>
+        <v>0.01958913348913693</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01946474831990636</v>
+        <v>0.01946474831990635</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01959045382222862</v>
+        <v>0.01959045382222864</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01274606627414211</v>
+        <v>0.0127460662741421</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02660693022598952</v>
+        <v>0.02660693022598955</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01272084175929255</v>
+        <v>0.01272084175929256</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01547911827656925</v>
+        <v>0.01547911827656926</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0156035047327065</v>
+        <v>0.01560350473270653</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0188056491125085</v>
+        <v>0.01880564911250854</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01547911764350882</v>
+        <v>0.01547911764350883</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01558505717218359</v>
+        <v>0.01558505717218362</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01560350344580061</v>
+        <v>0.01560350344580064</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01547911827656925</v>
+        <v>0.01547911827656926</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01560350344580061</v>
+        <v>0.01560350344580064</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01386551529613092</v>
+        <v>0.01393327848481938</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01560350344580061</v>
+        <v>0.01560350344580064</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00934379572826805</v>
+        <v>0.009343795728268057</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004683470825252689</v>
+        <v>0.004683470825252691</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009251636784808949</v>
+        <v>0.009251636784808951</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004683470825252689</v>
+        <v>0.004683470825252691</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004683470825252689</v>
+        <v>0.004683470825252691</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00905643662012951</v>
+        <v>0.009056436620129511</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009356181777878048</v>
+        <v>0.009356181777878055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004683470825252689</v>
+        <v>0.004683470825252691</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008712995601732797</v>
+        <v>0.008712995601732798</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008987636610891395</v>
+        <v>0.008987636610891398</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009536123712041987</v>
+        <v>0.009080593260716965</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009392829758784379</v>
+        <v>0.00939282975878439</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00491398342091572</v>
+        <v>0.004913983420915721</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009355305931474106</v>
+        <v>0.009355305931474111</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00491398342091572</v>
+        <v>0.004913983420915721</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00491398342091572</v>
+        <v>0.004913983420915721</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009273310504310872</v>
+        <v>0.009273310504310879</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009398194296842598</v>
+        <v>0.009398194296842596</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00491398342091572</v>
+        <v>0.004913983420915721</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009136285286219615</v>
+        <v>0.009136285286219624</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009247806112359858</v>
+        <v>0.009247806112359862</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009471287334346741</v>
+        <v>0.009286091152965921</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.028877016352293</v>
+        <v>0.02887701635229297</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0329835475231556</v>
+        <v>0.03298354752315549</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02206612185215431</v>
+        <v>0.02206612185215428</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0329835475231556</v>
+        <v>0.03298354752315549</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0329835475231556</v>
+        <v>0.03298354752315549</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03138785712446859</v>
+        <v>0.03138785712446839</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02290286623630395</v>
+        <v>0.0229028662363039</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0329835475231556</v>
+        <v>0.03298354752315549</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04243467535427994</v>
+        <v>0.04243467535427985</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03102770929193007</v>
+        <v>0.03102770929192999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02129708797322414</v>
+        <v>0.03258869011403042</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003023365350841571</v>
+        <v>0.003023365350841558</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002794379493100903</v>
+        <v>0.002794379493100899</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003023365350841572</v>
+        <v>0.003023365350841559</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002837442766727402</v>
+        <v>0.002837442766727401</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002837442766727399</v>
+        <v>0.002837442766727401</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003006138379415602</v>
+        <v>0.003006138379415592</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003023365350841571</v>
+        <v>0.003023365350841559</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002907047065125854</v>
+        <v>0.002907047065125843</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003023365350841571</v>
+        <v>0.003023365350841558</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003023365350841571</v>
+        <v>0.003023365350841559</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003023365350841571</v>
+        <v>0.003023365350841559</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00436794530793416</v>
+        <v>0.004367945307934181</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004212955830051986</v>
+        <v>0.004212955830051952</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004339076602679372</v>
+        <v>0.004339076602679358</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004093408962331635</v>
+        <v>0.004093408962331633</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004246300659858501</v>
+        <v>0.004246300659858494</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008091295792636323</v>
+        <v>0.004350718336508216</v>
       </c>
       <c r="H4" t="n">
         <v>0.008165132582706626</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004251627022218497</v>
+        <v>0.004251627022218468</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008100587531608144</v>
+        <v>0.004478872332340991</v>
       </c>
       <c r="K4" t="n">
         <v>0.004369891743021787</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004361185220375674</v>
+        <v>0.004361185220375669</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006080838358402954</v>
+        <v>0.00608083835840295</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005964520072687235</v>
+        <v>0.005964520072687227</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006080715094619043</v>
+        <v>0.006080715094619035</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005959467004290406</v>
+        <v>0.005959467004290401</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005959467004290406</v>
+        <v>0.005959467004290401</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006063611386976984</v>
+        <v>0.006063611386976977</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006080838358402954</v>
+        <v>0.00608083835840295</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005964520072687235</v>
+        <v>0.005964520072687227</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006080838358402954</v>
+        <v>0.00608083835840295</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006080838358402954</v>
+        <v>0.00608083835840295</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006080838358402954</v>
+        <v>0.00608083835840295</v>
       </c>
     </row>
     <row r="6">
@@ -7011,13 +7011,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01283922925504522</v>
+        <v>0.01283922925504521</v>
       </c>
       <c r="C6" t="n">
         <v>0.0194125415625342</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02092006317633737</v>
+        <v>0.02092006317633734</v>
       </c>
       <c r="E6" t="n">
         <v>0.01758239733249911</v>
@@ -7029,19 +7029,19 @@
         <v>0.01951499960871461</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01953222658013944</v>
+        <v>0.01953222658013945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01941590829442489</v>
+        <v>0.01941590829442487</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01953354194613476</v>
+        <v>0.01953354194613474</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01271490339352046</v>
+        <v>0.01271490339352045</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02652362194576379</v>
+        <v>0.02652362194576378</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01230375487164658</v>
+        <v>0.01230375487164656</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01495249813803366</v>
+        <v>0.01495249813803363</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01506881760707011</v>
+        <v>0.01506881760707009</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01814332085972177</v>
+        <v>0.01814332085972175</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01495249753774577</v>
+        <v>0.01495249753774575</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01505158945232338</v>
+        <v>0.01505158945232337</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01506881642374939</v>
+        <v>0.01506881642374936</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01495249813803366</v>
+        <v>0.01495249813803363</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01506881642374939</v>
+        <v>0.01506881642374936</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0134017306565816</v>
+        <v>0.01340173065658157</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01506881642374939</v>
+        <v>0.01506881642374936</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00902368485925917</v>
+        <v>0.009023684859259166</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004358639537517712</v>
+        <v>0.004358639537517708</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009202541985922748</v>
+        <v>0.009202541985922744</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004358639537517712</v>
+        <v>0.004358639537517708</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004358639537517712</v>
+        <v>0.004358639537517708</v>
       </c>
       <c r="G8" t="n">
         <v>0.008965224474216375</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009234010039784498</v>
+        <v>0.009234010039784499</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004358639537517712</v>
+        <v>0.004358639537517708</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008727706261879156</v>
+        <v>0.00872770626187915</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008940812146955088</v>
+        <v>0.008940812146955081</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008996834090697774</v>
+        <v>0.009279337616429907</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009184111246338269</v>
+        <v>0.009184111246338268</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004654688787740715</v>
+        <v>0.00465468878774071</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009256968243133677</v>
+        <v>0.009256968243133672</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004654688787740715</v>
+        <v>0.00465468878774071</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004654688787740715</v>
+        <v>0.00465468878774071</v>
       </c>
       <c r="G9" t="n">
         <v>0.009158557930957328</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009270082505341703</v>
+        <v>0.009270082505341696</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004654688787740715</v>
+        <v>0.00465468878774071</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009063880054194954</v>
+        <v>0.009063880054194956</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009150390711969254</v>
+        <v>0.00915039071196925</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009288452294689329</v>
+        <v>0.009288452294689333</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08673351714236073</v>
+        <v>0.08673351714236067</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04493427183697208</v>
+        <v>0.04493427183697209</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2498071657845301</v>
+        <v>0.2498071657845298</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04493427183697208</v>
+        <v>0.04493427183697209</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04493427183697208</v>
+        <v>0.04493427183697209</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1744451155552434</v>
+        <v>0.1744451155552426</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2167937925810005</v>
+        <v>0.2167937925809999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04493427183697208</v>
+        <v>0.04493427183697209</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1312766443698885</v>
+        <v>0.1312766443698883</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07849757828280238</v>
+        <v>0.07849757828280216</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5887969925996278</v>
+        <v>0.1547671031255927</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003469570395138781</v>
+        <v>0.003469570395138774</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003063145670503266</v>
+        <v>0.003063145670503261</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003469570395138781</v>
+        <v>0.003469570395138774</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003123320544464001</v>
+        <v>0.003123320544463994</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003123320544464001</v>
+        <v>0.003123320544463981</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003445643437026879</v>
+        <v>0.003445643437026865</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003469570395138781</v>
+        <v>0.003469570395138774</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003310050060660299</v>
+        <v>0.003310050060660287</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003469570395138781</v>
+        <v>0.003469570395138774</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003469570395138781</v>
+        <v>0.003469570395138774</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003469570395138781</v>
+        <v>0.003469570395138774</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005164137049857663</v>
+        <v>0.00516413704985765</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004770614399906134</v>
+        <v>0.004770614399906092</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005438178960343188</v>
+        <v>0.005438178960343238</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004633093309874257</v>
+        <v>0.004633093309874259</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004981631955836566</v>
+        <v>0.004981631955836564</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01007079729882213</v>
+        <v>0.01007079729882212</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01025882317780081</v>
+        <v>0.01025882317780077</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009935203922455541</v>
+        <v>0.009935203922455539</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0101577481789387</v>
+        <v>0.01015774817893868</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005059746069090917</v>
+        <v>0.005059746069090945</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005395421609713245</v>
+        <v>0.005395421609713229</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007378049193504472</v>
+        <v>0.00737804919350446</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007218528859025991</v>
+        <v>0.007218528859025977</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007377913960162888</v>
+        <v>0.007377913960162873</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007212910401732199</v>
+        <v>0.007212910401732163</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007212910401732199</v>
+        <v>0.007212910401732163</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007354122235392569</v>
+        <v>0.007354122235392546</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007378049193504472</v>
+        <v>0.00737804919350446</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007218528859025991</v>
+        <v>0.007218528859025977</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007378049193504472</v>
+        <v>0.00737804919350446</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007378049193504472</v>
+        <v>0.00737804919350446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007378049193504472</v>
+        <v>0.00737804919350446</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01523682526626956</v>
+        <v>0.01523682526626951</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02317834474803046</v>
+        <v>0.02317834474800451</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02502203381098245</v>
+        <v>0.02502203381098234</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02096214891376341</v>
+        <v>0.02096214891376337</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01533093898583045</v>
+        <v>0.01533093898583039</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02331755375008848</v>
+        <v>0.02331755375008843</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02334148070819991</v>
+        <v>0.02334148070819987</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02318196037372192</v>
+        <v>0.0231819603737218</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02334307350491079</v>
+        <v>0.02334307350491077</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01508627713053113</v>
+        <v>0.01508627713053108</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03180747101726845</v>
+        <v>0.03180747101726832</v>
       </c>
     </row>
     <row r="7">
@@ -7447,34 +7447,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01788045444338766</v>
+        <v>0.0178804544433876</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02197962029006289</v>
+        <v>0.02197962029006285</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02213914362484603</v>
+        <v>0.02213914362484597</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02689405200793732</v>
+        <v>0.02689405200793729</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02197961665113833</v>
+        <v>0.02197961665113826</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0221152136664294</v>
+        <v>0.02211521366642932</v>
       </c>
       <c r="H7" t="n">
         <v>0.02213914062454134</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02197962029006289</v>
+        <v>0.02197962029006285</v>
       </c>
       <c r="J7" t="n">
         <v>0.02213914062454134</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01967164238794614</v>
+        <v>0.01967164238794609</v>
       </c>
       <c r="L7" t="n">
         <v>0.02213914062454134</v>
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008385640056386296</v>
+        <v>0.008385640056386291</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004787158701966239</v>
+        <v>0.00478715870196623</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00440471861158794</v>
+        <v>0.004404718611587912</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004787158701966239</v>
+        <v>0.00478715870196623</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004787158701966239</v>
+        <v>0.00478715870196623</v>
       </c>
       <c r="G8" t="n">
         <v>0.006366373878318764</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005648108116405623</v>
+        <v>0.005648108116405626</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004787158701966239</v>
+        <v>0.00478715870196623</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007585889599934997</v>
+        <v>0.007585889599934982</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008597647218544001</v>
+        <v>0.008597647218543995</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0011773487290259</v>
+        <v>-0.001177348729025905</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009325137085821045</v>
+        <v>0.009325137085821028</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005203402529135251</v>
+        <v>0.005203402529135235</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007703888309297884</v>
+        <v>0.007703888309297864</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005203402529135251</v>
+        <v>0.005203402529135235</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005203402529135251</v>
+        <v>0.005203402529135235</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008488101018339678</v>
+        <v>0.008488101018339675</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008214445047337289</v>
+        <v>0.008214445047337274</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005203402529135251</v>
+        <v>0.005203402529135235</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009000421417716615</v>
+        <v>0.009000421417716599</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009411573873373881</v>
+        <v>0.009411573873373876</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00543885083500222</v>
+        <v>0.008861727225021005</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0173821324475647</v>
+        <v>0.01738213244756468</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02597240465654515</v>
+        <v>0.02597240465654514</v>
       </c>
       <c r="D2" t="n">
         <v>0.179234482157992</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02597240465654515</v>
+        <v>0.02597240465654514</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02597240465654515</v>
+        <v>0.02597240465654514</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09029978882849982</v>
+        <v>0.09029978882849965</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04129318457170681</v>
+        <v>0.04129318457170687</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02597240465654515</v>
+        <v>0.02597240465654514</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06094671935578515</v>
+        <v>0.06094671935578518</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03063789967721392</v>
+        <v>0.03063789967721393</v>
       </c>
       <c r="L2" t="n">
-        <v>0.040184214210318</v>
+        <v>3.155388334040374</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003231725787291963</v>
+        <v>0.003231725787291969</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002913853845559084</v>
+        <v>0.002913853845559093</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003231725787291963</v>
+        <v>0.003231725787291969</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002963873796889757</v>
+        <v>0.002963873796889761</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002963873796889756</v>
+        <v>0.002963873796889761</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003210645873803328</v>
+        <v>0.003210645873803329</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003231725787291963</v>
+        <v>0.003231725787291969</v>
       </c>
       <c r="I3" t="n">
         <v>0.003090513624850904</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003231725787291963</v>
+        <v>0.003231725787291969</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003231725787291963</v>
+        <v>0.003231725787291969</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003231725787291963</v>
+        <v>0.003231725787291969</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009831812323990826</v>
+        <v>0.009831812323990842</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004381121570992107</v>
+        <v>0.004381121570992112</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004919519214363205</v>
+        <v>0.004919532393473841</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004258497191739548</v>
+        <v>0.00425849719173955</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004505958387913143</v>
+        <v>0.004505958387913142</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004641922930069595</v>
+        <v>0.009810732410502218</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00988647289590165</v>
+        <v>0.009886472895901624</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009690600161549759</v>
+        <v>0.009690600161549779</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004793058743410691</v>
+        <v>0.004793058743410701</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004589076103694159</v>
+        <v>0.004589076103694137</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005848444470608964</v>
+        <v>0.005848444470608963</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006556755070343841</v>
+        <v>0.006556755070343838</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00641554290790278</v>
+        <v>0.006415542907902766</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006556632788674472</v>
+        <v>0.006556632788674486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006409439289095808</v>
+        <v>0.00640943928909579</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006409439289095808</v>
+        <v>0.00640943928909579</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006535675156855216</v>
+        <v>0.0065356751568552</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006556755070343841</v>
+        <v>0.006556755070343838</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00641554290790278</v>
+        <v>0.006415542907902766</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006556755070343841</v>
+        <v>0.006556755070343838</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006556755070343841</v>
+        <v>0.006556755070343838</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006556755070343841</v>
+        <v>0.006556755070343838</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01366344583948113</v>
+        <v>0.01366344583948112</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02066423463790549</v>
+        <v>0.02066423463790547</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02229155977147342</v>
+        <v>0.02229155977147346</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0187102186451301</v>
+        <v>0.01871021864513007</v>
       </c>
       <c r="F6" t="n">
         <v>0.01374519172386587</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02078865107800061</v>
+        <v>0.02078865107800058</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02080973099148889</v>
+        <v>0.02080973099148887</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02066851882904819</v>
+        <v>0.02066851882904818</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02081113544123126</v>
+        <v>0.02081113544123122</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01353069992388202</v>
+        <v>0.013530699923882</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02827462339541171</v>
+        <v>0.02827462339541166</v>
       </c>
     </row>
     <row r="7">
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01427880256689409</v>
+        <v>0.0142788025668941</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01741821702332885</v>
+        <v>0.01741821702332887</v>
       </c>
       <c r="D7" t="n">
         <v>0.01755942862756329</v>
@@ -7858,22 +7858,22 @@
         <v>0.01741821247439629</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01753834927228129</v>
+        <v>0.01753834927228128</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0175594291857699</v>
+        <v>0.01755942918576991</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01741821702332885</v>
+        <v>0.01741821702332887</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0175594291857699</v>
+        <v>0.01755942918576991</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01342853482750031</v>
+        <v>0.01565862100399884</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0175594291857699</v>
+        <v>0.01755942918576991</v>
       </c>
     </row>
     <row r="8">
@@ -7886,34 +7886,34 @@
         <v>0.009715111909510693</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004948592334444261</v>
+        <v>0.00494859233444426</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005308837545693668</v>
+        <v>0.005308837545693654</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004948592334444261</v>
+        <v>0.00494859233444426</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004948592334444261</v>
+        <v>0.00494859233444426</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007826501931213255</v>
+        <v>0.007826501931213252</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009187010805302705</v>
+        <v>0.009187010805302709</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004948592334444261</v>
+        <v>0.00494859233444426</v>
       </c>
       <c r="J8" t="n">
         <v>0.008713920557772417</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009363064895512661</v>
+        <v>0.009363064895512653</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.05831798092190792</v>
+        <v>-0.05831798092190794</v>
       </c>
     </row>
     <row r="9">
@@ -7923,34 +7923,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00969153882427248</v>
+        <v>0.009691538824272476</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005122621060059619</v>
+        <v>0.005122621060059612</v>
       </c>
       <c r="D9" t="n">
         <v>0.00789701452090345</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005122621060059619</v>
+        <v>0.005122621060059612</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005122621060059619</v>
+        <v>0.005122621060059612</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008913273665309574</v>
+        <v>0.008913273665309567</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009477158747133436</v>
+        <v>0.009477158747133438</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005122621060059619</v>
+        <v>0.005122621060059612</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009284232256510505</v>
+        <v>0.009284232256510509</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009548183495905195</v>
+        <v>0.00954818349590519</v>
       </c>
       <c r="L9" t="n">
         <v>-0.01796619340823453</v>

--- a/Results/Hydrogen/hydrogen acidification results.xlsx
+++ b/Results/Hydrogen/hydrogen acidification results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1857340927966097</v>
+        <v>0.01065515359676686</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09701696200747925</v>
+        <v>0.006112089995221739</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3121296782093867</v>
+        <v>0.0107794020785928</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09701696200747925</v>
+        <v>0.006112089995221739</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09701696200747925</v>
+        <v>0.006112089995221739</v>
       </c>
       <c r="G2" t="n">
-        <v>0.248033510683973</v>
+        <v>0.01068266593733245</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4498802099559128</v>
+        <v>0.01087618841528905</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09701696200747925</v>
+        <v>0.006112089995221739</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2327693227070064</v>
+        <v>0.01068740521572487</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1267865409028706</v>
+        <v>0.01058968362075362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9928481639916348</v>
+        <v>0.01068394625354631</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003914306244165959</v>
+        <v>0.01063466723480794</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003578162453133327</v>
+        <v>0.006116740897946062</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003914306244165959</v>
+        <v>0.01063466723480794</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003645440212022916</v>
+        <v>0.006116740897946062</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003645440212022916</v>
+        <v>0.006116740897946062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003893578033175798</v>
+        <v>0.01060823448068747</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003914306244165959</v>
+        <v>0.01063466723480794</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003776331094216983</v>
+        <v>0.006116740897946062</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003914306244165959</v>
+        <v>0.01063466723480794</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003914306244165959</v>
+        <v>0.01063466723480794</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003914306244165959</v>
+        <v>0.01063466723480794</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006002747738987898</v>
+        <v>0.1857340927966099</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005621131586167556</v>
+        <v>0.09701696200747957</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006253692663250144</v>
+        <v>0.3121296782093867</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005456617870408661</v>
+        <v>0.09701696200747957</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005848174496503681</v>
+        <v>0.09701696200747957</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01171762250569443</v>
+        <v>0.2480335106839729</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01193158230737016</v>
+        <v>0.4498802099559128</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01160037556673561</v>
+        <v>0.09701696200747957</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01177008422520834</v>
+        <v>0.2327693227070063</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005882980368756914</v>
+        <v>0.1267865409028707</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006272075705435197</v>
+        <v>0.9928481639916373</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008481529061823232</v>
+        <v>0.003914306244165958</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008343553911874264</v>
+        <v>0.003578162453133331</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008481373679581921</v>
+        <v>0.003914306244165958</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008338972503004666</v>
+        <v>0.003645440212022915</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008338972503004666</v>
+        <v>0.003645440212022913</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008460800850833079</v>
+        <v>0.0038935780331758</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008481529061823232</v>
+        <v>0.003914306244165958</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008343553911874264</v>
+        <v>0.003776331094216978</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008481529061823232</v>
+        <v>0.003914306244165958</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008481529061823232</v>
+        <v>0.003914306244165958</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008481529061823232</v>
+        <v>0.003914306244165958</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01728627851729872</v>
+        <v>0.006002747738987901</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02638653445324726</v>
+        <v>0.005621131586167577</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02844298523747883</v>
+        <v>0.006253692663250149</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02385952968094731</v>
+        <v>0.005456617870408652</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01743857599249397</v>
+        <v>0.005848174496503688</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02650615702620014</v>
+        <v>0.01171762250569443</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02652688523718993</v>
+        <v>0.01193158230737017</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02638891008724136</v>
+        <v>0.0116003755667356</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02652870128071146</v>
+        <v>0.01177008422520835</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01711462950339104</v>
+        <v>0.005882980368756938</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03617947164262652</v>
+        <v>0.006272075705435196</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02264740886382465</v>
+        <v>0.008481529061823241</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02801408680434021</v>
+        <v>0.008343553911874258</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02815206362428433</v>
+        <v>0.008481373679581915</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03436633290144032</v>
+        <v>0.008338972503004671</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02801408011519041</v>
+        <v>0.008338972503004671</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02813133374329899</v>
+        <v>0.008460800850833082</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02815206195428917</v>
+        <v>0.008481529061823241</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02801408680434021</v>
+        <v>0.008343553911874258</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02815206195428916</v>
+        <v>0.008481529061823241</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0212207207034663</v>
+        <v>0.008481529061823241</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02815206195428917</v>
+        <v>0.008481529061823241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006748262312231656</v>
+        <v>0.01728627851729873</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004214783797620481</v>
+        <v>0.02638653445324728</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004147608422264312</v>
+        <v>0.02844298523747888</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004214783797620481</v>
+        <v>0.02385952968094732</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004214783797620481</v>
+        <v>0.01743857599249397</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005615900277369541</v>
+        <v>0.02650615702620016</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002278615155344393</v>
+        <v>0.02652688523718995</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004214783797620481</v>
+        <v>0.02638891008724139</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006108547361710685</v>
+        <v>0.02652870128071149</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008123322068307294</v>
+        <v>0.01711462950339103</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006214099283694661</v>
+        <v>0.03617947164262656</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02264740886382465</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02801408680434022</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02815206362428434</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03436633290144031</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02801408011519043</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02813133374329899</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02815206195428918</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02801408680434022</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02815206195428918</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02122072070346631</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02815206195428918</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.006748262312231661</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004214783797620483</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.00414760842226432</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.004214783797620483</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.004214783797620483</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005615900277369536</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.002278615155344403</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.004214783797620483</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.006108547361710693</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.008123322068307293</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.006214099283694678</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.008886826971757003</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.008886826971757007</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.005246693453395962</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>0.007827769645855624</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.005246693453395962</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.005246693453395962</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.008411137965197652</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.007074158089975171</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.008411137965197666</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.007074158089975178</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.005246693453395962</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.008628006249577406</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.009447013566813612</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.003127080960542495</v>
+      <c r="J11" t="n">
+        <v>0.008628006249577413</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.009447013566813619</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.003127080960542501</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01567948043014008</v>
+        <v>0.00943339527079436</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03039589348898138</v>
+        <v>0.004963451867403417</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02972091806296256</v>
+        <v>0.009450893843753395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03039589348898138</v>
+        <v>0.004963451867403417</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03039589348898138</v>
+        <v>0.004963451867403417</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03511499962506964</v>
+        <v>0.009452431909650389</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02888744275140725</v>
+        <v>0.009446614947898469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03039589348898138</v>
+        <v>0.004963451867403417</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03976421165000668</v>
+        <v>0.009460087539699756</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02945402794500926</v>
+        <v>0.009451523429596754</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02257381217065741</v>
+        <v>0.009441396173300092</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003035219710756911</v>
+        <v>0.00957817571639704</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002798293720050253</v>
+        <v>0.005018894688807628</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003035219710756911</v>
+        <v>0.00957817571639704</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002842412302599362</v>
+        <v>0.005018894688807628</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002842412302599358</v>
+        <v>0.005018894688807628</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003017760240580163</v>
+        <v>0.009573813451211593</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003035219710756911</v>
+        <v>0.00957817571639704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002917425899776541</v>
+        <v>0.005018894688807628</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003035219710756911</v>
+        <v>0.00957817571639704</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003035219710756911</v>
+        <v>0.00957817571639704</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003035219710756911</v>
+        <v>0.00957817571639704</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004373863918641688</v>
+        <v>0.01567948043014003</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004214929986536825</v>
+        <v>0.0303958934889814</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008141999116131844</v>
+        <v>0.02972091806296256</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004094901296630732</v>
+        <v>0.0303958934889814</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004255966777580431</v>
+        <v>0.0303958934889814</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008099162272055564</v>
+        <v>0.03511499962506976</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008216597585221403</v>
+        <v>0.02888744275140724</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004256070107661316</v>
+        <v>0.0303958934889814</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004491464895689109</v>
+        <v>0.03976421165000659</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004377765042779844</v>
+        <v>0.02945402794500927</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004374541506231509</v>
+        <v>0.02257381217065742</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006126251383387508</v>
+        <v>0.003035219710756905</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006008457572407119</v>
+        <v>0.002798293720050252</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006126128266375226</v>
+        <v>0.003035219710756905</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006003034691770658</v>
+        <v>0.002842412302599353</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006003034691770658</v>
+        <v>0.002842412302599352</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006108791913210752</v>
+        <v>0.003017760240580159</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006126251383387508</v>
+        <v>0.003035219710756905</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006008457572407119</v>
+        <v>0.002917425899776533</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006126251383387508</v>
+        <v>0.003035219710756905</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006126251383387508</v>
+        <v>0.003035219710756905</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006126251383387508</v>
+        <v>0.003035219710756905</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01291855669580205</v>
+        <v>0.004373863918641676</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01954247762445089</v>
+        <v>0.004214929986536802</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02106268942042393</v>
+        <v>0.008141999116131846</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01769803136190742</v>
+        <v>0.004094901296630746</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0130114208729529</v>
+        <v>0.004255966777580427</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01964652214984483</v>
+        <v>0.008099162272055526</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01966398162002188</v>
+        <v>0.008216597585221369</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0195461878090412</v>
+        <v>0.004256070107661314</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01966530728945393</v>
+        <v>0.004491464895689096</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01279325696471606</v>
+        <v>0.004377765042779837</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02671014199677083</v>
+        <v>0.004374541506231493</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01239168899590093</v>
+        <v>0.006126251383387492</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01506415616407565</v>
+        <v>0.006008457572407126</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01518195125234827</v>
+        <v>0.006126128266375209</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01828405845929875</v>
+        <v>0.006003034691770658</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01506415547105373</v>
+        <v>0.006003034691770658</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01516449050487927</v>
+        <v>0.006108791913210756</v>
       </c>
       <c r="H7" t="n">
-        <v>0.015181949975056</v>
+        <v>0.006126251383387492</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01506415616407565</v>
+        <v>0.006008457572407126</v>
       </c>
       <c r="J7" t="n">
-        <v>0.015181949975056</v>
+        <v>0.006126251383387492</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01356526234275723</v>
+        <v>0.006126251383387492</v>
       </c>
       <c r="L7" t="n">
-        <v>0.015181949975056</v>
+        <v>0.006126251383387492</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009388527262897814</v>
+        <v>0.01291855669580207</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004447795831448502</v>
+        <v>0.0195424776244509</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00902207013741365</v>
+        <v>0.02106268942042388</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004447795831448502</v>
+        <v>0.01769803136190741</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004447795831448502</v>
+        <v>0.01301142087295289</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008897115634265682</v>
+        <v>0.01964652214984478</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009120575280819629</v>
+        <v>0.01966398162002187</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004447795831448502</v>
+        <v>0.01954618780904118</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008835078673566317</v>
+        <v>0.01966530728945394</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009009201200431702</v>
+        <v>0.01279325696471603</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009278461369751656</v>
+        <v>0.02671014199677081</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01239168899590092</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01506415616407564</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01518195125234828</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01828405845929874</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01506415547105376</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01516449050487925</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.015181949975056</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01506415616407564</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.015181949975056</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01356526234275721</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.015181949975056</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.009388527262897826</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004447795831448502</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.009022070137413648</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.004447795831448502</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.004447795831448502</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.008897115634265698</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.009120575280819644</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.004447795831448502</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.008835078673566312</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.009009201200431718</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.009278461369751675</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.009347104620078449</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.004703600067320939</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.0091978640331126</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.004703600067320939</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.004703600067320939</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009144532246432014</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.009238405291424676</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.004703600067320939</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.009121976017102001</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.009192638211618333</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.009302510205977188</v>
+      <c r="B11" t="n">
+        <v>0.009347104620078459</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.004703600067320938</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.009197864033112608</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.004703600067320938</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.004703600067320938</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.009144532246432019</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.009238405291424688</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.004703600067320938</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.009121976017102009</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.009192638211618335</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.009302510205977204</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,321 +1463,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03380694518029961</v>
+        <v>0.02363982440525718</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1796038114713068</v>
+        <v>0.004599196225122664</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1726839442366329</v>
+        <v>0.006765327771243458</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05526593035883259</v>
+        <v>0.00610103560744801</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05526593035883259</v>
+        <v>0.00610103560744801</v>
       </c>
       <c r="G2" t="n">
-        <v>0.119573320914719</v>
+        <v>0.01027516100322491</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1328431577757918</v>
+        <v>0.006707063121421454</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05526593035883259</v>
+        <v>0.00610103560744801</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1981289972521833</v>
+        <v>0.0110882759790281</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05936767151374327</v>
+        <v>0.01514954523669188</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1936283805566678</v>
+        <v>0.005956503363615993</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00352562634409874</v>
+        <v>0.02398599697074049</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00336907627138252</v>
+        <v>0.004486618193215624</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003525626344098738</v>
+        <v>0.006690382888404965</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003291929898167041</v>
+        <v>0.006148216065395221</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003291929898167039</v>
+        <v>0.006148216065395221</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00350482695185081</v>
+        <v>0.01031890073800076</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003525626344098741</v>
+        <v>0.006690382888404965</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003386360955834096</v>
+        <v>0.006148216065395221</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003525626344098741</v>
+        <v>0.01106291504388456</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003525626344098738</v>
+        <v>0.01533514457722888</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003525626344098738</v>
+        <v>0.005870951929785257</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009828287873760907</v>
+        <v>0.03380694518029963</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005393701607407599</v>
+        <v>0.1796038114713069</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005451009025788044</v>
+        <v>0.1726839442366331</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004873849377653687</v>
+        <v>0.05526593035883255</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005142603731810338</v>
+        <v>0.05526593035883255</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005266325328204641</v>
+        <v>0.1195733209147194</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01003722146933664</v>
+        <v>0.1328431577757921</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005147859332187953</v>
+        <v>0.05526593035883255</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009855281323432975</v>
+        <v>0.1981289972521832</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005214709407349304</v>
+        <v>0.05936767151374332</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005329192701179531</v>
+        <v>0.1936283805566679</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007290632401697222</v>
+        <v>0.003525626344098734</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007292254210918637</v>
+        <v>0.003369076271382533</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007290513464460034</v>
+        <v>0.003525626344098734</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007150737664041037</v>
+        <v>0.003291929898167037</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007150737664041037</v>
+        <v>0.003291929898167039</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007269833009449263</v>
+        <v>0.00350482695185079</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007290632401697222</v>
+        <v>0.003525626344098734</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007151367013432585</v>
+        <v>0.003386360955834093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007290632401697222</v>
+        <v>0.003525626344098734</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007290632401697222</v>
+        <v>0.003525626344098734</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007290632401697222</v>
+        <v>0.003525626344098734</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01498275071342009</v>
+        <v>0.009828287873760918</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02287714872987531</v>
+        <v>0.005393701607407589</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02451082523577922</v>
+        <v>0.00545100902578805</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02057781586618873</v>
+        <v>0.00487384937765275</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01509333499588113</v>
+        <v>0.005142603731810348</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0228536340253017</v>
+        <v>0.005266325328204651</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02287443341755672</v>
+        <v>0.01003722146933664</v>
       </c>
       <c r="I6" t="n">
-        <v>0.022735168029285</v>
+        <v>0.005147859332187961</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0228759843589579</v>
+        <v>0.009855281323432972</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01483615865562233</v>
+        <v>0.005214709407349301</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0311179558934819</v>
+        <v>0.005329192701179537</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01646695537523476</v>
+        <v>0.007290632401697235</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02031392267203296</v>
+        <v>0.007292254210918638</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02031230267918097</v>
+        <v>0.007290513464460044</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0246104808409003</v>
+        <v>0.007150737664041045</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02017303272752701</v>
+        <v>0.007150737664041045</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02029150147056359</v>
+        <v>0.007269833009449263</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02031230086281154</v>
+        <v>0.007290632401697235</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0201730354745469</v>
+        <v>0.007151367013432585</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02031230086281154</v>
+        <v>0.007290632401697235</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01808429334943042</v>
+        <v>0.007290632401697235</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02031230086281154</v>
+        <v>0.007290632401697235</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02332096655863214</v>
+        <v>0.01498275071342006</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006448317613038142</v>
+        <v>0.02287714872987534</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002897751283397394</v>
+        <v>0.02451082523577919</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005077736034473469</v>
+        <v>0.02057781586618871</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005077736034473469</v>
+        <v>0.0150933349958811</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007829178191277288</v>
+        <v>0.02285363402530169</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004166554379894866</v>
+        <v>0.02287443341755668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005077736034473469</v>
+        <v>0.02273516802928503</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006907857879169933</v>
+        <v>0.02287598435895786</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01416655500659432</v>
+        <v>0.01483615865562233</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002184669129782993</v>
+        <v>0.03111795589348182</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0164669553752348</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02031392267203296</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02031230267918096</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02461048084090034</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02017303272752705</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0202915014705636</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02031230086281154</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02017303547454693</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02031230086281154</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01808429334943044</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02031230086281154</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.02332096655863216</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.000644831761303813</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.002897751283397397</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.005077736034473471</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005077736034473471</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.007829178191277273</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.004166554379894861</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.005077736034473471</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.006907857879169946</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01416655500659433</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.002184669129782994</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.02333723344842173</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.02333723344842172</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.002851171155555859</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.005039668304565219</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.005613963781961166</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.005613963781961166</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009142329310190746</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.005558713107085119</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.005613963781961166</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.009197711727701405</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01461783325797915</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.004279232942128711</v>
+      <c r="D11" t="n">
+        <v>0.005039668304565223</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005613963781961171</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005613963781961171</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.009142329310190749</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.005558713107085121</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005613963781961171</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.009197711727701409</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01461783325797914</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004279232942128709</v>
       </c>
     </row>
   </sheetData>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02368919567650017</v>
+        <v>0.02353867889074905</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1073403050958527</v>
+        <v>0.004237065111540248</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1159948583435174</v>
+        <v>0.006514749576087072</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03738099926706007</v>
+        <v>0.0059119895651633</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03738099926706007</v>
+        <v>0.0059119895651633</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07313977714534416</v>
+        <v>0.0100485091802578</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07644959280814323</v>
+        <v>0.006460203472366391</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03738099926706007</v>
+        <v>0.0059119895651633</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1182180631447172</v>
+        <v>0.01086019262299514</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02919021197172971</v>
+        <v>0.01488947615808055</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06412245224694857</v>
+        <v>0.00523761576324989</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0032971161726743</v>
+        <v>0.0238934049383058</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0031336565300157</v>
+        <v>0.004191811139713695</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003297116172674299</v>
+        <v>0.006492636822171114</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003204193080899493</v>
+        <v>0.005974028406307428</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003204193080899493</v>
+        <v>0.005974028406307428</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003277978928802489</v>
+        <v>0.0101353830458641</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003297116172674299</v>
+        <v>0.006492636822171114</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003168636060463988</v>
+        <v>0.005974028406307428</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0032971161726743</v>
+        <v>0.01091036045828765</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003297116172674299</v>
+        <v>0.01510335589173938</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003297116172674299</v>
+        <v>0.005265141912117972</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008916945434904242</v>
+        <v>0.02368919567650019</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00487338841500815</v>
+        <v>0.1073403050958528</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008959630890162957</v>
+        <v>0.1159948583435177</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00450351630547647</v>
+        <v>0.03738099926706003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004711983421112708</v>
+        <v>0.03738099926706003</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008897808191032428</v>
+        <v>0.07313977714534381</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009145660911213715</v>
+        <v>0.0764495928081431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004706317816410063</v>
+        <v>0.03738099926706003</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004993597722587919</v>
+        <v>0.118218063144717</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004779969338866885</v>
+        <v>0.02919021197172974</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004838102413252074</v>
+        <v>0.06412245224694864</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006695333304234797</v>
+        <v>0.003297116172674268</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006696852378657191</v>
+        <v>0.003133656530015698</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006695225390118373</v>
+        <v>0.003297116172674268</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006573858994226884</v>
+        <v>0.003204193080899486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006573858994226884</v>
+        <v>0.003204193080899481</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006676196060362981</v>
+        <v>0.003277978928802477</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006695333304234797</v>
+        <v>0.003297116172674268</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006566853192024481</v>
+        <v>0.003168636060463986</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006695333304234797</v>
+        <v>0.003297116172674268</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006695333304234797</v>
+        <v>0.003297116172674268</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006695333304234797</v>
+        <v>0.003297116172674268</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01387113624931974</v>
+        <v>0.008916945434904244</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02115309270871691</v>
+        <v>0.004873388415008202</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02265125312760553</v>
+        <v>0.008959630890162941</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01903332211470048</v>
+        <v>0.004503516305476477</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0139774167697322</v>
+        <v>0.004711983421112713</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02112418147485817</v>
+        <v>0.008897808191032414</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02114331871874852</v>
+        <v>0.009145660911213674</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02101483860651964</v>
+        <v>0.004706317816410064</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0211447479104683</v>
+        <v>0.004993597722587935</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01373605172643842</v>
+        <v>0.004779969338866877</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02873972139763888</v>
+        <v>0.004838102413252079</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01398223841119845</v>
+        <v>0.006695333304234791</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01717972504490617</v>
+        <v>0.0066968523786572</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01717820756702538</v>
+        <v>0.006695225390118371</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02073780407987722</v>
+        <v>0.006573858994226882</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01704972424259933</v>
+        <v>0.006573858994226882</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01715906872661197</v>
+        <v>0.006676196060362967</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01717820597048382</v>
+        <v>0.006695333304234791</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01704972585827349</v>
+        <v>0.006566853192024477</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01717820597048382</v>
+        <v>0.006695333304234791</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01532645048659987</v>
+        <v>0.006695333304234791</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01717820597048382</v>
+        <v>0.006695333304234791</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0234248882411819</v>
+        <v>0.01387113624931971</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001838559266967116</v>
+        <v>0.02115309270871684</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003859388111929238</v>
+        <v>0.02265125312760552</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005263840850978633</v>
+        <v>0.01903332211470047</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005263840850978633</v>
+        <v>0.01397741676973218</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008594531603599877</v>
+        <v>0.02112418147485813</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005030115355362423</v>
+        <v>0.02114331871874849</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005263840850978633</v>
+        <v>0.02101483860651964</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008362714528278314</v>
+        <v>0.02114474791046832</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01459056070986313</v>
+        <v>0.01373605172643842</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004093496182518857</v>
+        <v>0.02873972139763885</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01398223841119842</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01717972504490618</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01717820756702534</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02073780407987721</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0170497242425993</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01715906872661193</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01717820597048379</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01704972585827349</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01717820597048379</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01532645048659984</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01717820597048379</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0234248882411819</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001838559266967116</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.003859388111929213</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.005263840850978632</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005263840850978632</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.00859453160359989</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.005030115355362423</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.005263840850978632</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.008362714528278307</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01459056070986311</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.004093496182518852</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.02332550230048358</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.02332550230048357</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.003166328010071805</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.005316613021261283</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.005588851964255253</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.005588851964255253</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009347416863625394</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.005794751544189069</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.005588851964255253</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.009701005605975038</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01465615271614559</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0047045132224689</v>
+      <c r="D11" t="n">
+        <v>0.005316613021261273</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005588851964255243</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005588851964255243</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.009347416863625389</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.005794751544189066</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005588851964255243</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.009701005605975022</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01465615271614556</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004704513222468901</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,321 +2415,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01128357393799489</v>
+        <v>0.02343118544675124</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06922041094361399</v>
+        <v>0.003981852738591762</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07801406630083289</v>
+        <v>0.006279339430723258</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01636399357343529</v>
+        <v>0.005568905379546658</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01636399357343529</v>
+        <v>0.005568905379546658</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04433107378834505</v>
+        <v>0.009788876977258536</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05213122150124894</v>
+        <v>0.006243560023409796</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01636399357343529</v>
+        <v>0.005568905379546658</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05145926794690546</v>
+        <v>0.01008022142709858</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01675636976287083</v>
+        <v>0.0146895246616706</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02651524201052957</v>
+        <v>0.005039456101166392</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003146094322986228</v>
+        <v>0.02379918081702866</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002979088895688546</v>
+        <v>0.003977274684762697</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003146094322986229</v>
+        <v>0.006299100081991665</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003075395045564969</v>
+        <v>0.005650768462530736</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00307539504556497</v>
+        <v>0.005650768462530736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003131369330279371</v>
+        <v>0.009905513115482217</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003146094322986229</v>
+        <v>0.006299100081991665</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003046948433119685</v>
+        <v>0.005650768462530736</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003146094322986229</v>
+        <v>0.01019424870368307</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003146094322986229</v>
+        <v>0.01491556269298649</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003146094322986229</v>
+        <v>0.005103615771223363</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004565979397008225</v>
+        <v>0.01128357393799491</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004578778506466664</v>
+        <v>0.06922041094361411</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00464832922718732</v>
+        <v>0.07801406630083289</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004275369189447729</v>
+        <v>0.01636399357343529</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004469808412403201</v>
+        <v>0.01636399357343529</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008501192231451408</v>
+        <v>0.04433107378834486</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008735331760449347</v>
+        <v>0.05213122150124907</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008416771334291705</v>
+        <v>0.01636399357343529</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008529340452848458</v>
+        <v>0.05145926794690547</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004536692421361135</v>
+        <v>0.01675636976287084</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004560458473420871</v>
+        <v>0.02651524201052958</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006410172232372145</v>
+        <v>0.003146094322986235</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006411766577229056</v>
+        <v>0.002979088895688552</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006410063110149774</v>
+        <v>0.003146094322986235</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006319348111678115</v>
+        <v>0.00307539504556498</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006319348111678115</v>
+        <v>0.003075395045564982</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006395447239665294</v>
+        <v>0.003131369330279371</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006410172232372145</v>
+        <v>0.003146094322986235</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006311026342505598</v>
+        <v>0.003046948433119691</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006410172232372145</v>
+        <v>0.003146094322986235</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006410172232372145</v>
+        <v>0.003146094322986235</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006410172232372145</v>
+        <v>0.003146094322986235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01349486601666558</v>
+        <v>0.00456597939700824</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02061403201392828</v>
+        <v>0.004578778506466675</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02207685991460681</v>
+        <v>0.004648329227186752</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01856826553945301</v>
+        <v>0.004275369189447745</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01362606491262016</v>
+        <v>0.004469808412403219</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02058822699165264</v>
+        <v>0.008501192231451415</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02060295198437887</v>
+        <v>0.008735331760449374</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02050380609449293</v>
+        <v>0.008416771334291726</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02060434892633346</v>
+        <v>0.008529340452848483</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01336282967055601</v>
+        <v>0.004536692421361152</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02802794214560894</v>
+        <v>0.004560458473420884</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01266958758700119</v>
+        <v>0.006410172232372159</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01553676547996035</v>
+        <v>0.006411766577229069</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01553517235037789</v>
+        <v>0.006410063110149787</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01874284733740763</v>
+        <v>0.006319348111678135</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01543602391664841</v>
+        <v>0.006319348111678135</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01552044614239658</v>
+        <v>0.006395447239665307</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01553517113510345</v>
+        <v>0.006410172232372159</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01543602524523689</v>
+        <v>0.006311026342505612</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01553517113510345</v>
+        <v>0.006410172232372159</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01380747955580111</v>
+        <v>0.006410172232372159</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01553517113510345</v>
+        <v>0.006410172232372159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02362047751337477</v>
+        <v>0.01349486601666562</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002524932069377079</v>
+        <v>0.0206140320139283</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004588738238050573</v>
+        <v>0.02207685991460678</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005445081705694002</v>
+        <v>0.01856826553945303</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005445081705694002</v>
+        <v>0.01362606491262017</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009043296347317729</v>
+        <v>0.02058822699165264</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005356426361282855</v>
+        <v>0.02060295198437885</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005445081705694002</v>
+        <v>0.02050380609449295</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009189336001955832</v>
+        <v>0.02060434892633349</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01470106517822098</v>
+        <v>0.01336282967055603</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004721802360521143</v>
+        <v>0.02802794214560896</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0126695875870012</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0155367654799604</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01553517235037793</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01874284733740767</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01543602391664844</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01552044614239663</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01553517113510348</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01543602524523693</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01553517113510348</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01380747955580115</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01553517113510348</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.02362047751337479</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.00252493206937708</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.004588738238050579</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.005445081705694004</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005445081705694004</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.009043296347317736</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.005356426361282859</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.005445081705694004</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.009189336001955851</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01470106517822103</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.004721802360521145</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.02334987487409507</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.003321032220250003</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.005501119341130271</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.005475317249701139</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.005475317249701139</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009396565600021896</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.005814640476364389</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.005475317249701139</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.009622982945345932</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01459192760888927</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.004865729782529741</v>
+      <c r="B11" t="n">
+        <v>0.02334987487409509</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.003321032220250006</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.005501119341130276</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005475317249701141</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005475317249701141</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.009396565600021894</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.00581464047636439</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005475317249701141</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.009622982945345939</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0145919276088893</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004865729782529743</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,321 +2891,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01361325948938709</v>
+        <v>0.02341097357524104</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01441526830376927</v>
+        <v>0.003823501236258138</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09409248131360289</v>
+        <v>0.006304097312661459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02251872941426052</v>
+        <v>0.005734920251446567</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02251872941426052</v>
+        <v>0.005734920251446567</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07585414718808449</v>
+        <v>0.009952501651837671</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1060271508964349</v>
+        <v>0.006305907514706933</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02251872941426052</v>
+        <v>0.005734920251446567</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1868336155604768</v>
+        <v>0.0108287733320269</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04094041563000355</v>
+        <v>0.01488506400916972</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1804926760457591</v>
+        <v>0.005693516769172672</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003134237111875768</v>
+        <v>0.02377625557425796</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002878265025402605</v>
+        <v>0.003880116637249621</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003134237111875768</v>
+        <v>0.006310582955509506</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002956601956202138</v>
+        <v>0.005813264892849581</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002956601956202138</v>
+        <v>0.005813264892849581</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003113835371873376</v>
+        <v>0.01003954769443541</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003134237111875768</v>
+        <v>0.006310582955509506</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002997445005418485</v>
+        <v>0.005813264892849581</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003134237111875768</v>
+        <v>0.01081210364888066</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003134237111875768</v>
+        <v>0.01508772497073521</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003134237111875768</v>
+        <v>0.005617450734812481</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004585380425500466</v>
+        <v>0.0136132594893871</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0044398939081742</v>
+        <v>0.0144152683037693</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00466304793658026</v>
+        <v>0.09409248131360289</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004211067312423112</v>
+        <v>0.0225187294142608</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004443361367064963</v>
+        <v>0.0225187294142608</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004564978685498076</v>
+        <v>0.07585414718808428</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009008569484936115</v>
+        <v>0.1060271508964353</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008683783749820401</v>
+        <v>0.0225187294142608</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004761427874000619</v>
+        <v>0.1868336155604769</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004546073621881436</v>
+        <v>0.04094041563000357</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004629969808570055</v>
+        <v>0.1804926760457592</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006691237222486927</v>
+        <v>0.003134237111875773</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006689988729976521</v>
+        <v>0.002878265025402598</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006691127214152839</v>
+        <v>0.003134237111875773</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006567159757514687</v>
+        <v>0.002956601956202127</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006567159757514687</v>
+        <v>0.002956601956202129</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006670835482484535</v>
+        <v>0.003113835371873375</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006691237222486927</v>
+        <v>0.003134237111875773</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006554445116029646</v>
+        <v>0.002997445005418487</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006691237222486927</v>
+        <v>0.003134237111875773</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006691237222486927</v>
+        <v>0.003134237111875773</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006691237222486927</v>
+        <v>0.003134237111875773</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01421976963576358</v>
+        <v>0.004585380425500472</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02184357606210947</v>
+        <v>0.004439893908175041</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02340929834963407</v>
+        <v>0.004663047936580258</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01962494226831298</v>
+        <v>0.004211067312423127</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01433189388483284</v>
+        <v>0.004443361367064967</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0218106480804577</v>
+        <v>0.004564978685498084</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02183104982046476</v>
+        <v>0.009008569484936118</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02169425771400282</v>
+        <v>0.008683783749820413</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02183254565481754</v>
+        <v>0.004761427874000616</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01407838619871809</v>
+        <v>0.004546073621881432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02978166841803345</v>
+        <v>0.00462996980857005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0148036110405937</v>
+        <v>0.006691237222486937</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01827666176725144</v>
+        <v>0.006689988729976538</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01827791212088182</v>
+        <v>0.006691127214152843</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02215038534636382</v>
+        <v>0.006567159757514707</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01814111645632008</v>
+        <v>0.006567159757514707</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01825750851975949</v>
+        <v>0.006670835482484545</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01827791025976187</v>
+        <v>0.006691237222486937</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01814111815330458</v>
+        <v>0.006554445116029655</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01827791025976186</v>
+        <v>0.006691237222486937</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01626488843032971</v>
+        <v>0.006691237222486937</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01827791025976186</v>
+        <v>0.006691237222486937</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02355536303549637</v>
+        <v>0.0142197696357636</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003742652694071677</v>
+        <v>0.02184357606210951</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004325415778656329</v>
+        <v>0.02340929834963411</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005483197351800161</v>
+        <v>0.01962494226831299</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005483197351800161</v>
+        <v>0.01433189388483285</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008521925097762126</v>
+        <v>0.02181064808045771</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004325426698964346</v>
+        <v>0.02183104982046479</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005483197351800161</v>
+        <v>0.02169425771400282</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006896458226316981</v>
+        <v>0.02183254565481758</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0143344215487664</v>
+        <v>0.01407838619871809</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002185859083031004</v>
+        <v>0.02978166841803351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01480361104059375</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01827666176725149</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01827791212088188</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02215038534636392</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01814111645632012</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01825750851975953</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01827791025976191</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01814111815330462</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01827791025976191</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01626488843032975</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01827791025976191</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.02355536303549635</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.003742652694071679</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.004325415778656334</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.005483197351800166</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005483197351800165</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.008521925097762128</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.004325426698964343</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.005483197351800166</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.006896458226317007</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01433442154876644</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.002185859083031006</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.02331046676616177</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.003760954704040576</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.005400839920840834</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.005584738468406234</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.005584738468406234</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009261978533975059</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.005402655091661252</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.005584738468406234</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.00904714218633886</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01454230855153831</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.00413213163177837</v>
+      <c r="B11" t="n">
+        <v>0.02331046676616176</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.00376095470404058</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.005400839920840842</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005584738468406244</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005584738468406243</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.009261978533975063</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.005402655091661259</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005584738468406243</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.009047142186338876</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01454230855153836</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004132131631778374</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,320 +3367,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008886508093734754</v>
+        <v>0.02326188004002411</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01317268604645614</v>
+        <v>0.003700164436879434</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01684615541312434</v>
+        <v>0.006069682698483525</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01779344540443877</v>
+        <v>0.005597019570339002</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01779344540443877</v>
+        <v>0.005597019570339002</v>
       </c>
       <c r="G2" t="n">
-        <v>0.019301737803734</v>
+        <v>0.009700919851368327</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02161078001053101</v>
+        <v>0.006073184814339968</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01779344540443877</v>
+        <v>0.005597019570339002</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05859999191388923</v>
+        <v>0.01044761614314648</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01456636157822957</v>
+        <v>0.01462689450498652</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03265936879183572</v>
+        <v>0.004952739009131677</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002972851186683715</v>
+        <v>0.02363037609234934</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002784270327579673</v>
+        <v>0.003756284645398613</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002972851186683715</v>
+        <v>0.006158885869871383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00294324239123818</v>
+        <v>0.005677824435210014</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00294324239123818</v>
+        <v>0.005677824435210014</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002955016341762893</v>
+        <v>0.009845365214235031</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002972851186683715</v>
+        <v>0.006158885869871383</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002852619155348074</v>
+        <v>0.005677824435210014</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002972851186683715</v>
+        <v>0.01055981232485138</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002972851186683715</v>
+        <v>0.01485492287823014</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002972851186683715</v>
+        <v>0.005009555472364545</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004260390574682121</v>
+        <v>0.008886508093734747</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004199964412999212</v>
+        <v>0.01317268604645613</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008031784316505195</v>
+        <v>0.01684615541312431</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004004540806770754</v>
+        <v>0.01779344540443877</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004151164644148569</v>
+        <v>0.01779344540443877</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004242555729761292</v>
+        <v>0.0193017378037343</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008202939558767127</v>
+        <v>0.021610780010531</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007904617361913831</v>
+        <v>0.01779344540443877</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008020229597162098</v>
+        <v>0.05859999191388918</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004252079227031285</v>
+        <v>0.01456636157822957</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004259471337629542</v>
+        <v>0.03265936879183569</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006109511391004171</v>
+        <v>0.002972851186683711</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006110713551229466</v>
+        <v>0.002784270327579668</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006109407832102504</v>
+        <v>0.002972851186683709</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00600621361032978</v>
+        <v>0.002943242391238186</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00600621361032978</v>
+        <v>0.002943242391238186</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00609167654608336</v>
+        <v>0.002955016341762886</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006109511391004171</v>
+        <v>0.002972851186683711</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005989279359668537</v>
+        <v>0.00285261915534808</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006109511391004171</v>
+        <v>0.002972851186683711</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006109511391004171</v>
+        <v>0.002972851186683711</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006109511391004171</v>
+        <v>0.002972851186683711</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01306866511017576</v>
+        <v>0.004260390574682106</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01999431874504807</v>
+        <v>0.004199964412999215</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02140761927594572</v>
+        <v>0.008031784316505187</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01798205448012416</v>
+        <v>0.00400454080677075</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01317753143953853</v>
+        <v>0.004151164644148568</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01995761717232088</v>
+        <v>0.004242555729761289</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01997545201725529</v>
+        <v>0.008202939558767117</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01985521998590604</v>
+        <v>0.007904617361913838</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01997680939851304</v>
+        <v>0.008020229597162094</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01294036799744087</v>
+        <v>0.004252079227031373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0271901684776171</v>
+        <v>0.004259471337629536</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01237791235480485</v>
+        <v>0.006109511391004163</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01519428580433721</v>
+        <v>0.006110713551229456</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01519308474417125</v>
+        <v>0.006109407832102506</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01832149982247226</v>
+        <v>0.00600621361032978</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01507285100371939</v>
+        <v>0.00600621361032978</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01517524879919111</v>
+        <v>0.006091676546083348</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01519308364411193</v>
+        <v>0.006109511391004163</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0150728516127763</v>
+        <v>0.005989279359668525</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01519308364411193</v>
+        <v>0.006109511391004163</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01356196280573723</v>
+        <v>0.006109511391004163</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01519308364411193</v>
+        <v>0.006109511391004163</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02350549945617978</v>
+        <v>0.01306866511017575</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003630471259481202</v>
+        <v>0.0199943187450481</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005937405221861314</v>
+        <v>0.02140761927594566</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005433564885670246</v>
+        <v>0.01798205448012418</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005433564885670245</v>
+        <v>0.01317753143953855</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009572345349231693</v>
+        <v>0.01995761717232086</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005869733732258805</v>
+        <v>0.01997545201725526</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005433564885670246</v>
+        <v>0.01985521998590604</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009386077305255322</v>
+        <v>0.01997680939851306</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01469007521125327</v>
+        <v>0.01294036799744084</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004494994219524952</v>
+        <v>0.02719016847761706</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01237791235480484</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01519428580433724</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01519308474417126</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01832149982247228</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01507285100371938</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01517524879919113</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01519308364411193</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01507285161277632</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01519308364411193</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01356196280573725</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01519308364411193</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.02350549945617979</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.003630471259481204</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.005937405221861316</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.005433564885670243</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005433564885670243</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.009572345349231692</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.005869733732258802</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.005433564885670243</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.009386077305255312</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01469007521125328</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.004494994219524947</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.02320506077260875</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.003642918945343541</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.005968908297821989</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.00548588069688941</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.00548588069688941</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009576694942729102</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.005941619670253063</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.00548588069688941</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.009913562968758701</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="B11" t="n">
+        <v>0.02320506077260873</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.003642918945343536</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.005968908297821984</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005485880696889403</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005485880696889403</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.009576694942729112</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.005941619670253058</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005485880696889403</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.009913562968758694</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.01455188829117369</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
         <v>0.004718611999280247</v>
       </c>
     </row>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008599788720060356</v>
+        <v>0.02319137982880949</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0134627481133618</v>
+        <v>0.003646974695517915</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01608041960289697</v>
+        <v>0.006024260825937239</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01548685597904239</v>
+        <v>0.005383209499287423</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01548685597904239</v>
+        <v>0.005383209499287423</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01511497825841449</v>
+        <v>0.009565739422051092</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01769093862546027</v>
+        <v>0.006024551572434662</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01548685597904239</v>
+        <v>0.005383209499287423</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01847570971537862</v>
+        <v>0.009789055221599893</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01287060428164847</v>
+        <v>0.01452314189194705</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01571103033876277</v>
+        <v>0.004855149172931505</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002954578612930028</v>
+        <v>0.02355935265992357</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002786988927392983</v>
+        <v>0.003702183568629799</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002954578612930028</v>
+        <v>0.006113917766253718</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002926399416784656</v>
+        <v>0.005463587535072902</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002926399416784656</v>
+        <v>0.005463587535072902</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002940925079378511</v>
+        <v>0.009713127911534182</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002954578612930028</v>
+        <v>0.006113917766253718</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002862227079973048</v>
+        <v>0.005463587535072902</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002954578612930028</v>
+        <v>0.009936473369705611</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002954578612930028</v>
+        <v>0.01475178959801115</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002954578612930028</v>
+        <v>0.004928299634882311</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007986145282362286</v>
+        <v>0.008599788720060415</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004184109339604566</v>
+        <v>0.01346274811336182</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004227794892643436</v>
+        <v>0.01608041960289701</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004005968574783978</v>
+        <v>0.01548685597904241</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004150907830300555</v>
+        <v>0.01548685597904241</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00797249174881081</v>
+        <v>0.01511497825841472</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004229244888797616</v>
+        <v>0.01769093862546032</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007893793749405287</v>
+        <v>0.01548685597904241</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004345379793010388</v>
+        <v>0.01847570971537865</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004232294500588195</v>
+        <v>0.01287060428164854</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004227452599272688</v>
+        <v>0.01571103033876279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006040010612943432</v>
+        <v>0.002954578612930089</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00604143890546729</v>
+        <v>0.002786988927392947</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006039902446159946</v>
+        <v>0.002954578612930089</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00596111026674198</v>
+        <v>0.002926399416784656</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00596111026674198</v>
+        <v>0.002926399416784657</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006026357079391904</v>
+        <v>0.002940925079378589</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006040010612943432</v>
+        <v>0.002954578612930089</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00594765907998642</v>
+        <v>0.002862227079973054</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006040010612943432</v>
+        <v>0.002954578612930089</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006040010612943432</v>
+        <v>0.002954578612930089</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006040010612943432</v>
+        <v>0.002954578612930089</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01297529362770462</v>
+        <v>0.007986145282362326</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01983915304645631</v>
+        <v>0.004184109339604567</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02124338736754389</v>
+        <v>0.004227794892643463</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01787094065536516</v>
+        <v>0.004005968574783994</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01310810498754307</v>
+        <v>0.00415090783030054</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01980973644454877</v>
+        <v>0.007972491748810833</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01982338997811558</v>
+        <v>0.004229244888797626</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01973103844514325</v>
+        <v>0.007893793749405296</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01982473582502019</v>
+        <v>0.004345379793010393</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01284808672218536</v>
+        <v>0.004232294500588197</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02697679924443983</v>
+        <v>0.004227452599272748</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.011848163244575</v>
+        <v>0.006040010612943445</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01451853519984682</v>
+        <v>0.006041438905467282</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01451710791205329</v>
+        <v>0.006039902446159967</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01750465994712833</v>
+        <v>0.005961110266741979</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01442475478912065</v>
+        <v>0.005961110266741979</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01450345337377146</v>
+        <v>0.00602635707939194</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01451710690732292</v>
+        <v>0.006040010612943445</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01442475537436595</v>
+        <v>0.005947659079986403</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01451710690732292</v>
+        <v>0.006040010612943445</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01297071088996187</v>
+        <v>0.006040010612943445</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01451710690732292</v>
+        <v>0.006040010612943445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0234409719768757</v>
+        <v>0.01297529362770462</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003569242767451584</v>
+        <v>0.01983915304645628</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005910841272076368</v>
+        <v>0.0212433873675439</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005275429362037753</v>
+        <v>0.01787094065536514</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005275429362037753</v>
+        <v>0.01310810498754305</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009539081751066649</v>
+        <v>0.01980973644454874</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005908848551871904</v>
+        <v>0.01982338997811558</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005275429362037753</v>
+        <v>0.01973103844514324</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009691894685974256</v>
+        <v>0.01982473582502024</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01462786460577064</v>
+        <v>0.01284808672218538</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004770948543742899</v>
+        <v>0.02697679924443979</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.011848163244575</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01451853519984681</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01451710791205326</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01750465994712832</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01442475478912065</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01450345337377145</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01451710690732298</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01442475537436595</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01451710690732298</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01297071088996182</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01451710690732298</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.02344097197687573</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.003569242767451577</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.005910841272076369</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.005275429362037752</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005275429362037752</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.009539081751066667</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.005908848551871919</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.005275429362037752</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.009691894685974256</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01462786460577065</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.004770948543742894</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.02313751624076586</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.003586486207324622</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.00593186037392018</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B11" t="n">
+        <v>0.02313751624076587</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.003586486207324619</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.005931860373920159</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.005297596930931913</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.005297596930931913</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.009486547864386165</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.005931244426374114</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.005297596930931913</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.009677771141076121</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01446675562555208</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.004783553925014875</v>
+      <c r="G11" t="n">
+        <v>0.009486547864386187</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.005931244426374129</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005297596930931912</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.009677771141076113</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01446675562555209</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004783553925014898</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01169407178780477</v>
+        <v>0.02330636090248922</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01399991781024967</v>
+        <v>0.00377776319570805</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02816559652470747</v>
+        <v>0.006135213267105631</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02124715671069845</v>
+        <v>0.005631704458755912</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02124715671069845</v>
+        <v>0.005631704458755912</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03599552325970767</v>
+        <v>0.009773876848584408</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0897458057560522</v>
+        <v>0.006193603278110821</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02124715671069845</v>
+        <v>0.005631704458755912</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02657857207788682</v>
+        <v>0.01038659058428655</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0200235107651149</v>
+        <v>0.01470168301479817</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1464784220578489</v>
+        <v>0.005558089585734062</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003045597705752457</v>
+        <v>0.02367290514502389</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002819185724277052</v>
+        <v>0.00383489651168268</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003045597705752457</v>
+        <v>0.006213697039438515</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002909068940805864</v>
+        <v>0.005710320231405861</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002909068940805865</v>
+        <v>0.005710320231405861</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003026538488224297</v>
+        <v>0.009902333500883547</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003045597705752457</v>
+        <v>0.006213697039438515</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002917340125959149</v>
+        <v>0.005710320231405861</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003045597705752457</v>
+        <v>0.01053553345473115</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003045597705752457</v>
+        <v>0.01492558564874455</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003045597705752457</v>
+        <v>0.005514163390585333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004361730923878836</v>
+        <v>0.01169407178780477</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004275105173268603</v>
+        <v>0.01399991781024968</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004359507655346498</v>
+        <v>0.02816559652470746</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004061802677096864</v>
+        <v>0.02124715671069848</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004234649794931339</v>
+        <v>0.02124715671069848</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00434267170635069</v>
+        <v>0.03599552325970803</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008624556688906462</v>
+        <v>0.0897458057560522</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004233473344085519</v>
+        <v>0.02124715671069848</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004476756872744275</v>
+        <v>0.02657857207788689</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004331685449439452</v>
+        <v>0.02002351076511485</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004396735037918118</v>
+        <v>0.1464784220578489</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006425580897100104</v>
+        <v>0.003045597705752444</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006426126817819828</v>
+        <v>0.002819185724277062</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006425471598322803</v>
+        <v>0.003045597705752444</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006312963575285931</v>
+        <v>0.00290906894080586</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006312963575285931</v>
+        <v>0.00290906894080587</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006406521679572017</v>
+        <v>0.003026538488224349</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006425580897100104</v>
+        <v>0.003045597705752444</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006297323317306774</v>
+        <v>0.002917340125959155</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006425580897100104</v>
+        <v>0.003045597705752444</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006425580897100104</v>
+        <v>0.003045597705752444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006425580897100104</v>
+        <v>0.003045597705752444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01382497894726185</v>
+        <v>0.004361730923878813</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02122499971769535</v>
+        <v>0.00427510517326862</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02273883093634413</v>
+        <v>0.004359507655346444</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01907526166731154</v>
+        <v>0.004061802677096847</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01394014483693795</v>
+        <v>0.004234649794931329</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0211888690763532</v>
+        <v>0.004342671706350719</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02120792829388548</v>
+        <v>0.008624556688906474</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02107967071408789</v>
+        <v>0.004233473344085512</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02120937925471463</v>
+        <v>0.004476756872744218</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01368783687275609</v>
+        <v>0.004331685449439459</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02892003623839472</v>
+        <v>0.004396735037918126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01378842251211405</v>
+        <v>0.00642558089710007</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01699231283878128</v>
+        <v>0.006426126817819836</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01699176761066366</v>
+        <v>0.006425471598322772</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02056009949057078</v>
+        <v>0.006312963575285943</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01686350774116001</v>
+        <v>0.006312963575285943</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01697270770053345</v>
+        <v>0.006406521679571982</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01699176691806153</v>
+        <v>0.00642558089710007</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01686350933826823</v>
+        <v>0.006297323317306771</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01699176691806153</v>
+        <v>0.00642558089710007</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01513573688005704</v>
+        <v>0.00642558089710007</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01699176691806153</v>
+        <v>0.00642558089710007</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02349378267962536</v>
+        <v>0.01382497894726186</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003704821485575324</v>
+        <v>0.02122499971769539</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005750062879498967</v>
+        <v>0.02273883093634419</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005407482986501695</v>
+        <v>0.01907526166731158</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005407482986501695</v>
+        <v>0.01394014483693798</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009276796416253003</v>
+        <v>0.02118886907635315</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004558469504504043</v>
+        <v>0.02120792829388555</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005407482986501695</v>
+        <v>0.02107967071408793</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01013391290800199</v>
+        <v>0.02120937925471461</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01465158805226539</v>
+        <v>0.01368783687275613</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002760216168259015</v>
+        <v>0.02892003623839472</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01378842251211407</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01699231283878128</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01699176761066363</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02056009949057081</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01686350774116003</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01697270770053345</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01699176691806152</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01686350933826824</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01699176691806152</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01513573688005703</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01699176691806152</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.02349378267962534</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.003704821485575332</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.005750062879498974</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.005407482986501694</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005407482986501694</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.009276796416252984</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.004558469504504037</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.005407482986501694</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01013391290800201</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01465158805226535</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.002760216168259005</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.02322485960990349</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.003718578644304688</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.005924258246818734</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.005493912547239495</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.005493912547239495</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009489255481609071</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.005440469474818475</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.005493912547239495</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01020385195563604</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01457701323522165</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.004305034823266526</v>
+      <c r="B11" t="n">
+        <v>0.02322485960990344</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.003718578644304693</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.005924258246818741</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005493912547239494</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005493912547239494</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.009489255481609081</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.005440469474818468</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005493912547239494</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01020385195563607</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01457701323522161</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004305034823266516</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.009224635767217295</v>
+        <v>0.02300543136690805</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01339024999273035</v>
+        <v>0.003739294988315033</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0162262823861192</v>
+        <v>0.006038398948426236</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01743459616671993</v>
+        <v>0.005580858911965688</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01743459616671993</v>
+        <v>0.005580858911965688</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01544399652685609</v>
+        <v>0.009658782801059451</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01795602488678408</v>
+        <v>0.006038796493771876</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01743459616671993</v>
+        <v>0.005580858911965688</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01913419248796768</v>
+        <v>0.01032938950954246</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01421667979447918</v>
+        <v>0.01467722347877527</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01567988978571763</v>
+        <v>0.004907350667921914</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002949231022718562</v>
+        <v>0.02336955475017305</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002764351900169939</v>
+        <v>0.00379587711708843</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002949231022718562</v>
+        <v>0.006127927495049711</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002934839717943014</v>
+        <v>0.005661886901107283</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002934839717943014</v>
+        <v>0.005661886901107283</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002931539216082069</v>
+        <v>0.009807087738400354</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002949231022718562</v>
+        <v>0.006127927495049711</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00282989785059091</v>
+        <v>0.005661886901107283</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002949231022718562</v>
+        <v>0.01048447473391986</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002949231022718562</v>
+        <v>0.01490655397792312</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002949231022718562</v>
+        <v>0.004981183937210004</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007962199281257871</v>
+        <v>0.009224635767217342</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004161848994556375</v>
+        <v>0.01339024999273032</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004215189211771274</v>
+        <v>0.01622628238611922</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003970185482568505</v>
+        <v>0.01743459616671993</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004109062950914592</v>
+        <v>0.01743459616671993</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004198679525177687</v>
+        <v>0.01544399652685636</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008135453483146923</v>
+        <v>0.01795602488678413</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007842866109130212</v>
+        <v>0.01743459616671993</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004326671718739084</v>
+        <v>0.01913419248796765</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004211409481256898</v>
+        <v>0.01421667979447919</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004210316876003821</v>
+        <v>0.01567988978571767</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006041149430154887</v>
+        <v>0.002949231022718591</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006042567243285206</v>
+        <v>0.002764351900169937</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006041046067998744</v>
+        <v>0.002949231022718591</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00594221078769272</v>
+        <v>0.002934839717943016</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00594221078769272</v>
+        <v>0.002934839717943016</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006023457623518385</v>
+        <v>0.002931539216082056</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006041149430154887</v>
+        <v>0.002949231022718591</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005921816258027237</v>
+        <v>0.002829897850590903</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006041149430154887</v>
+        <v>0.002949231022718588</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006041149430154887</v>
+        <v>0.002949231022718591</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006041149430154887</v>
+        <v>0.002949231022718591</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01296702402139767</v>
+        <v>0.007962199281257874</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01983650683477279</v>
+        <v>0.004161848994556392</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02123392121911791</v>
+        <v>0.004215189211771307</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01784090012469769</v>
+        <v>0.003970185482568503</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01307696150241378</v>
+        <v>0.004109062950914605</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01979643752223955</v>
+        <v>0.004198679525177708</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01981412932888942</v>
+        <v>0.008135453483146891</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01969479615674836</v>
+        <v>0.007842866109130226</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0198154749810377</v>
+        <v>0.00432667171873908</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01283983552501392</v>
+        <v>0.004211409481257056</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02696650336801577</v>
+        <v>0.004210316876003826</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01225706130292632</v>
+        <v>0.006041149430154865</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01504236124457706</v>
+        <v>0.006042567243285207</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0150409444509518</v>
+        <v>0.006041046067998759</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0181341514452296</v>
+        <v>0.005942210787692715</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01492160971197766</v>
+        <v>0.005942210787692715</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01502325162481025</v>
+        <v>0.006023457623518384</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01504094343144674</v>
+        <v>0.006041149430154865</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0149216102593191</v>
+        <v>0.005921816258027227</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01504094343144674</v>
+        <v>0.006041149430154865</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01153553864620362</v>
+        <v>0.006041149430154865</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01504094343144674</v>
+        <v>0.006041149430154865</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02323642499930583</v>
+        <v>0.01296702402139764</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00366457056439344</v>
+        <v>0.01983650683477277</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005921161149191078</v>
+        <v>0.02123392121911792</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005425908427801274</v>
+        <v>0.01784090012469767</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005425908427801274</v>
+        <v>0.01307696150241378</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009625032532799949</v>
+        <v>0.01979643752223956</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005917041739546142</v>
+        <v>0.01981412932888943</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005425908427801274</v>
+        <v>0.01969479615674836</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01022452011362425</v>
+        <v>0.0198154749810377</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01474979350075399</v>
+        <v>0.01283983552501393</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004824379987865414</v>
+        <v>0.0269665033680158</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01225706130292628</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01504236124457706</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01504094445095179</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01813415144522959</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01492160971197766</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01502325162481026</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01504094343144675</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01492161025931912</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01504094343144675</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0115355386462036</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01504094343144675</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.02323642499930585</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.003664570564393442</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.005921161149191072</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.005425908427801271</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005425908427801271</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.009625032532799926</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.005917041739546157</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.005425908427801271</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01022452011362426</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01474979350075399</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.004824379987865427</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.02294485690600417</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.003679550088389666</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.005944319602135286</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.005473487954592678</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.005473487954592678</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009575947102335759</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.005942842802964715</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.005473487954592678</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>0.02294485690600413</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.003679550088389656</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.005944319602135284</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005473487954592677</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005473487954592677</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.009575947102335749</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.005942842802964706</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005473487954592677</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.01021110932888175</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.01460589696209732</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.004836004371265585</v>
+      <c r="K11" t="n">
+        <v>0.0146058969620973</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004836004371265573</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008833502214377795</v>
+        <v>0.02231790678976808</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01340488412654959</v>
+        <v>0.003709705392188005</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01555125037519057</v>
+        <v>0.005993684866288725</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01544068238039763</v>
+        <v>0.005361876571700042</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01544068238039763</v>
+        <v>0.005361876571700042</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01483202660468358</v>
+        <v>0.009478512298187518</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01730087504122372</v>
+        <v>0.005994182558086204</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01544068238039763</v>
+        <v>0.005361876571700042</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01841327637492716</v>
+        <v>0.009745572009938761</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01369328576275756</v>
+        <v>0.01454141778361699</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0155588096060146</v>
+        <v>0.00483213207205629</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002929637956866334</v>
+        <v>0.02267176000291012</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002763037465401209</v>
+        <v>0.00376601972818883</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002929637956866334</v>
+        <v>0.006083520338150581</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002912322339560774</v>
+        <v>0.005442004847396143</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002912322339560774</v>
+        <v>0.005442004847396143</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002916038518521154</v>
+        <v>0.009624877833042722</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002929637956866334</v>
+        <v>0.006083520338150581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002837630225288185</v>
+        <v>0.005442004847396143</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002929637956866334</v>
+        <v>0.009892408484430052</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002929637956866334</v>
+        <v>0.01476942496133217</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002929637956866334</v>
+        <v>0.004905114722892241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00794179788439385</v>
+        <v>0.008833502214377797</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004156556941733487</v>
+        <v>0.01340488412654959</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004198327495270646</v>
+        <v>0.0155512503751906</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00398171298035517</v>
+        <v>0.01544068238039763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004124132778254892</v>
+        <v>0.01544068238039763</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004193174492097304</v>
+        <v>0.0148320266046838</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008112974609429941</v>
+        <v>0.01730087504122373</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004114766198864343</v>
+        <v>0.01544068238039763</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007933171863355154</v>
+        <v>0.0184132763749272</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004205815573628684</v>
+        <v>0.01369328576275755</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004199795142788689</v>
+        <v>0.01555880960601461</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005983760044628242</v>
+        <v>0.002929637956866329</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005985231435880706</v>
+        <v>0.002763037465401218</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005983651936477088</v>
+        <v>0.002929637956866329</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005908196952098289</v>
+        <v>0.002912322339560772</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005908196952098289</v>
+        <v>0.002912322339560772</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005970160606283053</v>
+        <v>0.002916038518521149</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005983760044628242</v>
+        <v>0.002929637956866329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005891752313050095</v>
+        <v>0.002837630225288179</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005983760044628242</v>
+        <v>0.002929637956866329</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005983760044628242</v>
+        <v>0.002929637956866329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005983760044628242</v>
+        <v>0.002929637956866329</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01288898076382283</v>
+        <v>0.007941797884393842</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01970557430602284</v>
+        <v>0.004156556941733488</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02109651277543055</v>
+        <v>0.004198327495270632</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0177510793194026</v>
+        <v>0.003981712980355069</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01302233161598251</v>
+        <v>0.004124132778254895</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01967331707499279</v>
+        <v>0.004193174492097309</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01968691651335347</v>
+        <v>0.008112974609429944</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0195949087817598</v>
+        <v>0.004114766198864352</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0196882525023934</v>
+        <v>0.007933171863355154</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01276270561720565</v>
+        <v>0.004205815573628689</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02678792883781971</v>
+        <v>0.004199795142788701</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01179402822379606</v>
+        <v>0.005983760044628243</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0144515096624742</v>
+        <v>0.00598523143588071</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01445003925718718</v>
+        <v>0.005983651936477079</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01742301000547359</v>
+        <v>0.005908196952098297</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01435802997669883</v>
+        <v>0.005908196952098297</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01443643883287654</v>
+        <v>0.005970160606283055</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01445003827122173</v>
+        <v>0.005983760044628243</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01435803053964356</v>
+        <v>0.005891752313050107</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01445003827122173</v>
+        <v>0.005983760044628243</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0128487007857685</v>
+        <v>0.005983760044628243</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01445003827122173</v>
+        <v>0.005983760044628243</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02254760088685317</v>
+        <v>0.01288898076382283</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00363421288308629</v>
+        <v>0.01970557430602284</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00589305283934819</v>
+        <v>0.02109651277543055</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00525467018152562</v>
+        <v>0.01775107931940261</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00525467018152562</v>
+        <v>0.01302233161598251</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009457240640813205</v>
+        <v>0.01967331707499279</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005886570219566339</v>
+        <v>0.01968691651335349</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00525467018152562</v>
+        <v>0.01959490878175982</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009648985736305637</v>
+        <v>0.01968825250239341</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01462521013351357</v>
+        <v>0.01276270561720567</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004750703837320687</v>
+        <v>0.02678792883781973</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01179402822379609</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01445150966247421</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0144500392571872</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01742301000547363</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01435802997669885</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01443643883287656</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01445003827122175</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0143580305396436</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01445003827122175</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01284870078576852</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01445003827122175</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.02254760088685317</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.003634212883086293</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.005893052839348199</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.005254670181525624</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005254670181525624</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.009457240640813208</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.005886570219566331</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.005254670181525624</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.009648985736305639</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01462521013351356</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.004750703837320697</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.02226141399629057</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.02226141399629056</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.003649732857622855</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.005907021547349733</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0052766387017288</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0052766387017288</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="D11" t="n">
+        <v>0.005907021547349739</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005276638701728801</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005276638701728801</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.009402236841495064</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.00590456962648757</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0052766387017288</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.00963481388379989</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01447579957737411</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.004761874627042947</v>
+      <c r="H11" t="n">
+        <v>0.005904569626487575</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005276638701728801</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.009634813883799899</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01447579957737412</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004761874627042944</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.139114870183489</v>
+        <v>0.01039767482951533</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05384168725244126</v>
+        <v>0.005750951645499635</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2730259730998579</v>
+        <v>0.0105420816238509</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05384168725244126</v>
+        <v>0.005750951645499635</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05384168725244126</v>
+        <v>0.005750951645499635</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2104575628769696</v>
+        <v>0.01043867658600589</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2406288622654865</v>
+        <v>0.01047989324268751</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05384168725244126</v>
+        <v>0.005750951645499635</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2086654510090266</v>
+        <v>0.01045853425928257</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09563489094235468</v>
+        <v>0.01034586116370529</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2241597077176096</v>
+        <v>0.01046467710889648</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003585972859797619</v>
+        <v>0.01041302496792798</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003163828868890294</v>
+        <v>0.005791947994723268</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003585972859797619</v>
+        <v>0.01041302496792798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003225686266417523</v>
+        <v>0.005791947994723268</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003225686266417523</v>
+        <v>0.005791947994723268</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003561283140588568</v>
+        <v>0.0103832123247647</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003585972859797619</v>
+        <v>0.01041302496792798</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003421607277261441</v>
+        <v>0.005791947994723268</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003585972859797619</v>
+        <v>0.01041302496792798</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003585972859797619</v>
+        <v>0.01041302496792798</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003585972859797619</v>
+        <v>0.01041302496792798</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005386208891879901</v>
+        <v>0.1391148701834886</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004956032068951335</v>
+        <v>0.05384168725244142</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005638405954819944</v>
+        <v>0.2730259730998585</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004811673799686998</v>
+        <v>0.05384168725244142</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005195692425632405</v>
+        <v>0.05384168725244142</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005361519172670845</v>
+        <v>0.2104575628769695</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01065320682249958</v>
+        <v>0.2406288622654868</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0103464485985073</v>
+        <v>0.05384168725244142</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005584138652997544</v>
+        <v>0.2086654510090267</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005266159413164483</v>
+        <v>0.09563489094235469</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005641116911568059</v>
+        <v>0.2241597077176092</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007661843513957541</v>
+        <v>0.003585972859797623</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007497477931421381</v>
+        <v>0.00316382886889029</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007661705338640658</v>
+        <v>0.003585972859797623</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007492694051283783</v>
+        <v>0.003225686266417519</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007492694051283783</v>
+        <v>0.00322568626641752</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007637153794748516</v>
+        <v>0.003561283140588571</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007661843513957541</v>
+        <v>0.003585972859797623</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007497477931421381</v>
+        <v>0.003421607277261448</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007661843513957541</v>
+        <v>0.003585972859797623</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007661843513957541</v>
+        <v>0.003585972859797623</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007661843513957541</v>
+        <v>0.003585972859797623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0156629215515872</v>
+        <v>0.005386208891879887</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02383019208820953</v>
+        <v>0.004956032068951307</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02572551973840935</v>
+        <v>0.005638405954819929</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02155107139117203</v>
+        <v>0.004811673799686994</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01575997235062026</v>
+        <v>0.005195692425632398</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02397263684604433</v>
+        <v>0.005361519172670831</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02399732656525265</v>
+        <v>0.01065320682249956</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02383296098271719</v>
+        <v>0.01034644859850727</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0239989645142581</v>
+        <v>0.005584138652997528</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01550810569960823</v>
+        <v>0.005266159413164507</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03270330951326953</v>
+        <v>0.005641116911568036</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01879896543215796</v>
+        <v>0.007661843513957546</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02312946429967274</v>
+        <v>0.007497477931421373</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02329383371807998</v>
+        <v>0.007661705338640634</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02831644134345024</v>
+        <v>0.007492694051283778</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02312946054558781</v>
+        <v>0.007492694051283778</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02326914016299987</v>
+        <v>0.007637153794748505</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02329382988220889</v>
+        <v>0.007661843513957546</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02312946429967274</v>
+        <v>0.007497477931421373</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02329382988220889</v>
+        <v>0.007661843513957546</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02068948938050704</v>
+        <v>0.007661843513957546</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02329382988220889</v>
+        <v>0.007661843513957546</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007322864621737297</v>
+        <v>0.0156629215515872</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004726023062654862</v>
+        <v>0.02383019208820946</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004299481204293913</v>
+        <v>0.02572551973840937</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004726023062654862</v>
+        <v>0.02155107139117202</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004726023062654862</v>
+        <v>0.01575997235062025</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005831367330374048</v>
+        <v>0.02397263684604436</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005691895508352732</v>
+        <v>0.02399732656525264</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004726023062654862</v>
+        <v>0.02383296098271718</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006081963288904445</v>
+        <v>0.02399896451425807</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008411120575777019</v>
+        <v>0.01550810569960823</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005987889051848066</v>
+        <v>0.03270330951326947</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01879896543215795</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02312946429967273</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02329383371807995</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02831644134345023</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02312946054558778</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02326914016299984</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02329382988220887</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02312946429967273</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02329382988220887</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02068948938050699</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02329382988220887</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.007322864621737288</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004726023062654859</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.004299481204293896</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.004726023062654859</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.004726023062654859</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005831367330374047</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.005691895508352719</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.004726023062654859</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.006081963288904442</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.00841112057577701</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.005987889051848061</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.008991642024241851</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.005265952404507298</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.007760399728689417</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.005265952404507298</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.005265952404507298</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.008367572607688839</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.00833176429323389</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.005265952404507298</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.008487887393052247</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.009434988285585829</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.004885104527802984</v>
+      <c r="B11" t="n">
+        <v>0.008991642024241846</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.005265952404507296</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.007760399728689407</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005265952404507296</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005265952404507296</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.008367572607688827</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.008331764293233878</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005265952404507296</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.008487887393052227</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.009434988285585824</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004885104527802977</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1049430685742179</v>
+        <v>0.0103191722369443</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06766194198148101</v>
+        <v>0.005769989946895957</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2358628664672273</v>
+        <v>0.01047800427300409</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06766194198148101</v>
+        <v>0.005769989946895957</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06766194198148101</v>
+        <v>0.005769989946895957</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1844427034826812</v>
+        <v>0.01038656003514021</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2028644527964759</v>
+        <v>0.01041025198219618</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06766194198148101</v>
+        <v>0.005769989946895957</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1409540307219803</v>
+        <v>0.0103520890579217</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08413267438081082</v>
+        <v>0.01029868926068821</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2391211046126759</v>
+        <v>0.01045293545181518</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003539714169772108</v>
+        <v>0.01036611191044108</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003178985245783681</v>
+        <v>0.005788221647813192</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003539714169772106</v>
+        <v>0.01036611191044108</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003234562344303571</v>
+        <v>0.005788221647813192</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003234562344303572</v>
+        <v>0.005788221647813192</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003516993835112846</v>
+        <v>0.01034163791000477</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003539714169772106</v>
+        <v>0.01036611191044108</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003388137973469608</v>
+        <v>0.005788221647813192</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003539714169772106</v>
+        <v>0.01036611191044108</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003539714169772106</v>
+        <v>0.01036611191044108</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003539714169772106</v>
+        <v>0.01036611191044108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005268293812914962</v>
+        <v>0.1049430685742182</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004912532531765321</v>
+        <v>0.06766194198148119</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005472242899997735</v>
+        <v>0.2358628664672275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004774998643654482</v>
+        <v>0.06766194198148119</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00509725558157303</v>
+        <v>0.06766194198148119</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005245573478255682</v>
+        <v>0.1844427034826813</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01016857426492378</v>
+        <v>0.2028644527964764</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009899241560111257</v>
+        <v>0.06766194198148119</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005432950410411666</v>
+        <v>0.1409540307219802</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005165330721408149</v>
+        <v>0.08413267438081076</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005649359534612936</v>
+        <v>0.2391211046126757</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007263848247138021</v>
+        <v>0.003539714169772114</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007112272050835504</v>
+        <v>0.003178985245783678</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007263720039739076</v>
+        <v>0.003539714169772112</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007105748190588063</v>
+        <v>0.003234562344303567</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007105748190588063</v>
+        <v>0.003234562344303575</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007241127912478723</v>
+        <v>0.003516993835112831</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007263848247138019</v>
+        <v>0.003539714169772112</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007112272050835504</v>
+        <v>0.003388137973469597</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007263848247138019</v>
+        <v>0.003539714169772112</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007263848247138019</v>
+        <v>0.003539714169772112</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007263848247138019</v>
+        <v>0.003539714169772112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01463319913106686</v>
+        <v>0.005268293812914961</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02212465762319044</v>
+        <v>0.004912532531765323</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02386659762887017</v>
+        <v>0.005472242899997727</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02003356302341983</v>
+        <v>0.004774998643654481</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01472022522297506</v>
+        <v>0.005097255581573029</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02225809438280905</v>
+        <v>0.005245573478255697</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02228081471746822</v>
+        <v>0.0101685742649238</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02212923852116583</v>
+        <v>0.009899241560111266</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02228231769275346</v>
+        <v>0.00543295041041168</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01449114074529013</v>
+        <v>0.005165330721408146</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03026938868039052</v>
+        <v>0.005649359534612937</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01669726572208795</v>
+        <v>0.007263848247138004</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02044516606832149</v>
+        <v>0.007112272050835511</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02059674570514729</v>
+        <v>0.007263720039739075</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02494507863180435</v>
+        <v>0.00710574819058807</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02044516303271704</v>
+        <v>0.00710574819058807</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02057402192996471</v>
+        <v>0.007241127912478738</v>
       </c>
       <c r="H7" t="n">
-        <v>0.020596742264624</v>
+        <v>0.007263848247138004</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02044516606832149</v>
+        <v>0.007112272050835511</v>
       </c>
       <c r="J7" t="n">
-        <v>0.020596742264624</v>
+        <v>0.007263848247138004</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01833737168852324</v>
+        <v>0.007263848247138004</v>
       </c>
       <c r="L7" t="n">
-        <v>0.020596742264624</v>
+        <v>0.007263848247138004</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00795014344517341</v>
+        <v>0.01463319913106686</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004249156280351913</v>
+        <v>0.02212465762319044</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004624197785104198</v>
+        <v>0.02386659762887018</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004249156280351913</v>
+        <v>0.02003356302341981</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004249156280351913</v>
+        <v>0.01472022522297506</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006021672242010131</v>
+        <v>0.02225809438280905</v>
       </c>
       <c r="H8" t="n">
-        <v>0.006124088506774317</v>
+        <v>0.02228081471746822</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004249156280351913</v>
+        <v>0.02212923852116584</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007284927984042939</v>
+        <v>0.02228231769275343</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00838168340895518</v>
+        <v>0.01449114074529012</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00522701624463877</v>
+        <v>0.03026938868039052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01669726572208795</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02044516606832151</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02059674570514734</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02494507863180439</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02044516303271706</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02057402192996471</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02059674226462399</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02044516606832151</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02059674226462399</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01833737168852322</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02059674226462399</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.007950143445173403</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004249156280351916</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.004624197785104193</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.004249156280351916</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.004249156280351916</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.006021672242010131</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.006124088506774317</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.004249156280351916</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.007284927984042931</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.008381683408955171</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.005227016244638763</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.009219898886012838</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.005069710299990762</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.007865415047581217</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.005069710299990762</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.005069710299990762</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.00842096188928889</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.008480117815001329</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.005069710299990762</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.008950140552259981</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.009395767968513727</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.005180764545433817</v>
+      <c r="B11" t="n">
+        <v>0.00921989888601283</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.005069710299990764</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.007865415047581197</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005069710299990764</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005069710299990764</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.008420961889288892</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.00848011781500132</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005069710299990764</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.008950140552259976</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.009395767968513708</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.005180764545433802</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08776368811570272</v>
+        <v>0.01011764006778766</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09756063451059127</v>
+        <v>0.005652469260527261</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1924140202161272</v>
+        <v>0.01024941071592972</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09756063451059127</v>
+        <v>0.005652469260527261</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09756063451059127</v>
+        <v>0.005652469260527261</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1574808400970188</v>
+        <v>0.01018566741576508</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1862555838382431</v>
+        <v>0.01021680899673831</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09756063451059127</v>
+        <v>0.005652469260527261</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09753531858912884</v>
+        <v>0.01011954073980765</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07155038704493133</v>
+        <v>0.01010304201344504</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1626555975894998</v>
+        <v>0.01054946679832486</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003599396281762079</v>
+        <v>0.01017974530586895</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003307031656187676</v>
+        <v>0.005628938331203107</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003599396281762078</v>
+        <v>0.01017974530586895</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003359604503387267</v>
+        <v>0.005628938331203107</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003359604503387265</v>
+        <v>0.005628938331203107</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003579824434736068</v>
+        <v>0.01016570268492956</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003599396281762078</v>
+        <v>0.01017974530586895</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003468203790704683</v>
+        <v>0.005628938331203107</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003599396281762078</v>
+        <v>0.01017974530586895</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003599396281762078</v>
+        <v>0.01017974530586895</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003599396281762078</v>
+        <v>0.01017974530586895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005339820376747765</v>
+        <v>0.08776368811570258</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005108324348298509</v>
+        <v>0.0975606345105914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005485697223340827</v>
+        <v>0.192414020216127</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004968955643044747</v>
+        <v>0.0975606345105914</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005215872255264563</v>
+        <v>0.0975606345105914</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009912719000164142</v>
+        <v>0.1574808400970182</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01005211065707606</v>
+        <v>0.1862555838382431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005208627885690391</v>
+        <v>0.0975606345105914</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009961181850405463</v>
+        <v>0.09753531858912881</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005246173330510323</v>
+        <v>0.07155038704493151</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005481077024096164</v>
+        <v>0.1626555975895008</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007257507230589378</v>
+        <v>0.003599396281762036</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007126314739532</v>
+        <v>0.003307031656187674</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007257376852313793</v>
+        <v>0.003599396281762036</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007119303694337373</v>
+        <v>0.003359604503387261</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007119303694337373</v>
+        <v>0.003359604503387261</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007237935383563389</v>
+        <v>0.003579824434736064</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007257507230589372</v>
+        <v>0.003599396281762036</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007126314739532</v>
+        <v>0.003468203790704677</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007257507230589372</v>
+        <v>0.003599396281762036</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007257507230589372</v>
+        <v>0.003599396281762036</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007257507230589372</v>
+        <v>0.003599396281762036</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01452718238871777</v>
+        <v>0.005339820376747793</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02191484442898829</v>
+        <v>0.005108324348298472</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02361123893116539</v>
+        <v>0.005485697223340809</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01985762932591806</v>
+        <v>0.004968955643044747</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01463038196363289</v>
+        <v>0.005215872255264563</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02203153279180148</v>
+        <v>0.009912719000164135</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02205110463882796</v>
+        <v>0.01005211065707608</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02191991214777008</v>
+        <v>0.005208627885690336</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02205258330488889</v>
+        <v>0.009961181850405461</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01438742167016049</v>
+        <v>0.005246173330510348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0299104705689846</v>
+        <v>0.00548107702409617</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01576276292081628</v>
+        <v>0.007257507230589398</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01924808792156912</v>
+        <v>0.007126314739532012</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01937928291366228</v>
+        <v>0.007257376852313797</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02342147124305044</v>
+        <v>0.007119303694337374</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01924808516765413</v>
+        <v>0.007119303694337374</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01935970856560046</v>
+        <v>0.007237935383563403</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01937928041262644</v>
+        <v>0.007257507230589395</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01924808792156912</v>
+        <v>0.007126314739532012</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01937928041262644</v>
+        <v>0.007257507230589395</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01728385702663745</v>
+        <v>0.007257507230589395</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01937928041262644</v>
+        <v>0.007257507230589395</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008136190966557403</v>
+        <v>0.01452718238871782</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003271926246964267</v>
+        <v>0.02191484442898828</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00537693417707247</v>
+        <v>0.02361123893116546</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003271926246964267</v>
+        <v>0.01985762932591805</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003271926246964267</v>
+        <v>0.01463038196363289</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006420527866448041</v>
+        <v>0.02203153279180147</v>
       </c>
       <c r="H8" t="n">
-        <v>0.006136701345871672</v>
+        <v>0.022051104638828</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003271926246964267</v>
+        <v>0.02191991214777009</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008112966522508463</v>
+        <v>0.0220525833048889</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008444106010709386</v>
+        <v>0.0143874216701605</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0007414050132747219</v>
+        <v>0.02991047056898466</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01576276292081629</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01924808792156911</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01937928291366229</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02342147124305044</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01924808516765412</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0193597085656005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01937928041262649</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01924808792156911</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01937928041262649</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01728385702663747</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01937928041262649</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.008136190966557391</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.003271926246964267</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.005376934177072457</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.003271926246964267</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.003271926246964267</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.006420527866448044</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.006136701345871658</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.003271926246964267</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.008112966522508456</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.008444106010709372</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.0007414050132747414</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.009187816330979634</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.004580021250846755</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.009187816330979627</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.004580021250846754</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.008064116346676404</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.004580021250846755</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.004580021250846755</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.008481600938192011</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.00837721111052292</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.004580021250846755</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.009179149806945447</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.00931332060299318</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.005580308599473447</v>
+      <c r="E11" t="n">
+        <v>0.004580021250846754</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.004580021250846754</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.008481600938192004</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.008377211110522916</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.004580021250846754</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.009179149806945451</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.009313320602993178</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.005580308599473449</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03276133159311482</v>
+        <v>0.00972334973491586</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02790546019177458</v>
+        <v>0.005278655136531844</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07935207103928549</v>
+        <v>0.009781081640862931</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02790546019177458</v>
+        <v>0.005278655136531844</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02790546019177458</v>
+        <v>0.005278655136531844</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06970936614136553</v>
+        <v>0.009754289417508223</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08308123159615224</v>
+        <v>0.009776387008900052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02790546019177458</v>
+        <v>0.005278655136531844</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09412969759987096</v>
+        <v>0.00978532585277782</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04902086187525933</v>
+        <v>0.009743063126728679</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6271645655508229</v>
+        <v>0.009788354899896334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003178701277571728</v>
+        <v>0.009853300227681022</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002848588281451587</v>
+        <v>0.005344441346529797</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003178701277571728</v>
+        <v>0.009853300227681022</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002902308631379984</v>
+        <v>0.005344441346529797</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002902308631379986</v>
+        <v>0.005344441346529797</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00315791668059901</v>
+        <v>0.009841922744645834</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003178701277571728</v>
+        <v>0.009853300227681022</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003039193972430729</v>
+        <v>0.005344441346529797</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003178701277571728</v>
+        <v>0.009853300227681022</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003178701277571728</v>
+        <v>0.009853300227681022</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003178701277571728</v>
+        <v>0.009853300227681022</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009050313066533663</v>
+        <v>0.03276133159311452</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004382652059430125</v>
+        <v>0.02790546019177458</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009091870125213109</v>
+        <v>0.0793520710392854</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004255068100254939</v>
+        <v>0.02790546019177458</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00448150789980589</v>
+        <v>0.02790546019177458</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009029528469560962</v>
+        <v>0.06970936614136557</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004646831018279519</v>
+        <v>0.0830812315961522</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008910805761392665</v>
+        <v>0.02790546019177458</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009079934774326906</v>
+        <v>0.09412969759987115</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00461406461662607</v>
+        <v>0.04902086187525925</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00488760400542011</v>
+        <v>0.6271645655508215</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00666010368664391</v>
+        <v>0.003178701277571712</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006520596381502908</v>
+        <v>0.002848588281451589</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006659973662169466</v>
+        <v>0.003178701277571712</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006514601018772535</v>
+        <v>0.002902308631379991</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006514601018772535</v>
+        <v>0.002902308631379991</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0066393190896712</v>
+        <v>0.003157916680599008</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00666010368664391</v>
+        <v>0.003178701277571716</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006520596381502908</v>
+        <v>0.003039193972430714</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00666010368664391</v>
+        <v>0.003178701277571712</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00666010368664391</v>
+        <v>0.003178701277571712</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00666010368664391</v>
+        <v>0.003178701277571712</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01414525098244919</v>
+        <v>0.009050313066533651</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02150824407308388</v>
+        <v>0.004382652059430111</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02320839337117289</v>
+        <v>0.009091870125213099</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01945566315214514</v>
+        <v>0.004255068100254938</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01424019234682472</v>
+        <v>0.004481507899805893</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02163106636707205</v>
+        <v>0.009029528469560958</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02165185096404455</v>
+        <v>0.004646831018279522</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02151234365890379</v>
+        <v>0.008910805761392667</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02165332622598232</v>
+        <v>0.009079934774326897</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01400581203390163</v>
+        <v>0.004614064616626071</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02949312233646115</v>
+        <v>0.004887604005420109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01498851350541784</v>
+        <v>0.006660103686643913</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0183494878994787</v>
+        <v>0.006520596381502908</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01848899638218162</v>
+        <v>0.006659973662169472</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02238896790243691</v>
+        <v>0.006514601018772536</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01834948572331049</v>
+        <v>0.006514601018772536</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01846821060764699</v>
+        <v>0.006639319089671205</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0184889952046197</v>
+        <v>0.006660103686643913</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0183494878994787</v>
+        <v>0.006520596381502908</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0184889952046197</v>
+        <v>0.006660103686643913</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01646080285592763</v>
+        <v>0.006660103686643913</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0184889952046197</v>
+        <v>0.006660103686643913</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009280129089372233</v>
+        <v>0.01414525098244918</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004893688963477473</v>
+        <v>0.02150824407308385</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008071056610768785</v>
+        <v>0.02320839337117286</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004893688963477473</v>
+        <v>0.01945566315214512</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004893688963477473</v>
+        <v>0.01424019234682472</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008389020455942111</v>
+        <v>0.02163106636707204</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008200911512743658</v>
+        <v>0.02165185096404456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004893688963477473</v>
+        <v>0.02151234365890377</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007996036209368857</v>
+        <v>0.02165332622598235</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008868038087464031</v>
+        <v>0.01400581203390164</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.002811561197319163</v>
+        <v>0.02949312233646109</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01498851350541782</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01834948789947869</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01848899638218162</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02238896790243691</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01834948572331047</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01846821060764699</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01848899520461968</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01834948789947869</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01848899520461968</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01646080285592762</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01848899520461968</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.009280129089372242</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004893688963477489</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.00807105661076879</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.004893688963477489</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.004893688963477489</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.008389020455942118</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.008200911512743662</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.004893688963477489</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.00799603620936885</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.008868038087464043</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.00281156119731916</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.009462555040397339</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.00507356136578042</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.008970155115494439</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.00507356136578042</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.00507356136578042</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009093214246023164</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.009024544877753159</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.00507356136578042</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.008940264805696516</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.009294765713085792</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.00454728784363599</v>
+      <c r="B11" t="n">
+        <v>0.009462555040397344</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.00507356136578043</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.00897015511549445</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.00507356136578043</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.00507356136578043</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.009093214246023166</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.009024544877753164</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.00507356136578043</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.008940264805696527</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.009294765713085799</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004547287843635998</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02175975174209293</v>
+        <v>0.009549968506041912</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02881846791083752</v>
+        <v>0.005156882562160503</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02508978662580441</v>
+        <v>0.009554377291698663</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02881846791083752</v>
+        <v>0.005156882562160503</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02881846791083752</v>
+        <v>0.005156882562160503</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03264787394296526</v>
+        <v>0.009559179417573831</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0233812853168155</v>
+        <v>0.009549697352055578</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02881846791083752</v>
+        <v>0.005156882562160503</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04804716679327266</v>
+        <v>0.009580440101291426</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03469047586543834</v>
+        <v>0.009566998393035537</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03450736559124173</v>
+        <v>0.009562987861735678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003023121666215105</v>
+        <v>0.009689153193473745</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002769534828303367</v>
+        <v>0.005217311352716358</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003023121666215105</v>
+        <v>0.009689153193473745</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002814031025775841</v>
+        <v>0.005217311352716358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002814031025775845</v>
+        <v>0.005217311352716358</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00300467539259808</v>
+        <v>0.009684715545529101</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003023121666215105</v>
+        <v>0.009689153193473745</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002898736496983737</v>
+        <v>0.005217311352716358</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003023121666215105</v>
+        <v>0.009689153193473745</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003023121666215105</v>
+        <v>0.009689153193473745</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003023121666215105</v>
+        <v>0.009689153193473745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008159205874820191</v>
+        <v>0.02175975174209293</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004177804443473761</v>
+        <v>0.02881846791083749</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004337235939198951</v>
+        <v>0.02508978662580439</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004059032565156761</v>
+        <v>0.02881846791083749</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004219734434578771</v>
+        <v>0.02881846791083749</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00814075960120317</v>
+        <v>0.03264787394296498</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008233008210039618</v>
+        <v>0.02338128531681551</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008034820705588822</v>
+        <v>0.02881846791083749</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004465853465612334</v>
+        <v>0.04804716679327252</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004358017916205682</v>
+        <v>0.03469047586543833</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004569693519145109</v>
+        <v>0.03450736559124171</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006094315009200281</v>
+        <v>0.003023121666215111</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005969929839968912</v>
+        <v>0.002769534828303367</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006094192749478223</v>
+        <v>0.003023121666215111</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005964922023470447</v>
+        <v>0.002814031025775841</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005964922023470447</v>
+        <v>0.002814031025775842</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006075868735583255</v>
+        <v>0.003004675392598083</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006094315009200281</v>
+        <v>0.003023121666215111</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005969929839968912</v>
+        <v>0.002898736496983735</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006094315009200281</v>
+        <v>0.003023121666215111</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006094315009200281</v>
+        <v>0.003023121666215111</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006094315009200281</v>
+        <v>0.003023121666215111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01287086162323128</v>
+        <v>0.00815920587482017</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01946142787871202</v>
+        <v>0.004177804443473747</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02098221092601406</v>
+        <v>0.004337235939198951</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01762436726679434</v>
+        <v>0.004059032565156759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01295652082659204</v>
+        <v>0.004219734434578766</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01957068721552067</v>
+        <v>0.008140759601203161</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01958913348913693</v>
+        <v>0.008233008210039614</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01946474831990635</v>
+        <v>0.008034820705588806</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01959045382222864</v>
+        <v>0.004465853465612326</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0127460662741421</v>
+        <v>0.00435801791620568</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02660693022598955</v>
+        <v>0.004569693519145103</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01272084175929256</v>
+        <v>0.006094315009200285</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01547911827656926</v>
+        <v>0.005969929839968907</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01560350473270653</v>
+        <v>0.006094192749478225</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01880564911250854</v>
+        <v>0.005964922023470439</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01547911764350883</v>
+        <v>0.005964922023470439</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01558505717218362</v>
+        <v>0.006075868735583251</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01560350344580064</v>
+        <v>0.006094315009200285</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01547911827656926</v>
+        <v>0.005969929839968907</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01560350344580064</v>
+        <v>0.006094315009200285</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01393327848481938</v>
+        <v>0.006094315009200285</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01560350344580064</v>
+        <v>0.006094315009200285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009343795728268057</v>
+        <v>0.01287086162323129</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004683470825252691</v>
+        <v>0.01946142787871204</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009251636784808951</v>
+        <v>0.02098221092601408</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004683470825252691</v>
+        <v>0.01762436726679434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004683470825252691</v>
+        <v>0.01295652082659203</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009056436620129511</v>
+        <v>0.01957068721552068</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009356181777878055</v>
+        <v>0.0195891334891369</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004683470825252691</v>
+        <v>0.01946474831990632</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008712995601732798</v>
+        <v>0.01959045382222863</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008987636610891398</v>
+        <v>0.01274606627414211</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009080593260716965</v>
+        <v>0.02660693022598956</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01272084175929254</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01547911827656921</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0156035047327065</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0188056491125085</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0154791176435088</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01558505717218358</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01560350344580063</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01547911827656921</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01560350344580063</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01393327848481934</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01560350344580063</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.009343795728268057</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004683470825252689</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.00925163678480896</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.004683470825252689</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.004683470825252689</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.009056436620129513</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00935618177787806</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.004683470825252689</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.008712995601732807</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.008987636610891395</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.009080593260716972</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.00939282975878439</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.004913983420915721</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.009355305931474111</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.004913983420915721</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.004913983420915721</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009273310504310879</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.009398194296842596</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.004913983420915721</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>0.009392829758784391</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.004913983420915718</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.009355305931474118</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.004913983420915718</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.004913983420915718</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.009273310504310874</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.009398194296842605</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.004913983420915718</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.009136285286219624</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.009247806112359862</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.009286091152965921</v>
+      <c r="K11" t="n">
+        <v>0.009247806112359858</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.009286091152965923</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02887701635229297</v>
+        <v>0.009425144869305667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03298354752315549</v>
+        <v>0.004945213790713594</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02206612185215428</v>
+        <v>0.009416621303485292</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03298354752315549</v>
+        <v>0.004945213790713594</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03298354752315549</v>
+        <v>0.004945213790713594</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03138785712446839</v>
+        <v>0.009424745705967786</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0229028662363039</v>
+        <v>0.009415417500903482</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03298354752315549</v>
+        <v>0.004945213790713594</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04243467535427985</v>
+        <v>0.009439584882198081</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03102770929192999</v>
+        <v>0.009429131683134665</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03258869011403042</v>
+        <v>0.009426849196578801</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003023365350841558</v>
+        <v>0.009553425375269146</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002794379493100899</v>
+        <v>0.004997151555442571</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003023365350841559</v>
+        <v>0.009553425375269146</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002837442766727401</v>
+        <v>0.004997151555442571</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002837442766727401</v>
+        <v>0.004997151555442571</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003006138379415592</v>
+        <v>0.009550248453666182</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003023365350841559</v>
+        <v>0.009553425375269146</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002907047065125843</v>
+        <v>0.004997151555442571</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003023365350841558</v>
+        <v>0.009553425375269146</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003023365350841559</v>
+        <v>0.009553425375269146</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003023365350841559</v>
+        <v>0.009553425375269146</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004367945307934181</v>
+        <v>0.02887701635229297</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004212955830051952</v>
+        <v>0.03298354752315551</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004339076602679358</v>
+        <v>0.02206612185215426</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004093408962331633</v>
+        <v>0.03298354752315551</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004246300659858494</v>
+        <v>0.03298354752315551</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004350718336508216</v>
+        <v>0.03138785712446869</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008165132582706626</v>
+        <v>0.02290286623630391</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004251627022218468</v>
+        <v>0.03298354752315551</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004478872332340991</v>
+        <v>0.04243467535427994</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004369891743021787</v>
+        <v>0.03102770929193005</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004361185220375669</v>
+        <v>0.03258869011403044</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00608083835840295</v>
+        <v>0.003023365350841553</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005964520072687227</v>
+        <v>0.002794379493100897</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006080715094619035</v>
+        <v>0.003023365350841553</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005959467004290401</v>
+        <v>0.002837442766727399</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005959467004290401</v>
+        <v>0.002837442766727399</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006063611386976977</v>
+        <v>0.003006138379415582</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00608083835840295</v>
+        <v>0.003023365350841553</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005964520072687227</v>
+        <v>0.002907047065125836</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00608083835840295</v>
+        <v>0.003023365350841553</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00608083835840295</v>
+        <v>0.003023365350841553</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00608083835840295</v>
+        <v>0.003023365350841553</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01283922925504521</v>
+        <v>0.004367945307934186</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0194125415625342</v>
+        <v>0.004212955830051956</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02092006317633734</v>
+        <v>0.004339076602679363</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01758239733249911</v>
+        <v>0.004093408962331643</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01293212778197711</v>
+        <v>0.004246300659858489</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01951499960871461</v>
+        <v>0.004350718336508214</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01953222658013945</v>
+        <v>0.008165132582706619</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01941590829442487</v>
+        <v>0.004251627022218468</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01953354194613474</v>
+        <v>0.004478872332340978</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01271490339352045</v>
+        <v>0.004369891743021778</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02652362194576378</v>
+        <v>0.004361185220375672</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01230375487164656</v>
+        <v>0.006080838358402945</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01495249813803363</v>
+        <v>0.005964520072687234</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01506881760707009</v>
+        <v>0.00608071509461903</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01814332085972175</v>
+        <v>0.005959467004290401</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01495249753774575</v>
+        <v>0.005959467004290401</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01505158945232337</v>
+        <v>0.006063611386976981</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01506881642374936</v>
+        <v>0.006080838358402945</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01495249813803363</v>
+        <v>0.005964520072687234</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01506881642374936</v>
+        <v>0.006080838358402945</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01340173065658157</v>
+        <v>0.006080838358402945</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01506881642374936</v>
+        <v>0.006080838358402945</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009023684859259166</v>
+        <v>0.01283922925504522</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004358639537517708</v>
+        <v>0.01941254156253422</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009202541985922744</v>
+        <v>0.02092006317633734</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004358639537517708</v>
+        <v>0.01758239733249913</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004358639537517708</v>
+        <v>0.01293212778197713</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008965224474216375</v>
+        <v>0.0195149996087146</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009234010039784499</v>
+        <v>0.01953222658013941</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004358639537517708</v>
+        <v>0.01941590829442492</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00872770626187915</v>
+        <v>0.01953354194613476</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008940812146955081</v>
+        <v>0.01271490339352046</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009279337616429907</v>
+        <v>0.02652362194576374</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01230375487164658</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01495249813803365</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01506881760707011</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01814332085972178</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01495249753774577</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01505158945232339</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01506881642374937</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01495249813803365</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01506881642374937</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01340173065658158</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01506881642374937</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.009023684859259168</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004358639537517714</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.00920254198592275</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.004358639537517714</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.004358639537517714</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.008965224474216375</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.009234010039784496</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.004358639537517714</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.008727706261879156</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.008940812146955085</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.009279337616429913</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.009184111246338268</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.00465468878774071</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.009184111246338266</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.004654688787740713</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.009256968243133672</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.00465468878774071</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.00465468878774071</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009158557930957328</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.009270082505341696</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.00465468878774071</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.009063880054194956</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="E11" t="n">
+        <v>0.004654688787740713</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.004654688787740713</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.009158557930957325</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.009270082505341695</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.004654688787740713</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.009063880054194942</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.00915039071196925</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.009288452294689333</v>
+      <c r="L11" t="n">
+        <v>0.009288452294689326</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08673351714236067</v>
+        <v>0.01016990182147338</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04493427183697209</v>
+        <v>0.005592155818508811</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2498071657845298</v>
+        <v>0.01035998498877741</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04493427183697209</v>
+        <v>0.005592155818508811</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04493427183697209</v>
+        <v>0.005592155818508811</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1744451155552426</v>
+        <v>0.01023972864915976</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2167937925809999</v>
+        <v>0.01030479553967754</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04493427183697209</v>
+        <v>0.005592155818508811</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1312766443698883</v>
+        <v>0.01020907515970782</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07849757828280216</v>
+        <v>0.01015987467461777</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1547671031255927</v>
+        <v>0.01063480594345419</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003469570395138774</v>
+        <v>0.01024225284534997</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003063145670503261</v>
+        <v>0.005641555551575837</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003469570395138774</v>
+        <v>0.01024225284534997</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003123320544463994</v>
+        <v>0.005641555551575837</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003123320544463981</v>
+        <v>0.005641555551575837</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003445643437026865</v>
+        <v>0.01021607797181559</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003469570395138774</v>
+        <v>0.01024225284534997</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003310050060660287</v>
+        <v>0.005641555551575837</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003469570395138774</v>
+        <v>0.01024225284534997</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003469570395138774</v>
+        <v>0.01024225284534997</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003469570395138774</v>
+        <v>0.01024225284534997</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00516413704985765</v>
+        <v>0.08673351714236058</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004770614399906092</v>
+        <v>0.04493427183697156</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005438178960343238</v>
+        <v>0.2498071657845302</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004633093309874259</v>
+        <v>0.04493427183697156</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004981631955836564</v>
+        <v>0.04493427183697156</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01007079729882212</v>
+        <v>0.1744451155552432</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01025882317780077</v>
+        <v>0.2167937925810004</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009935203922455539</v>
+        <v>0.04493427183697156</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01015774817893868</v>
+        <v>0.1312766443698883</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005059746069090945</v>
+        <v>0.07849757828280221</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005395421609713229</v>
+        <v>0.1547671031255938</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00737804919350446</v>
+        <v>0.003469570395138752</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007218528859025977</v>
+        <v>0.003063145670503247</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007377913960162873</v>
+        <v>0.003469570395138752</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007212910401732163</v>
+        <v>0.003123320544463985</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007212910401732163</v>
+        <v>0.003123320544463987</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007354122235392546</v>
+        <v>0.003445643437026867</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00737804919350446</v>
+        <v>0.003469570395138752</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007218528859025977</v>
+        <v>0.003310050060660265</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00737804919350446</v>
+        <v>0.003469570395138752</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00737804919350446</v>
+        <v>0.003469570395138752</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00737804919350446</v>
+        <v>0.003469570395138752</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01523682526626951</v>
+        <v>0.005164137049857656</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02317834474800451</v>
+        <v>0.004770614399906071</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02502203381098234</v>
+        <v>0.005438178960343241</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02096214891376337</v>
+        <v>0.004633093309874244</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01533093898583039</v>
+        <v>0.004981631955836546</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02331755375008843</v>
+        <v>0.01007079729882211</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02334148070819987</v>
+        <v>0.01025882317780079</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0231819603737218</v>
+        <v>0.009935203922455527</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02334307350491077</v>
+        <v>0.01015774817893868</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01508627713053108</v>
+        <v>0.005059746069090911</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03180747101726832</v>
+        <v>0.00539542160971324</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0178804544433876</v>
+        <v>0.007378049193504457</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02197962029006285</v>
+        <v>0.007218528859025967</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02213914362484597</v>
+        <v>0.007377913960162883</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02689405200793729</v>
+        <v>0.007212910401732182</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02197961665113826</v>
+        <v>0.007212910401732182</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02211521366642932</v>
+        <v>0.007354122235392557</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02213914062454134</v>
+        <v>0.007378049193504457</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02197962029006285</v>
+        <v>0.007218528859025967</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02213914062454134</v>
+        <v>0.007378049193504457</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01967164238794609</v>
+        <v>0.007378049193504457</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02213914062454134</v>
+        <v>0.007378049193504457</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008385640056386291</v>
+        <v>0.01523682526626952</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00478715870196623</v>
+        <v>0.0231783447480045</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004404718611587912</v>
+        <v>0.02502203381098235</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00478715870196623</v>
+        <v>0.02096214891376335</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00478715870196623</v>
+        <v>0.01533093898583039</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006366373878318764</v>
+        <v>0.02331755375008839</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005648108116405626</v>
+        <v>0.02334148070819985</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00478715870196623</v>
+        <v>0.02318196037372182</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007585889599934982</v>
+        <v>0.0233430735049107</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008597647218543995</v>
+        <v>0.01508627713053108</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.001177348729025905</v>
+        <v>0.03180747101726835</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01788045444338763</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02197962029006286</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02213914362484599</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02689405200793727</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02197961665113829</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02211521366642937</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02213914062454131</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02197962029006286</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02213914062454131</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01967164238794612</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02213914062454131</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.008385640056386272</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004787158701966217</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.004404718611587894</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.004787158701966217</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.004787158701966217</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.006366373878318753</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00564810811640561</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.004787158701966217</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.00758588959993499</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.008597647218543983</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.001177348729025926</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.009325137085821028</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.005203402529135235</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.007703888309297864</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.005203402529135235</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.005203402529135235</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.008488101018339675</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.008214445047337274</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.005203402529135235</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="C11" t="n">
+        <v>0.005203402529135222</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.007703888309297873</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005203402529135222</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005203402529135222</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.008488101018339664</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.008214445047337291</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005203402529135222</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.009000421417716599</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.009411573873373876</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.008861727225021005</v>
+      <c r="K11" t="n">
+        <v>0.009411573873373867</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.008861727225021003</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,321 +9079,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01738213244756468</v>
+        <v>0.009794434908614985</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02597240465654514</v>
+        <v>0.00532312694898763</v>
       </c>
       <c r="D2" t="n">
-        <v>0.179234482157992</v>
+        <v>0.01000477948274595</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02597240465654514</v>
+        <v>0.00532312694898763</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02597240465654514</v>
+        <v>0.00532312694898763</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09029978882849965</v>
+        <v>0.009868166108133127</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04129318457170687</v>
+        <v>0.009820342516848934</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02597240465654514</v>
+        <v>0.00532312694898763</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06094671935578518</v>
+        <v>0.009842673596501456</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03063789967721393</v>
+        <v>0.009811262093524068</v>
       </c>
       <c r="L2" t="n">
-        <v>3.155388334040374</v>
+        <v>0.009818368776983371</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003231725787291969</v>
+        <v>0.009941255565918234</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002913853845559093</v>
+        <v>0.005389261531364279</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003231725787291969</v>
+        <v>0.009941255565918234</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002963873796889761</v>
+        <v>0.005389261531364279</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002963873796889761</v>
+        <v>0.005389261531364279</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003210645873803329</v>
+        <v>0.009925151941812821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003231725787291969</v>
+        <v>0.009941255565918234</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003090513624850904</v>
+        <v>0.005389261531364279</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003231725787291969</v>
+        <v>0.009941255565918234</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003231725787291969</v>
+        <v>0.009941255565918234</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003231725787291969</v>
+        <v>0.009941255565918234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009831812323990842</v>
+        <v>0.01738213244756468</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004381121570992112</v>
+        <v>0.02597240465654515</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004919532393473841</v>
+        <v>0.1792344821579918</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00425849719173955</v>
+        <v>0.02597240465654515</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004505958387913142</v>
+        <v>0.02597240465654515</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009810732410502218</v>
+        <v>0.09029978882849975</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009886472895901624</v>
+        <v>0.0412931845717069</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009690600161549779</v>
+        <v>0.02597240465654515</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004793058743410701</v>
+        <v>0.06094671935578518</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004589076103694137</v>
+        <v>0.0306378996772139</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005848444470608963</v>
+        <v>3.155388334040368</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006556755070343838</v>
+        <v>0.003231725787291973</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006415542907902766</v>
+        <v>0.002913853845559104</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006556632788674486</v>
+        <v>0.003231725787291973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00640943928909579</v>
+        <v>0.002963873796889762</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00640943928909579</v>
+        <v>0.002963873796889763</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0065356751568552</v>
+        <v>0.003210645873803341</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006556755070343838</v>
+        <v>0.003231725787291973</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006415542907902766</v>
+        <v>0.003090513624850922</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006556755070343838</v>
+        <v>0.003231725787291973</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006556755070343838</v>
+        <v>0.003231725787291973</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006556755070343838</v>
+        <v>0.003231725787291973</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01366344583948112</v>
+        <v>0.009831812323990842</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02066423463790547</v>
+        <v>0.004381121570992098</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02229155977147346</v>
+        <v>0.004919532393473842</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01871021864513007</v>
+        <v>0.004258497191739554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01374519172386587</v>
+        <v>0.004505958387913147</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02078865107800058</v>
+        <v>0.009810732410502213</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02080973099148887</v>
+        <v>0.009886472895901648</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02066851882904818</v>
+        <v>0.009690600161549788</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02081113544123122</v>
+        <v>0.004793058743410705</v>
       </c>
       <c r="K6" t="n">
-        <v>0.013530699923882</v>
+        <v>0.004589076103694143</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02827462339541166</v>
+        <v>0.005848444470608962</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0142788025668941</v>
+        <v>0.006556755070343837</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01741821702332887</v>
+        <v>0.006415542907902764</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01755942862756329</v>
+        <v>0.006556632788674487</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02120398439021827</v>
+        <v>0.006409439289095806</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01741821247439629</v>
+        <v>0.006409439289095806</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01753834927228128</v>
+        <v>0.006535675156855209</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01755942918576991</v>
+        <v>0.006556755070343837</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01741821702332887</v>
+        <v>0.006415542907902764</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01755942918576991</v>
+        <v>0.006556755070343837</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01565862100399884</v>
+        <v>0.006556755070343837</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01755942918576991</v>
+        <v>0.006556755070343837</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009715111909510693</v>
+        <v>0.01366344583948116</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00494859233444426</v>
+        <v>0.02066423463790561</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005308837545693654</v>
+        <v>0.02229155977147356</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00494859233444426</v>
+        <v>0.0187102186451302</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00494859233444426</v>
+        <v>0.01374519172386596</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007826501931213252</v>
+        <v>0.02078865107800066</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009187010805302709</v>
+        <v>0.020809730991489</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00494859233444426</v>
+        <v>0.02066851882904823</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008713920557772417</v>
+        <v>0.02081113544123132</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009363064895512653</v>
+        <v>0.01353069992388206</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.05831798092190794</v>
+        <v>0.02827462339541179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01427880256689407</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01741821702332884</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01755942862756326</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02120398439021824</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01741821247439626</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01753834927228129</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0175594291857699</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01741821702332884</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0175594291857699</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01565862100399886</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0175594291857699</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0097151119095107</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004948592334444262</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.005308837545693666</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.004948592334444262</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.004948592334444262</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.007826501931213274</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.009187010805302714</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.004948592334444262</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.008713920557772422</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.009363064895512665</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.0583179809219079</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.009691538824272476</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.005122621060059612</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.00789701452090345</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.005122621060059612</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.005122621060059612</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.008913273665309567</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.009477158747133438</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.005122621060059612</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.009284232256510509</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.00954818349590519</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.01796619340823453</v>
+      <c r="B11" t="n">
+        <v>0.009691538824272488</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.005122621060059619</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.007897014520903458</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.005122621060059619</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005122621060059619</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.008913273665309571</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.009477158747133441</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005122621060059619</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.009284232256510516</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.009548183495905192</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.01796619340823452</v>
       </c>
     </row>
   </sheetData>
